--- a/Excel/尊尼获加/莫菲丝.xlsx
+++ b/Excel/尊尼获加/莫菲丝.xlsx
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="669">
   <si>
     <t>Id</t>
   </si>
@@ -313,6 +313,15 @@
     <t>UnitData[]</t>
   </si>
   <si>
+    <t>莫菲丝</t>
+  </si>
+  <si>
+    <t>沃尔夫</t>
+  </si>
+  <si>
+    <t>卡尔顿</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
@@ -370,6 +379,9 @@
     <t>部署策略</t>
   </si>
   <si>
+    <t>可部署上限</t>
+  </si>
+  <si>
     <t>仇恨等级</t>
   </si>
   <si>
@@ -526,6 +538,9 @@
     <t>RedeployPolicy</t>
   </si>
   <si>
+    <t>BuildCountLimit</t>
+  </si>
+  <si>
     <t>Hatred</t>
   </si>
   <si>
@@ -676,9 +691,6 @@
     <t>System.Collections.Generic.Dictionary&lt;string,object&gt;</t>
   </si>
   <si>
-    <t>莫菲丝</t>
-  </si>
-  <si>
     <t>干员</t>
   </si>
   <si>
@@ -733,9 +745,6 @@
     <t>B_Die</t>
   </si>
   <si>
-    <t>沃尔夫</t>
-  </si>
-  <si>
     <t>mjcgst</t>
   </si>
   <si>
@@ -763,9 +772,6 @@
     <t>Die</t>
   </si>
   <si>
-    <t>卡尔顿</t>
-  </si>
-  <si>
     <t>mjcbat</t>
   </si>
   <si>
@@ -2224,6 +2230,9 @@
     <t>MapHp</t>
   </si>
   <si>
+    <t>UnitTypeEnum[]</t>
+  </si>
+  <si>
     <t>仅单面</t>
   </si>
   <si>
@@ -2297,16 +2306,14 @@
   </si>
   <si>
     <t>/Spine/卡尔顿/enemy_10106_mjcbat.skel.bytes</t>
-  </si>
-  <si>
-    <t>UnitTypeEnum[]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2319,19 +2326,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2365,17 +2359,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2687,11 +2684,11 @@
   <dimension ref="A2:B6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="9" customWidth="1" style="1"/>
+    <col min="3" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2699,7 +2696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2707,1021 +2704,1249 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>125</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BT7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.58203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.25" style="1" customWidth="1"/>
-    <col min="8" max="10" width="9" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="4" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.75" style="1" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" style="1" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" style="1" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10.25" style="1" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.75" style="1" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="10.75" style="1" customWidth="1"/>
-    <col min="27" max="28" width="9" style="1" customWidth="1"/>
-    <col min="29" max="29" width="8" style="1" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" style="1" customWidth="1"/>
-    <col min="31" max="31" width="9" style="1" customWidth="1"/>
-    <col min="32" max="32" width="9.75" style="1" customWidth="1"/>
-    <col min="33" max="33" width="7.83203125" style="1" customWidth="1"/>
-    <col min="34" max="34" width="15.83203125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="13.83203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="34.5" style="1" customWidth="1"/>
-    <col min="37" max="38" width="9.83203125" style="1" customWidth="1"/>
-    <col min="39" max="42" width="9" style="1" customWidth="1"/>
-    <col min="43" max="43" width="12.5" style="1" customWidth="1"/>
-    <col min="44" max="49" width="9" style="1" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" style="1" customWidth="1"/>
-    <col min="51" max="51" width="9" style="1" customWidth="1"/>
-    <col min="52" max="52" width="17.75" style="1" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" style="1" customWidth="1"/>
-    <col min="54" max="55" width="9" style="1" customWidth="1"/>
-    <col min="56" max="56" width="24.25" style="1" customWidth="1"/>
-    <col min="57" max="57" width="13.25" style="1" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" style="1" customWidth="1"/>
-    <col min="59" max="59" width="8" style="1" customWidth="1"/>
-    <col min="60" max="61" width="9" style="1" customWidth="1"/>
-    <col min="62" max="62" width="27.33203125" style="1" customWidth="1"/>
-    <col min="63" max="63" width="9" style="1" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" style="1" customWidth="1"/>
-    <col min="65" max="65" width="14" style="1" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" style="1" customWidth="1"/>
-    <col min="67" max="70" width="14" style="1" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" style="1" customWidth="1"/>
-    <col min="72" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
+    <col min="8" max="8" width="9" customWidth="1" style="2"/>
+    <col min="9" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="9" customWidth="1" style="2"/>
+    <col min="11" max="11" width="6" customWidth="1" style="2"/>
+    <col min="12" max="12" width="5.5" customWidth="1" style="2"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="4" customWidth="1" style="2"/>
+    <col min="15" max="15" width="7.75" customWidth="1" style="2"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1" style="2"/>
+    <col min="17" max="17" width="3.83203125" customWidth="1" style="2"/>
+    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="3.58203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="10.25" customWidth="1" style="2"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1" style="2"/>
+    <col min="23" max="23" width="10.75" customWidth="1" style="2"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1" style="2"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="10.75" customWidth="1" style="2"/>
+    <col min="27" max="27" width="9" customWidth="1" style="2"/>
+    <col min="28" max="28" width="9" customWidth="1" style="2"/>
+    <col min="29" max="29" width="8" customWidth="1" style="2"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1" style="2"/>
+    <col min="31" max="31" width="9" customWidth="1" style="2"/>
+    <col min="32" max="32" width="9" customWidth="1" style="2"/>
+    <col min="33" max="33" width="9.75" customWidth="1" style="2"/>
+    <col min="34" max="34" width="7.83203125" customWidth="1" style="2"/>
+    <col min="35" max="35" width="15.83203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="13.83203125" customWidth="1" style="2"/>
+    <col min="37" max="37" width="34.5" customWidth="1" style="2"/>
+    <col min="38" max="38" width="9.83203125" customWidth="1" style="2"/>
+    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="9" customWidth="1" style="2"/>
+    <col min="41" max="41" width="9" customWidth="1" style="2"/>
+    <col min="42" max="42" width="9" customWidth="1" style="2"/>
+    <col min="43" max="43" width="9" customWidth="1" style="2"/>
+    <col min="44" max="44" width="12.5" customWidth="1" style="2"/>
+    <col min="45" max="45" width="9" customWidth="1" style="2"/>
+    <col min="46" max="46" width="9" customWidth="1" style="2"/>
+    <col min="47" max="47" width="9" customWidth="1" style="2"/>
+    <col min="48" max="48" width="9" customWidth="1" style="2"/>
+    <col min="49" max="49" width="9" customWidth="1" style="2"/>
+    <col min="50" max="50" width="9" customWidth="1" style="2"/>
+    <col min="51" max="51" width="24.33203125" customWidth="1" style="2"/>
+    <col min="52" max="52" width="9" customWidth="1" style="2"/>
+    <col min="53" max="53" width="17.75" customWidth="1" style="2"/>
+    <col min="54" max="54" width="7.83203125" customWidth="1" style="2"/>
+    <col min="55" max="55" width="9" customWidth="1" style="2"/>
+    <col min="56" max="56" width="9" customWidth="1" style="2"/>
+    <col min="57" max="57" width="24.25" customWidth="1" style="2"/>
+    <col min="58" max="58" width="13.25" customWidth="1" style="2"/>
+    <col min="59" max="59" width="16.08203125" customWidth="1" style="2"/>
+    <col min="60" max="60" width="8" customWidth="1" style="2"/>
+    <col min="61" max="61" width="9" customWidth="1" style="2"/>
+    <col min="62" max="62" width="9" customWidth="1" style="2"/>
+    <col min="63" max="63" width="27.33203125" customWidth="1" style="2"/>
+    <col min="64" max="64" width="9" customWidth="1" style="2"/>
+    <col min="65" max="65" width="39.58203125" customWidth="1" style="2"/>
+    <col min="66" max="66" width="14" customWidth="1" style="2"/>
+    <col min="67" max="67" width="14.83203125" customWidth="1" style="2"/>
+    <col min="68" max="68" width="14" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="71" max="71" width="14" customWidth="1" style="2"/>
+    <col min="72" max="72" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="D1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AY1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="BB1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BC1" s="2"/>
+      <c r="BD1" s="2"/>
+      <c r="BE1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="BF1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="BG1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="BH1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="BI1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BJ1" s="2"/>
+      <c r="BK1" s="2"/>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2"/>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BD2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BI2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BK2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AS3" s="2"/>
+      <c r="AT3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2"/>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2"/>
+      <c r="BA4" s="2"/>
+      <c r="BB4" s="2"/>
+      <c r="BC4" s="2"/>
+      <c r="BD4" s="2"/>
+      <c r="BE4" s="2"/>
+      <c r="BF4" s="2"/>
+      <c r="BG4" s="2"/>
+      <c r="BH4" s="2"/>
+      <c r="BI4" s="2"/>
+      <c r="BJ4" s="2"/>
+      <c r="BK4" s="2"/>
+      <c r="BL4" s="2"/>
+      <c r="BM4" s="2"/>
+      <c r="BN4" s="2"/>
+      <c r="BO4" s="2"/>
+      <c r="BP4" s="2"/>
+      <c r="BQ4" s="2"/>
+      <c r="BR4" s="2"/>
+      <c r="BS4" s="2"/>
+      <c r="BT4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2">
+        <v>90</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1950</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2">
+        <v>605</v>
+      </c>
+      <c r="N5" s="2">
+        <v>90</v>
+      </c>
+      <c r="O5" s="2">
+        <v>125</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2">
+        <v>25</v>
+      </c>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2">
+        <v>13</v>
+      </c>
+      <c r="T5" s="2">
+        <v>-2</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="V5" s="2">
+        <v>70</v>
+      </c>
+      <c r="W5" s="2">
+        <v>-4</v>
+      </c>
+      <c r="X5" s="2">
+        <v>7</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM5" s="2"/>
+      <c r="AN5" s="2"/>
+      <c r="AO5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AP5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AR5" s="2"/>
+      <c r="AS5" s="2"/>
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2"/>
+      <c r="AW5" s="2"/>
+      <c r="AX5" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="AY5" s="2"/>
+      <c r="AZ5" s="2"/>
+      <c r="BA5" s="2"/>
+      <c r="BB5" s="2"/>
+      <c r="BC5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BD5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BE5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BI5" s="2">
+        <v>6</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BK5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BL5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BN5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="BP5" s="2"/>
+      <c r="BQ5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BS5" s="2"/>
+      <c r="BT5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2">
+        <v>90</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1500</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2">
+        <v>520</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2">
+        <v>115</v>
+      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2">
+        <v>50</v>
+      </c>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="V6" s="2">
+        <v>25</v>
+      </c>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2"/>
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AM6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="2"/>
+      <c r="AO6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AP6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AR6" s="2"/>
+      <c r="AS6" s="2"/>
+      <c r="AT6" s="2"/>
+      <c r="AU6" s="2"/>
+      <c r="AV6" s="2"/>
+      <c r="AW6" s="2"/>
+      <c r="AX6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="AY6" s="2"/>
+      <c r="AZ6" s="2"/>
+      <c r="BA6" s="2"/>
+      <c r="BB6" s="2"/>
+      <c r="BC6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BD6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BE6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BF6" s="2"/>
+      <c r="BG6" s="2"/>
+      <c r="BH6" s="2"/>
+      <c r="BI6" s="2">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="BJ6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BK6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BL6" s="2"/>
+      <c r="BM6" s="2"/>
+      <c r="BN6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BO6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BP6" s="2"/>
+      <c r="BQ6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BS6" s="2"/>
+      <c r="BT6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2">
+        <v>90</v>
+      </c>
+      <c r="K7" s="2">
+        <v>100</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2">
+        <v>175</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
         <v>10</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AU2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AV2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="BB2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="BF2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="BG2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="BH2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ2" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="BK2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="BL2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="BO2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="BP2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS2" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AH3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AK3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AN3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AO3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AP3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AQ3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AS3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AT3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AU3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AV3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AW3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AY3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AZ3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="BA3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BD3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BI3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BJ3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BL3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="BM3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BN3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BO3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1">
-        <v>90</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1950</v>
-      </c>
-      <c r="M5" s="1">
-        <v>605</v>
-      </c>
-      <c r="N5" s="1">
-        <v>90</v>
-      </c>
-      <c r="O5" s="1">
-        <v>125</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>25</v>
-      </c>
-      <c r="S5" s="1">
-        <v>13</v>
-      </c>
-      <c r="T5" s="1">
-        <v>-2</v>
-      </c>
-      <c r="U5" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="V5" s="1">
-        <v>70</v>
-      </c>
-      <c r="W5" s="1">
-        <v>-4</v>
-      </c>
-      <c r="X5" s="1">
-        <v>7</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI5" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AJ5" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AK5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN5" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AO5" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP5" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="AW5" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="BB5" s="1" t="s">
+      <c r="AD7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="2"/>
+      <c r="AF7" s="2"/>
+      <c r="AG7" s="2"/>
+      <c r="AH7" s="2"/>
+      <c r="AI7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="BC5" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="BD5" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="BE5" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="BF5" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="BG5" s="1" t="s">
+      <c r="AK7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="2"/>
+      <c r="AO7" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AP7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="2"/>
+      <c r="AS7" s="2"/>
+      <c r="AT7" s="2"/>
+      <c r="AU7" s="2"/>
+      <c r="AV7" s="2"/>
+      <c r="AW7" s="2"/>
+      <c r="AX7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="2"/>
+      <c r="AZ7" s="2"/>
+      <c r="BA7" s="2"/>
+      <c r="BB7" s="2"/>
+      <c r="BC7" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="BH5" s="1">
+      <c r="BD7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BE7" s="2"/>
+      <c r="BF7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="BG7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="BH7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BI7" s="2">
         <v>6</v>
       </c>
-      <c r="BI5" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="BJ5" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="BK5" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="BL5" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="BM5" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="BN5" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="BP5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BQ5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BS5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>90</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1500</v>
-      </c>
-      <c r="M6" s="1">
-        <v>520</v>
-      </c>
-      <c r="O6" s="1">
-        <v>115</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>50</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
-      <c r="U6" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="V6" s="1">
-        <v>25</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AJ6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AK6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AL6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AO6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP6" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="AW6" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="BB6" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC6" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="BD6" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="BH6" s="1">
-        <v>6</v>
-      </c>
-      <c r="BI6" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="BJ6" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="BM6" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="BN6" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BP6" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BQ6" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BS6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="BJ7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="BK7" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BL7" s="2"/>
+      <c r="BM7" s="2"/>
+      <c r="BN7" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="BO7" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
-        <v>2</v>
-      </c>
-      <c r="J7" s="1">
-        <v>90</v>
-      </c>
-      <c r="K7" s="1">
-        <v>100</v>
-      </c>
-      <c r="M7" s="1">
-        <v>175</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1">
-        <v>10</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
+      <c r="BP7" s="2"/>
+      <c r="BQ7" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AK7" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AL7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN7" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AO7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB7" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="BE7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="BF7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="BG7" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="BH7" s="1">
-        <v>6</v>
-      </c>
-      <c r="BI7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="BJ7" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="BM7" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="BN7" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BP7" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BQ7" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BS7" s="1">
+      <c r="BR7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BS7" s="2"/>
+      <c r="BT7" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3729,6 +3954,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3738,769 +3964,769 @@
   <dimension ref="A1:DI59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" style="1" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="21.5" style="1" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="19.08203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="17.75" style="1" customWidth="1"/>
-    <col min="23" max="23" width="8.33203125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="18.5" style="1" customWidth="1"/>
-    <col min="25" max="25" width="16.58203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" style="1" customWidth="1"/>
-    <col min="29" max="30" width="8.58203125" style="1" customWidth="1"/>
-    <col min="31" max="31" width="13.4140625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="13.75" style="1" customWidth="1"/>
-    <col min="33" max="33" width="14.58203125" style="1" customWidth="1"/>
-    <col min="34" max="34" width="17.4140625" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5" style="1" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" style="1" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" style="1" customWidth="1"/>
-    <col min="40" max="40" width="15" style="1" customWidth="1"/>
-    <col min="41" max="41" width="13.25" style="1" customWidth="1"/>
-    <col min="42" max="45" width="11.83203125" style="1" customWidth="1"/>
-    <col min="46" max="46" width="18.4140625" style="1" customWidth="1"/>
-    <col min="47" max="47" width="12.25" style="1" customWidth="1"/>
-    <col min="48" max="48" width="11.9140625" style="1" customWidth="1"/>
-    <col min="49" max="49" width="19.58203125" style="1" customWidth="1"/>
-    <col min="50" max="50" width="12.6640625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="9" style="1" customWidth="1"/>
-    <col min="52" max="52" width="7" style="1" customWidth="1"/>
-    <col min="53" max="53" width="11.75" style="1" customWidth="1"/>
-    <col min="54" max="54" width="19.75" style="1" customWidth="1"/>
-    <col min="55" max="55" width="5.08203125" style="1" customWidth="1"/>
-    <col min="56" max="56" width="8.5" style="1" customWidth="1"/>
-    <col min="57" max="57" width="13.5" style="1" customWidth="1"/>
-    <col min="58" max="58" width="14.6640625" style="1" customWidth="1"/>
-    <col min="59" max="59" width="10.1640625" style="1" customWidth="1"/>
-    <col min="60" max="60" width="8.25" style="1" customWidth="1"/>
-    <col min="61" max="66" width="8.33203125" style="1" customWidth="1"/>
-    <col min="67" max="67" width="19.25" style="1" customWidth="1"/>
-    <col min="68" max="68" width="22.33203125" style="1" customWidth="1"/>
-    <col min="69" max="70" width="11.25" style="1" customWidth="1"/>
-    <col min="71" max="71" width="6.58203125" style="1" customWidth="1"/>
-    <col min="72" max="73" width="8" style="1" customWidth="1"/>
-    <col min="74" max="74" width="7.33203125" style="1" customWidth="1"/>
-    <col min="75" max="76" width="8.5" style="1" customWidth="1"/>
-    <col min="77" max="78" width="7.83203125" style="1" customWidth="1"/>
-    <col min="79" max="79" width="22.1640625" style="1" customWidth="1"/>
-    <col min="80" max="80" width="35" style="1" customWidth="1"/>
-    <col min="81" max="81" width="20.6640625" style="1" customWidth="1"/>
-    <col min="82" max="82" width="15.75" style="1" customWidth="1"/>
-    <col min="83" max="83" width="15.58203125" style="1" customWidth="1"/>
-    <col min="84" max="84" width="12.83203125" style="1" customWidth="1"/>
-    <col min="85" max="85" width="16.1640625" style="1" customWidth="1"/>
-    <col min="86" max="86" width="9" style="1" customWidth="1"/>
-    <col min="87" max="87" width="16" style="1" customWidth="1"/>
-    <col min="88" max="89" width="12.83203125" style="1" customWidth="1"/>
-    <col min="90" max="90" width="23.58203125" style="1" customWidth="1"/>
-    <col min="91" max="91" width="12.83203125" style="1" customWidth="1"/>
-    <col min="92" max="92" width="25.9140625" style="1" customWidth="1"/>
-    <col min="93" max="93" width="9.5" style="1" customWidth="1"/>
-    <col min="94" max="98" width="9" style="1" customWidth="1"/>
-    <col min="99" max="99" width="14" style="1" customWidth="1"/>
-    <col min="100" max="100" width="8" style="1" customWidth="1"/>
-    <col min="101" max="101" width="9" style="1" customWidth="1"/>
-    <col min="102" max="102" width="11.08203125" style="1" customWidth="1"/>
-    <col min="103" max="103" width="13.75" style="1" customWidth="1"/>
-    <col min="104" max="104" width="9.5" style="1" customWidth="1"/>
-    <col min="105" max="106" width="9" style="1" customWidth="1"/>
-    <col min="107" max="108" width="9.5" style="1" customWidth="1"/>
-    <col min="109" max="109" width="9" style="1" customWidth="1"/>
-    <col min="110" max="110" width="15.5" style="1" customWidth="1"/>
-    <col min="111" max="111" width="9" style="1" customWidth="1"/>
-    <col min="112" max="113" width="9.5" style="1" customWidth="1"/>
-    <col min="114" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1" style="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1" style="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="1"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="1"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="1"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="1"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="1"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="1"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="1"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="1"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="1"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="1"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="1"/>
+    <col min="40" max="40" width="15" customWidth="1" style="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="1"/>
+    <col min="51" max="51" width="9" customWidth="1" style="1"/>
+    <col min="52" max="52" width="7" customWidth="1" style="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="1"/>
+    <col min="61" max="66" width="8.33203125" customWidth="1" style="1"/>
+    <col min="67" max="67" width="19.25" customWidth="1" style="1"/>
+    <col min="68" max="68" width="22.33203125" customWidth="1" style="1"/>
+    <col min="69" max="70" width="11.25" customWidth="1" style="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="1"/>
+    <col min="72" max="73" width="8" customWidth="1" style="1"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="1"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="1"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="1"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="1"/>
+    <col min="80" max="80" width="35" customWidth="1" style="1"/>
+    <col min="81" max="81" width="20.6640625" customWidth="1" style="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="1"/>
+    <col min="86" max="86" width="9" customWidth="1" style="1"/>
+    <col min="87" max="87" width="16" customWidth="1" style="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="1"/>
+    <col min="92" max="92" width="25.9140625" customWidth="1" style="1"/>
+    <col min="93" max="93" width="9.5" customWidth="1" style="1"/>
+    <col min="94" max="98" width="9" customWidth="1" style="1"/>
+    <col min="99" max="99" width="14" customWidth="1" style="1"/>
+    <col min="100" max="100" width="8" customWidth="1" style="1"/>
+    <col min="101" max="101" width="9" customWidth="1" style="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="1"/>
+    <col min="104" max="104" width="9.5" customWidth="1" style="1"/>
+    <col min="105" max="106" width="9" customWidth="1" style="1"/>
+    <col min="107" max="108" width="9.5" customWidth="1" style="1"/>
+    <col min="109" max="109" width="9" customWidth="1" style="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="1"/>
+    <col min="111" max="111" width="9" customWidth="1" style="1"/>
+    <col min="112" max="113" width="9.5" customWidth="1" style="1"/>
+    <col min="114" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="B1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BV1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="CR1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="BW1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="CB1" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="CS1" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="BT2" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="BU2" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="CB2" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="CC2" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="CD2" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="CE2" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="CF2" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="CG2" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="CH2" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="CI2" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="CJ2" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="CK2" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="CL2" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="CM2" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="CN2" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="CO2" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="CP2" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="CQ2" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="CR2" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="CS2" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="CT2" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="CU2" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="CV2" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="CW2" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="CX2" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="CY2" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="CZ2" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="DA2" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="DB2" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="DC2" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="DD2" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="DE2" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="DF2" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="DG2" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="DH2" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="DI2" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4517,112 +4743,112 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="O3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="T3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="Z3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AJ3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AQ3" s="1" t="s">
         <v>2</v>
@@ -4634,222 +4860,222 @@
         <v>2</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AU3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AV3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AY3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AZ3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BA3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BB3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BC3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BD3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BF3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BG3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BH3" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BI3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BJ3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BK3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BL3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BM3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BN3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BO3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BP3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BQ3" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BR3" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="BS3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BT3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BU3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BV3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BW3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BX3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BY3" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BZ3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="CA3" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="CB3" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="CC3" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="CD3" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="CE3" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="CF3" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="CG3" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="CH3" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="CI3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="CK3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="CL3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="CM3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="CN3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="CO3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="CQ3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="CR3" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="CI3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="CK3" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="CL3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="CM3" s="1" t="s">
+      <c r="CS3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="CN3" s="1" t="s">
+      <c r="CU3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="CV3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="CW3" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="CX3" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="CY3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="CZ3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="DA3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="DB3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="DC3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="DD3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="CO3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="CP3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="CQ3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="CR3" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="CS3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="CT3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="CU3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="CV3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="CW3" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="CX3" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="CY3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="CZ3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="DA3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="DB3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="DC3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="DD3" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="DE3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="DF3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="DG3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="DH3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="DI3" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AC5" s="1">
         <v>2</v>
@@ -4858,13 +5084,13 @@
         <v>1</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AT5" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AX5" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AZ5" s="1">
         <v>1</v>
@@ -4873,25 +5099,25 @@
         <v>1</v>
       </c>
       <c r="BO5" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="CB5" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="CG5" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CH5" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="CI5" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="CJ5" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="CN5" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="CO5" s="1">
         <v>-0.1</v>
@@ -4900,66 +5126,66 @@
         <v>2</v>
       </c>
       <c r="CW5" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="CY5" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="DG5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AT6" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="AX6" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="AZ6" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD6" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB6" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CG6" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="CH6" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="CI6" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="CJ6" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="CY5" s="1" t="s">
+      <c r="CN6" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="DG5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="AT6" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="AX6" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="AZ6" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD6" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB6" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="CG6" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="CH6" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="CI6" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="CJ6" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="CN6" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="CO6" s="1">
         <v>-0.1</v>
@@ -4968,66 +5194,66 @@
         <v>2</v>
       </c>
       <c r="CW6" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="CY6" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="DG6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AT7" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="AX7" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="AZ7" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB7" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="CG7" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="CH7" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="CI7" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="CJ7" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="CY6" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="DG6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="AT7" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="AX7" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="AZ7" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD7" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB7" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="CG7" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="CH7" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="CI7" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="CJ7" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="CN7" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="CO7" s="1">
         <v>-0.1</v>
@@ -5036,30 +5262,30 @@
         <v>8</v>
       </c>
       <c r="CW7" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="CY7" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="DG7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AC8" s="1">
         <v>2</v>
@@ -5074,7 +5300,7 @@
         <v>99</v>
       </c>
       <c r="CN8" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="CR8" s="1">
         <v>99999</v>
@@ -5083,21 +5309,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AC9" s="1">
         <v>2</v>
@@ -5112,7 +5338,7 @@
         <v>99</v>
       </c>
       <c r="CN9" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="CO9" s="1">
         <v>-0.1</v>
@@ -5124,21 +5350,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AC10" s="1">
         <v>2</v>
@@ -5156,10 +5382,10 @@
         <v>0.1</v>
       </c>
       <c r="CN10" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="CO10" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="CR10" s="1">
         <v>0.2</v>
@@ -5168,24 +5394,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AC11" s="1">
         <v>2</v>
@@ -5203,10 +5429,10 @@
         <v>0.1</v>
       </c>
       <c r="CN11" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="CO11" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="CR11" s="1">
         <v>0.2</v>
@@ -5215,21 +5441,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="AC12" s="1">
         <v>2</v>
@@ -5247,7 +5473,7 @@
         <v>0.1</v>
       </c>
       <c r="CN12" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="CR12" s="1">
         <v>0.2</v>
@@ -5256,21 +5482,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AC13" s="1">
         <v>2</v>
@@ -5285,10 +5511,10 @@
         <v>1</v>
       </c>
       <c r="BO13" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="CN13" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="CR13" s="1">
         <v>10</v>
@@ -5297,36 +5523,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H14" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AW14" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD14" s="1">
+        <v>1</v>
+      </c>
+      <c r="CN14" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="AC14" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AW14" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD14" s="1">
-        <v>1</v>
-      </c>
-      <c r="CN14" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="CR14" s="1">
         <v>10</v>
@@ -5335,18 +5561,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AC15" s="1">
         <v>2</v>
@@ -5364,7 +5590,7 @@
         <v>0.1</v>
       </c>
       <c r="CN15" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="CR15" s="1">
         <v>0.2</v>
@@ -5373,21 +5599,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AC16" s="1">
         <v>2</v>
@@ -5402,16 +5628,16 @@
         <v>99</v>
       </c>
       <c r="BO16" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="BP16" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="CM16" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="CM16" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="CN16" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="CR16" s="1">
         <v>10.1</v>
@@ -5420,21 +5646,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AC17" s="1">
         <v>2</v>
@@ -5449,13 +5675,13 @@
         <v>99</v>
       </c>
       <c r="BP17" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="CM17" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="CN17" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="CR17" s="1">
         <v>99999</v>
@@ -5464,21 +5690,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AC18" s="1">
         <v>2</v>
@@ -5493,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="BP18" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="BS18" s="1">
         <v>1</v>
@@ -5508,50 +5734,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="AC19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="BD19" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO19" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="CU19" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="DI19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="I19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="AC19" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="BD19" s="1">
-        <v>1</v>
-      </c>
-      <c r="BO19" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="CU19" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="DI19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>447</v>
       </c>
       <c r="AC20" s="1">
         <v>2</v>
@@ -5578,12 +5804,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
@@ -5592,7 +5818,7 @@
         <v>1</v>
       </c>
       <c r="AJ21" s="1" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="AV21" s="1">
         <v>20</v>
@@ -5601,7 +5827,7 @@
         <v>99</v>
       </c>
       <c r="BP21" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="BS21" s="1">
         <v>0.1</v>
@@ -5613,33 +5839,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AC22" s="1">
         <v>1</v>
       </c>
       <c r="AG22" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD22" s="1">
         <v>1</v>
       </c>
       <c r="CN22" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="CR22" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="DH22" s="1">
         <v>1</v>
@@ -5648,39 +5874,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I23" s="1">
         <v>1</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AC23" s="1">
         <v>1</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD23" s="1">
         <v>1</v>
       </c>
       <c r="CB23" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="CG23" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CN23" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="CO23" s="1">
         <v>0.15</v>
@@ -5689,21 +5915,21 @@
         <v>99999</v>
       </c>
     </row>
-    <row r="24" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AC24" s="1">
         <v>2</v>
@@ -5718,16 +5944,16 @@
         <v>99</v>
       </c>
       <c r="BO24" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="BP24" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="CM24" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="CN24" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="CR24" s="1">
         <v>99999</v>
@@ -5739,18 +5965,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AC25" s="1">
         <v>1</v>
@@ -5762,24 +5988,24 @@
         <v>99</v>
       </c>
       <c r="CU25" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="1" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="26" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="I26" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="R26" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AC26" s="1">
         <v>2</v>
@@ -5791,7 +6017,7 @@
         <v>20</v>
       </c>
       <c r="AX26" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AZ26" s="1">
         <v>9999999</v>
@@ -5803,10 +6029,10 @@
         <v>99</v>
       </c>
       <c r="CM26" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="CN26" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="CR26" s="1">
         <v>99999</v>
@@ -5818,45 +6044,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AC27" s="1">
         <v>1</v>
       </c>
       <c r="AG27" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD27" s="1">
         <v>1</v>
       </c>
       <c r="BO27" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="BP27" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="BT27" s="1">
         <v>0.2</v>
@@ -5871,16 +6097,16 @@
         <v>2</v>
       </c>
       <c r="BY27" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="CB27" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="CG27" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CN27" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="CO27" s="1">
         <v>0.08</v>
@@ -5889,15 +6115,15 @@
         <v>99999</v>
       </c>
     </row>
-    <row r="28" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AC28" s="1">
         <v>2</v>
@@ -5906,16 +6132,16 @@
         <v>1</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AR28" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AW28" s="1">
         <v>1</v>
       </c>
       <c r="AX28" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AZ28" s="1">
         <v>1.6</v>
@@ -5924,48 +6150,48 @@
         <v>2</v>
       </c>
       <c r="CG28" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CH28" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="CI28" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="CJ28" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="CN28" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="CR28" s="1">
         <v>5</v>
       </c>
       <c r="CW28" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="CY28" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="DG28" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AC29" s="1">
         <v>2</v>
@@ -5980,7 +6206,7 @@
         <v>99</v>
       </c>
       <c r="CN29" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="CO29" s="1">
         <v>-0.1</v>
@@ -5992,30 +6218,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G30" s="1">
         <v>3</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AB30" s="1">
         <v>1</v>
@@ -6024,13 +6250,13 @@
         <v>1</v>
       </c>
       <c r="AG30" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD30" s="1">
         <v>1</v>
       </c>
       <c r="BO30" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="BT30" s="1">
         <v>15</v>
@@ -6045,33 +6271,33 @@
         <v>1</v>
       </c>
       <c r="BY30" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="CB30" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="CG30" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CM30" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="CN30" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="CR30" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AC31" s="1">
         <v>2</v>
@@ -6080,13 +6306,13 @@
         <v>1</v>
       </c>
       <c r="AO31" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AT31" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AX31" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AZ31" s="1">
         <v>1.2</v>
@@ -6095,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="BJ31" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="BK31" s="1">
         <v>1</v>
@@ -6107,16 +6333,16 @@
         <v>1</v>
       </c>
       <c r="CH31" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="CI31" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="CJ31" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="CN31" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="CO31" s="1">
         <v>-0.1</v>
@@ -6128,27 +6354,27 @@
         <v>2</v>
       </c>
       <c r="CY31" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="DG31" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AC32" s="1">
         <v>2</v>
@@ -6163,10 +6389,10 @@
         <v>99</v>
       </c>
       <c r="CM32" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="CN32" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="CR32" s="1">
         <v>2</v>
@@ -6175,59 +6401,59 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I33" s="1">
         <v>1</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AC33" s="1">
         <v>1</v>
       </c>
       <c r="AG33" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD33" s="1">
         <v>1</v>
       </c>
       <c r="BP33" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="CB33" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="CG33" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CM33" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="CN33" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="CR33" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AC34" s="1">
         <v>2</v>
@@ -6236,13 +6462,13 @@
         <v>1</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AT34" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AX34" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AZ34" s="1">
         <v>3</v>
@@ -6260,13 +6486,13 @@
         <v>1</v>
       </c>
       <c r="CG34" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CJ34" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="CN34" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="CO34" s="1">
         <v>0.8</v>
@@ -6278,21 +6504,21 @@
         <v>8</v>
       </c>
       <c r="CY34" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="DG34" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AC35" s="1">
         <v>2</v>
@@ -6307,27 +6533,27 @@
         <v>99</v>
       </c>
       <c r="CM35" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="DG35" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I36" s="1">
         <v>1</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AC36" s="1">
         <v>2</v>
@@ -6345,10 +6571,10 @@
         <v>0.1</v>
       </c>
       <c r="CN36" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="CO36" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="CR36" s="1">
         <v>0.2</v>
@@ -6357,24 +6583,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AC37" s="1">
         <v>2</v>
@@ -6392,10 +6618,10 @@
         <v>0.1</v>
       </c>
       <c r="CN37" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="CO37" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="CR37" s="1">
         <v>0.2</v>
@@ -6404,21 +6630,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AC38" s="1">
         <v>1</v>
@@ -6427,21 +6653,21 @@
         <v>1</v>
       </c>
       <c r="AG38" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD38" s="1">
         <v>1</v>
       </c>
       <c r="CU38" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="39" spans="1:113" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
@@ -6450,7 +6676,7 @@
         <v>1</v>
       </c>
       <c r="AJ39" s="1" t="s">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="AW39" s="1">
         <v>1</v>
@@ -6462,7 +6688,7 @@
         <v>0.1</v>
       </c>
       <c r="CN39" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="CR39" s="1">
         <v>0.2</v>
@@ -6471,24 +6697,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AC40" s="1">
         <v>1</v>
       </c>
       <c r="AJ40" s="1" t="s">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="AV40" s="1">
         <v>20</v>
@@ -6500,7 +6726,7 @@
         <v>0.1</v>
       </c>
       <c r="CN40" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="CO40" s="1">
         <v>80</v>
@@ -6512,30 +6738,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AB41" s="1">
         <v>1</v>
@@ -6547,13 +6773,13 @@
         <v>1</v>
       </c>
       <c r="AO41" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AT41" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AX41" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AZ41" s="1">
         <v>1</v>
@@ -6562,7 +6788,7 @@
         <v>4</v>
       </c>
       <c r="BO41" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="BT41" s="1">
         <v>35</v>
@@ -6577,34 +6803,34 @@
         <v>1</v>
       </c>
       <c r="BY41" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="CB41" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CE41" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="CG41" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CH41" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="CI41" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="CJ41" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="CN41" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="CR41" s="1">
         <v>1</v>
       </c>
       <c r="CY41" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="DG41" s="1">
         <v>1</v>
@@ -6613,18 +6839,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AC42" s="1">
         <v>1</v>
@@ -6633,10 +6859,10 @@
         <v>1</v>
       </c>
       <c r="BP42" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="CN42" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="CO42" s="1">
         <v>-0.8</v>
@@ -6648,15 +6874,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AC43" s="1">
         <v>2</v>
@@ -6665,13 +6891,13 @@
         <v>1</v>
       </c>
       <c r="AT43" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="BD43" s="1">
         <v>99</v>
       </c>
       <c r="CN43" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="CR43" s="1">
         <v>15</v>
@@ -6680,15 +6906,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AC44" s="1">
         <v>2</v>
@@ -6706,10 +6932,10 @@
         <v>0.1</v>
       </c>
       <c r="CN44" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="CO44" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="CR44" s="1">
         <v>0.2</v>
@@ -6718,65 +6944,65 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I45" s="1">
         <v>1</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AC45" s="1">
         <v>1</v>
       </c>
       <c r="AG45" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD45" s="1">
         <v>1</v>
       </c>
       <c r="CB45" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="CG45" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CM45" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="CN45" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="CR45" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I46" s="1">
         <v>1</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AC46" s="1">
         <v>1</v>
       </c>
       <c r="AJ46" s="1" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="AV46" s="1">
         <v>20</v>
@@ -6788,7 +7014,7 @@
         <v>0.1</v>
       </c>
       <c r="CN46" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="CR46" s="1">
         <v>0.2</v>
@@ -6800,21 +7026,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I47" s="1">
         <v>1</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N47" s="1">
         <v>1</v>
@@ -6823,56 +7049,56 @@
         <v>1</v>
       </c>
       <c r="AG47" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD47" s="1">
         <v>1</v>
       </c>
       <c r="CB47" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="CG47" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="49" spans="1:112" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I49" s="1">
         <v>1</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AC49" s="1">
         <v>1</v>
       </c>
       <c r="AG49" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD49" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AC50" s="1">
         <v>2</v>
@@ -6881,78 +7107,78 @@
         <v>1</v>
       </c>
       <c r="AO50" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AR50" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AT50" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AX50" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="AZ50" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD50" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO50" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="CB50" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="CG50" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="CH50" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="CI50" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="CJ50" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="CM50" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="CY50" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="DG50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="AC51" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD51" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO51" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="AZ50" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD50" s="1">
-        <v>1</v>
-      </c>
-      <c r="BO50" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="CB50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="CG50" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="CH50" s="1" t="s">
+      <c r="AR51" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="AT51" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="CI50" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="CJ50" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="CM50" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="CY50" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="DG50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="AC51" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD51" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO51" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="AR51" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="AT51" s="1" t="s">
-        <v>539</v>
-      </c>
       <c r="AX51" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AZ51" s="1">
         <v>1</v>
@@ -6961,80 +7187,80 @@
         <v>1</v>
       </c>
       <c r="CB51" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="CG51" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CH51" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="CI51" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="CJ51" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="CM51" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="CN51" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="CR51" s="1">
         <v>15</v>
       </c>
       <c r="CY51" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="DG51" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I53" s="1">
         <v>1</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AC53" s="1">
         <v>1</v>
       </c>
       <c r="AG53" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD53" s="1">
         <v>1</v>
       </c>
       <c r="CN53" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="CR53" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="54" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AC54" s="1">
         <v>2</v>
@@ -7043,16 +7269,16 @@
         <v>1</v>
       </c>
       <c r="AO54" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AR54" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AT54" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AX54" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AZ54" s="1">
         <v>1</v>
@@ -7061,80 +7287,80 @@
         <v>1</v>
       </c>
       <c r="CB54" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="CG54" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CH54" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="CI54" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="CJ54" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="CY54" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="DG54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I55" s="1">
+        <v>1</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="AC55" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD55" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT55" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="CJ54" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="CY54" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="DG54" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="I55" s="1">
-        <v>1</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="AC55" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD55" s="1">
-        <v>1</v>
-      </c>
-      <c r="AT55" s="1" t="s">
-        <v>546</v>
       </c>
       <c r="BD55" s="1">
         <v>99</v>
       </c>
       <c r="BO55" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="BS55" s="1">
         <v>0.1</v>
       </c>
       <c r="CN55" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="CO55" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="CR55" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="56" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I56" s="1">
         <v>1</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AC56" s="1">
         <v>2</v>
@@ -7143,7 +7369,7 @@
         <v>1</v>
       </c>
       <c r="AT56" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="BD56" s="1">
         <v>99</v>
@@ -7152,27 +7378,27 @@
         <v>0.1</v>
       </c>
       <c r="CN56" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="CO56" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="CR56" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="57" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I57" s="1">
         <v>1</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AC57" s="1">
         <v>2</v>
@@ -7187,10 +7413,10 @@
         <v>1</v>
       </c>
       <c r="BO57" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="BP57" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="BS57" s="1">
         <v>0.1</v>
@@ -7202,30 +7428,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I58" s="1">
         <v>1</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AC58" s="1">
         <v>1</v>
       </c>
       <c r="AG58" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD58" s="1">
         <v>1</v>
       </c>
       <c r="CN58" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="CR58" s="1">
         <v>0.2</v>
@@ -7234,24 +7460,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I59" s="1">
         <v>1</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AC59" s="1">
         <v>1</v>
       </c>
       <c r="AG59" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BD59" s="1">
         <v>1</v>
@@ -7260,7 +7486,7 @@
         <v>1</v>
       </c>
       <c r="CN59" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="CR59" s="1">
         <v>99999</v>
@@ -7273,6 +7499,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -7282,111 +7509,111 @@
   <dimension ref="A1:Q126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.25" style="1" customWidth="1"/>
-    <col min="3" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" customWidth="1"/>
-    <col min="9" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.08203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="22.1640625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="19" customWidth="1" style="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="1"/>
+    <col min="3" max="6" width="9" customWidth="1" style="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="1"/>
+    <col min="8" max="8" width="15" customWidth="1" style="1"/>
+    <col min="9" max="13" width="9" customWidth="1" style="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="1"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="1"/>
+    <col min="18" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7397,379 +7624,380 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
       </c>
       <c r="Q7" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="K9" s="1">
         <v>5</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="K13" s="1">
         <v>5</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q14" s="1" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>592</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>590</v>
       </c>
       <c r="K16" s="1">
         <v>5</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="C27" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="K28" s="1">
         <v>5</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K30" s="1">
         <v>5</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K31" s="1">
         <v>5</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="125">
       <c r="A125" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="126">
       <c r="A126" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7778,36 +8006,36 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="1"/>
+    <col min="3" max="3" width="9" customWidth="1" style="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="1"/>
+    <col min="5" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7815,30 +8043,31 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7847,52 +8076,52 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
-    <col min="5" max="10" width="9" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
+    <col min="2" max="2" width="9" customWidth="1" style="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="1"/>
+    <col min="5" max="10" width="9" customWidth="1" style="1"/>
+    <col min="11" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="I1" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7906,28 +8135,29 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7936,89 +8166,89 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.08203125" style="1" customWidth="1"/>
-    <col min="5" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
+    <col min="2" max="2" width="28" customWidth="1" style="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="1"/>
+    <col min="12" max="12" width="9" customWidth="1" style="1"/>
+    <col min="13" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8026,40 +8256,41 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -8069,50 +8300,50 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" style="1" customWidth="1"/>
-    <col min="7" max="9" width="9" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="1"/>
+    <col min="7" max="9" width="9" customWidth="1" style="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="1"/>
+    <col min="11" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8126,27 +8357,28 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -8155,84 +8387,84 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.9140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="1" customWidth="1"/>
-    <col min="6" max="7" width="15.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.9140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.75" style="1"/>
+    <col min="1" max="1" width="7.5" customWidth="1" style="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1" style="1"/>
+    <col min="3" max="3" width="21.9140625" customWidth="1" style="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1" style="1"/>
+    <col min="5" max="5" width="14" customWidth="1" style="1"/>
+    <col min="6" max="7" width="15.1640625" customWidth="1" style="1"/>
+    <col min="8" max="8" width="12.9140625" customWidth="1" style="1"/>
+    <col min="9" max="9" width="14" customWidth="1" style="1"/>
+    <col min="10" max="16384" width="8.75" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -8253,9 +8485,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>125</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -8264,27 +8496,27 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -8293,27 +8525,27 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -8322,27 +8554,28 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/尊尼获加/莫菲丝.xlsx
+++ b/Excel/尊尼获加/莫菲丝.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\尊尼获加\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FB7E8B-7F61-4AC3-B871-2DB072D4FCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C26DB0-F44E-490F-9007-790A3E0381EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="669">
   <si>
     <t>Id</t>
   </si>
@@ -2312,8 +2312,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2326,6 +2325,19 @@
       <name val="宋体"/>
       <family val="3"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2359,20 +2371,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2681,14 +2690,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:B6"/>
+  <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="1"/>
-    <col min="3" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2696,7 +2705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2704,34 +2713,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -2740,1213 +2732,994 @@
   <dimension ref="A1:BT7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
-    <col min="8" max="8" width="9" customWidth="1" style="2"/>
-    <col min="9" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="9" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6" customWidth="1" style="2"/>
-    <col min="12" max="12" width="5.5" customWidth="1" style="2"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="4" customWidth="1" style="2"/>
-    <col min="15" max="15" width="7.75" customWidth="1" style="2"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="3.83203125" customWidth="1" style="2"/>
-    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="3.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="10.25" customWidth="1" style="2"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1" style="2"/>
-    <col min="23" max="23" width="10.75" customWidth="1" style="2"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1" style="2"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.75" customWidth="1" style="2"/>
-    <col min="27" max="27" width="9" customWidth="1" style="2"/>
-    <col min="28" max="28" width="9" customWidth="1" style="2"/>
-    <col min="29" max="29" width="8" customWidth="1" style="2"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="9" customWidth="1" style="2"/>
-    <col min="32" max="32" width="9" customWidth="1" style="2"/>
-    <col min="33" max="33" width="9.75" customWidth="1" style="2"/>
-    <col min="34" max="34" width="7.83203125" customWidth="1" style="2"/>
-    <col min="35" max="35" width="15.83203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="13.83203125" customWidth="1" style="2"/>
-    <col min="37" max="37" width="34.5" customWidth="1" style="2"/>
-    <col min="38" max="38" width="9.83203125" customWidth="1" style="2"/>
-    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="9" customWidth="1" style="2"/>
-    <col min="41" max="41" width="9" customWidth="1" style="2"/>
-    <col min="42" max="42" width="9" customWidth="1" style="2"/>
-    <col min="43" max="43" width="9" customWidth="1" style="2"/>
-    <col min="44" max="44" width="12.5" customWidth="1" style="2"/>
-    <col min="45" max="45" width="9" customWidth="1" style="2"/>
-    <col min="46" max="46" width="9" customWidth="1" style="2"/>
-    <col min="47" max="47" width="9" customWidth="1" style="2"/>
-    <col min="48" max="48" width="9" customWidth="1" style="2"/>
-    <col min="49" max="49" width="9" customWidth="1" style="2"/>
-    <col min="50" max="50" width="9" customWidth="1" style="2"/>
-    <col min="51" max="51" width="24.33203125" customWidth="1" style="2"/>
-    <col min="52" max="52" width="9" customWidth="1" style="2"/>
-    <col min="53" max="53" width="17.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="7.83203125" customWidth="1" style="2"/>
-    <col min="55" max="55" width="9" customWidth="1" style="2"/>
-    <col min="56" max="56" width="9" customWidth="1" style="2"/>
-    <col min="57" max="57" width="24.25" customWidth="1" style="2"/>
-    <col min="58" max="58" width="13.25" customWidth="1" style="2"/>
-    <col min="59" max="59" width="16.08203125" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8" customWidth="1" style="2"/>
-    <col min="61" max="61" width="9" customWidth="1" style="2"/>
-    <col min="62" max="62" width="9" customWidth="1" style="2"/>
-    <col min="63" max="63" width="27.33203125" customWidth="1" style="2"/>
-    <col min="64" max="64" width="9" customWidth="1" style="2"/>
-    <col min="65" max="65" width="39.58203125" customWidth="1" style="2"/>
-    <col min="66" max="66" width="14" customWidth="1" style="2"/>
-    <col min="67" max="67" width="14.83203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
-    <col min="71" max="71" width="14" customWidth="1" style="2"/>
-    <col min="72" max="72" width="19.1640625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="2" max="3" width="9" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
+    <col min="8" max="10" width="9" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="5.5" customWidth="1"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1"/>
+    <col min="14" max="14" width="4" customWidth="1"/>
+    <col min="15" max="15" width="7.75" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="18" width="3.83203125" customWidth="1"/>
+    <col min="19" max="20" width="3.58203125" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1"/>
+    <col min="23" max="23" width="10.75" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1"/>
+    <col min="26" max="26" width="10.75" customWidth="1"/>
+    <col min="27" max="28" width="9" customWidth="1"/>
+    <col min="29" max="29" width="8" customWidth="1"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1"/>
+    <col min="31" max="32" width="9" customWidth="1"/>
+    <col min="33" max="33" width="9.75" customWidth="1"/>
+    <col min="34" max="34" width="7.83203125" customWidth="1"/>
+    <col min="35" max="35" width="15.83203125" customWidth="1"/>
+    <col min="36" max="36" width="13.83203125" customWidth="1"/>
+    <col min="37" max="37" width="34.5" customWidth="1"/>
+    <col min="38" max="39" width="9.83203125" customWidth="1"/>
+    <col min="40" max="43" width="9" customWidth="1"/>
+    <col min="44" max="44" width="12.5" customWidth="1"/>
+    <col min="45" max="50" width="9" customWidth="1"/>
+    <col min="51" max="51" width="24.33203125" customWidth="1"/>
+    <col min="52" max="52" width="9" customWidth="1"/>
+    <col min="53" max="53" width="17.75" customWidth="1"/>
+    <col min="54" max="54" width="7.83203125" customWidth="1"/>
+    <col min="55" max="56" width="9" customWidth="1"/>
+    <col min="57" max="57" width="24.25" customWidth="1"/>
+    <col min="58" max="58" width="13.25" customWidth="1"/>
+    <col min="59" max="59" width="16.08203125" customWidth="1"/>
+    <col min="60" max="60" width="8" customWidth="1"/>
+    <col min="61" max="62" width="9" customWidth="1"/>
+    <col min="63" max="63" width="27.33203125" customWidth="1"/>
+    <col min="64" max="64" width="9" customWidth="1"/>
+    <col min="65" max="65" width="39.58203125" customWidth="1"/>
+    <col min="66" max="66" width="14" customWidth="1"/>
+    <col min="67" max="67" width="14.83203125" customWidth="1"/>
+    <col min="68" max="71" width="14" customWidth="1"/>
+    <col min="72" max="72" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2" t="s">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2" t="s">
+      <c r="U1" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2" t="s">
+      <c r="X1" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" t="s">
         <v>24</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" t="s">
         <v>25</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>26</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>27</v>
       </c>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" t="s">
         <v>28</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" t="s">
         <v>29</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" t="s">
         <v>30</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" t="s">
         <v>31</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" t="s">
         <v>32</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" t="s">
         <v>33</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" t="s">
         <v>34</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" t="s">
         <v>35</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" t="s">
         <v>36</v>
       </c>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" t="s">
         <v>37</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" t="s">
         <v>38</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" t="s">
         <v>39</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" t="s">
         <v>40</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" t="s">
         <v>41</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" t="s">
         <v>42</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>43</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>44</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" t="s">
         <v>45</v>
       </c>
-      <c r="BC1" s="2"/>
-      <c r="BD1" s="2"/>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" t="s">
         <v>46</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" t="s">
         <v>47</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" t="s">
         <v>48</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BH1" t="s">
         <v>49</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BI1" t="s">
         <v>50</v>
       </c>
-      <c r="BJ1" s="2"/>
-      <c r="BK1" s="2"/>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>57</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>58</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>59</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>62</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>63</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" t="s">
         <v>65</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" t="s">
         <v>66</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" t="s">
         <v>67</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" t="s">
         <v>68</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" t="s">
         <v>69</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" t="s">
         <v>70</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" t="s">
         <v>71</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" t="s">
         <v>72</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" t="s">
         <v>73</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" t="s">
         <v>74</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" t="s">
         <v>75</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" t="s">
         <v>76</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" t="s">
         <v>77</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AE2" t="s">
         <v>78</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" t="s">
         <v>79</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AG2" t="s">
         <v>80</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AH2" t="s">
         <v>81</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AI2" t="s">
         <v>82</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AJ2" t="s">
         <v>83</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AK2" t="s">
         <v>84</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AL2" t="s">
         <v>85</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AM2" t="s">
         <v>86</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AN2" t="s">
         <v>87</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AO2" t="s">
         <v>88</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AP2" t="s">
         <v>89</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AQ2" t="s">
         <v>90</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AR2" t="s">
         <v>91</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AS2" t="s">
         <v>92</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AT2" t="s">
         <v>93</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AU2" t="s">
         <v>94</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AV2" t="s">
         <v>95</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AW2" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AX2" t="s">
         <v>97</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AY2" t="s">
         <v>98</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AZ2" t="s">
         <v>99</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="BA2" t="s">
         <v>100</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BB2" t="s">
         <v>101</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BC2" t="s">
         <v>102</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BD2" t="s">
         <v>103</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BE2" t="s">
         <v>104</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BF2" t="s">
         <v>105</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BG2" t="s">
         <v>106</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BH2" t="s">
         <v>107</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BI2" t="s">
         <v>108</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BJ2" t="s">
         <v>109</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BK2" t="s">
         <v>110</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BL2" t="s">
         <v>111</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BM2" t="s">
         <v>112</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BN2" t="s">
         <v>113</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BO2" t="s">
         <v>114</v>
       </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BP2" t="s">
         <v>115</v>
       </c>
-      <c r="BQ2" s="2" t="s">
+      <c r="BQ2" t="s">
         <v>116</v>
       </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BR2" t="s">
         <v>117</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BS2" t="s">
         <v>118</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BT2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="3" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>120</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
         <v>122</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>122</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>122</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>122</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" t="s">
         <v>122</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" t="s">
         <v>122</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" t="s">
         <v>122</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" t="s">
         <v>122</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>122</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" t="s">
         <v>122</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" t="s">
         <v>122</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" t="s">
         <v>122</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U3" t="s">
         <v>121</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" t="s">
         <v>122</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" t="s">
         <v>122</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X3" t="s">
         <v>121</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" t="s">
         <v>121</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" t="s">
         <v>121</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" t="s">
         <v>122</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" t="s">
         <v>121</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" t="s">
         <v>122</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AD3" t="s">
         <v>120</v>
       </c>
-      <c r="AE3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AE3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="s">
         <v>122</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AG3" t="s">
         <v>122</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AH3" t="s">
         <v>122</v>
       </c>
-      <c r="AI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" s="2" t="s">
+      <c r="AI3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" t="s">
         <v>123</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="AL3" t="s">
         <v>123</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AM3" t="s">
         <v>122</v>
       </c>
-      <c r="AN3" s="2" t="s">
+      <c r="AN3" t="s">
         <v>121</v>
       </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AO3" t="s">
         <v>124</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AP3" t="s">
         <v>122</v>
       </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="AQ3" t="s">
         <v>121</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AR3" t="s">
         <v>120</v>
       </c>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2" t="s">
+      <c r="AT3" t="s">
         <v>121</v>
       </c>
-      <c r="AU3" s="2" t="s">
+      <c r="AU3" t="s">
         <v>120</v>
       </c>
-      <c r="AV3" s="2" t="s">
+      <c r="AV3" t="s">
         <v>122</v>
       </c>
-      <c r="AW3" s="2" t="s">
+      <c r="AW3" t="s">
         <v>125</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" t="s">
         <v>121</v>
       </c>
-      <c r="AY3" s="2" t="s">
+      <c r="AY3" t="s">
         <v>126</v>
       </c>
-      <c r="AZ3" s="2" t="s">
+      <c r="AZ3" t="s">
         <v>120</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BA3" t="s">
         <v>120</v>
       </c>
-      <c r="BB3" s="2" t="s">
+      <c r="BB3" t="s">
         <v>121</v>
       </c>
-      <c r="BC3" s="2" t="s">
+      <c r="BC3" t="s">
         <v>127</v>
       </c>
-      <c r="BD3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" s="2" t="s">
+      <c r="BD3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" t="s">
         <v>128</v>
       </c>
-      <c r="BI3" s="2" t="s">
+      <c r="BI3" t="s">
         <v>122</v>
       </c>
-      <c r="BJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BJ3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK3" t="s">
         <v>124</v>
       </c>
-      <c r="BL3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" s="2" t="s">
+      <c r="BL3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" t="s">
         <v>129</v>
       </c>
-      <c r="BN3" s="2" t="s">
+      <c r="BN3" t="s">
         <v>124</v>
       </c>
-      <c r="BO3" s="2" t="s">
+      <c r="BO3" t="s">
         <v>124</v>
       </c>
-      <c r="BP3" s="2" t="s">
+      <c r="BP3" t="s">
         <v>124</v>
       </c>
-      <c r="BQ3" s="2" t="s">
+      <c r="BQ3" t="s">
         <v>124</v>
       </c>
-      <c r="BR3" s="2" t="s">
+      <c r="BR3" t="s">
         <v>124</v>
       </c>
-      <c r="BS3" s="2" t="s">
+      <c r="BS3" t="s">
         <v>124</v>
       </c>
-      <c r="BT3" s="2" t="s">
+      <c r="BT3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
-      <c r="AR4" s="2"/>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2"/>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2"/>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2"/>
-      <c r="BA4" s="2"/>
-      <c r="BB4" s="2"/>
-      <c r="BC4" s="2"/>
-      <c r="BD4" s="2"/>
-      <c r="BE4" s="2"/>
-      <c r="BF4" s="2"/>
-      <c r="BG4" s="2"/>
-      <c r="BH4" s="2"/>
-      <c r="BI4" s="2"/>
-      <c r="BJ4" s="2"/>
-      <c r="BK4" s="2"/>
-      <c r="BL4" s="2"/>
-      <c r="BM4" s="2"/>
-      <c r="BN4" s="2"/>
-      <c r="BO4" s="2"/>
-      <c r="BP4" s="2"/>
-      <c r="BQ4" s="2"/>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2"/>
-      <c r="BT4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>131</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
         <v>90</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5">
         <v>1950</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2">
+      <c r="M5">
         <v>605</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5">
         <v>90</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5">
         <v>125</v>
       </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2">
+      <c r="Q5">
         <v>25</v>
       </c>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2">
+      <c r="S5">
         <v>13</v>
       </c>
-      <c r="T5" s="2">
+      <c r="T5">
         <v>-2</v>
       </c>
-      <c r="U5" s="2">
+      <c r="U5">
         <v>0.5</v>
       </c>
-      <c r="V5" s="2">
+      <c r="V5">
         <v>70</v>
       </c>
-      <c r="W5" s="2">
+      <c r="W5">
         <v>-4</v>
       </c>
-      <c r="X5" s="2">
+      <c r="X5">
         <v>7</v>
       </c>
-      <c r="Y5" s="2">
+      <c r="Y5">
         <v>0.05</v>
       </c>
-      <c r="Z5" s="2">
+      <c r="Z5">
         <v>1.6</v>
       </c>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="2"/>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
-      <c r="AI5" s="2" t="s">
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="s">
         <v>4</v>
       </c>
-      <c r="AJ5" s="2" t="s">
+      <c r="AJ5" t="s">
         <v>132</v>
       </c>
-      <c r="AK5" s="2" t="s">
+      <c r="AK5" t="s">
         <v>133</v>
       </c>
-      <c r="AL5" s="2" t="s">
+      <c r="AL5" t="s">
         <v>134</v>
       </c>
-      <c r="AM5" s="2"/>
-      <c r="AN5" s="2"/>
-      <c r="AO5" s="2" t="s">
+      <c r="AO5" t="s">
         <v>135</v>
       </c>
-      <c r="AP5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AQ5" s="2">
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="AQ5">
         <v>0.5</v>
       </c>
-      <c r="AR5" s="2"/>
-      <c r="AS5" s="2"/>
-      <c r="AT5" s="2"/>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2">
+      <c r="AX5">
         <v>0.25</v>
       </c>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2"/>
-      <c r="BA5" s="2"/>
-      <c r="BB5" s="2"/>
-      <c r="BC5" s="2" t="s">
+      <c r="BC5" t="s">
         <v>136</v>
       </c>
-      <c r="BD5" s="2" t="s">
+      <c r="BD5" t="s">
         <v>137</v>
       </c>
-      <c r="BE5" s="2" t="s">
+      <c r="BE5" t="s">
         <v>138</v>
       </c>
-      <c r="BF5" s="2" t="s">
+      <c r="BF5" t="s">
         <v>139</v>
       </c>
-      <c r="BG5" s="2" t="s">
+      <c r="BG5" t="s">
         <v>131</v>
       </c>
-      <c r="BH5" s="2" t="s">
+      <c r="BH5" t="s">
         <v>140</v>
       </c>
-      <c r="BI5" s="2">
+      <c r="BI5">
         <v>6</v>
       </c>
-      <c r="BJ5" s="2" t="s">
+      <c r="BJ5" t="s">
         <v>141</v>
       </c>
-      <c r="BK5" s="2" t="s">
+      <c r="BK5" t="s">
         <v>142</v>
       </c>
-      <c r="BL5" s="2" t="s">
+      <c r="BL5" t="s">
         <v>143</v>
       </c>
-      <c r="BM5" s="2" t="s">
+      <c r="BM5" t="s">
         <v>144</v>
       </c>
-      <c r="BN5" s="2" t="s">
+      <c r="BN5" t="s">
         <v>145</v>
       </c>
-      <c r="BO5" s="2" t="s">
+      <c r="BO5" t="s">
         <v>146</v>
       </c>
-      <c r="BP5" s="2"/>
-      <c r="BQ5" s="2" t="s">
+      <c r="BQ5" t="s">
         <v>147</v>
       </c>
-      <c r="BR5" s="2" t="s">
+      <c r="BR5" t="s">
         <v>147</v>
       </c>
-      <c r="BS5" s="2"/>
-      <c r="BT5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="BT5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>148</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
         <v>90</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6">
         <v>1500</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2">
+      <c r="M6">
         <v>520</v>
       </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2">
+      <c r="O6">
         <v>115</v>
       </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2">
+      <c r="Q6">
         <v>50</v>
       </c>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2">
+      <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2">
+      <c r="U6">
         <v>0.5</v>
       </c>
-      <c r="V6" s="2">
+      <c r="V6">
         <v>25</v>
       </c>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2">
+      <c r="Y6">
         <v>0.05</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z6">
         <v>1.2</v>
       </c>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2">
+      <c r="AC6">
         <v>0</v>
       </c>
-      <c r="AD6" s="2"/>
-      <c r="AE6" s="2"/>
-      <c r="AF6" s="2"/>
-      <c r="AG6" s="2"/>
-      <c r="AH6" s="2"/>
-      <c r="AI6" s="2" t="s">
+      <c r="AI6" t="s">
         <v>5</v>
       </c>
-      <c r="AJ6" s="2" t="s">
+      <c r="AJ6" t="s">
         <v>132</v>
       </c>
-      <c r="AK6" s="2" t="s">
+      <c r="AK6" t="s">
         <v>149</v>
       </c>
-      <c r="AL6" s="2" t="s">
+      <c r="AL6" t="s">
         <v>150</v>
       </c>
-      <c r="AM6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2" t="s">
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="s">
         <v>135</v>
       </c>
-      <c r="AP6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AQ6" s="2">
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
         <v>0.5</v>
       </c>
-      <c r="AR6" s="2"/>
-      <c r="AS6" s="2"/>
-      <c r="AT6" s="2"/>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2">
+      <c r="AX6">
         <v>0.25</v>
       </c>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2"/>
-      <c r="BA6" s="2"/>
-      <c r="BB6" s="2"/>
-      <c r="BC6" s="2" t="s">
+      <c r="BC6" t="s">
         <v>136</v>
       </c>
-      <c r="BD6" s="2" t="s">
+      <c r="BD6" t="s">
         <v>151</v>
       </c>
-      <c r="BE6" s="2" t="s">
+      <c r="BE6" t="s">
         <v>152</v>
       </c>
-      <c r="BF6" s="2"/>
-      <c r="BG6" s="2"/>
-      <c r="BH6" s="2"/>
-      <c r="BI6" s="2">
+      <c r="BI6">
         <v>6</v>
       </c>
-      <c r="BJ6" s="2" t="s">
+      <c r="BJ6" t="s">
         <v>141</v>
       </c>
-      <c r="BK6" s="2" t="s">
+      <c r="BK6" t="s">
         <v>153</v>
       </c>
-      <c r="BL6" s="2"/>
-      <c r="BM6" s="2"/>
-      <c r="BN6" s="2" t="s">
+      <c r="BN6" t="s">
         <v>154</v>
       </c>
-      <c r="BO6" s="2" t="s">
+      <c r="BO6" t="s">
         <v>155</v>
       </c>
-      <c r="BP6" s="2"/>
-      <c r="BQ6" s="2" t="s">
+      <c r="BQ6" t="s">
         <v>156</v>
       </c>
-      <c r="BR6" s="2" t="s">
+      <c r="BR6" t="s">
         <v>156</v>
       </c>
-      <c r="BS6" s="2"/>
-      <c r="BT6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="BT6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>157</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>157</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2">
-        <v>2</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>90</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7">
         <v>100</v>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2">
+      <c r="M7">
         <v>175</v>
       </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2">
+      <c r="O7">
         <v>0</v>
       </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2">
+      <c r="Q7">
         <v>0</v>
       </c>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2">
+      <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2">
+      <c r="U7">
         <v>0</v>
       </c>
-      <c r="V7" s="2">
+      <c r="V7">
         <v>10</v>
       </c>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2">
+      <c r="Y7">
         <v>0.05</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="Z7">
         <v>0.4</v>
       </c>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2">
+      <c r="AC7">
         <v>0</v>
       </c>
-      <c r="AD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="2"/>
-      <c r="AF7" s="2"/>
-      <c r="AG7" s="2"/>
-      <c r="AH7" s="2"/>
-      <c r="AI7" s="2" t="s">
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="s">
         <v>6</v>
       </c>
-      <c r="AJ7" s="2" t="s">
+      <c r="AJ7" t="s">
         <v>132</v>
       </c>
-      <c r="AK7" s="2" t="s">
+      <c r="AK7" t="s">
         <v>158</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AL7" t="s">
         <v>159</v>
       </c>
-      <c r="AM7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AN7" s="2"/>
-      <c r="AO7" s="2" t="s">
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="s">
         <v>160</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AP7">
         <v>0</v>
       </c>
-      <c r="AQ7" s="2">
+      <c r="AQ7">
         <v>0</v>
       </c>
-      <c r="AR7" s="2"/>
-      <c r="AS7" s="2"/>
-      <c r="AT7" s="2"/>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2">
+      <c r="AX7">
         <v>0</v>
       </c>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2"/>
-      <c r="BA7" s="2"/>
-      <c r="BB7" s="2"/>
-      <c r="BC7" s="2" t="s">
+      <c r="BC7" t="s">
         <v>136</v>
       </c>
-      <c r="BD7" s="2" t="s">
+      <c r="BD7" t="s">
         <v>151</v>
       </c>
-      <c r="BE7" s="2"/>
-      <c r="BF7" s="2" t="s">
+      <c r="BF7" t="s">
         <v>161</v>
       </c>
-      <c r="BG7" s="2" t="s">
+      <c r="BG7" t="s">
         <v>157</v>
       </c>
-      <c r="BH7" s="2" t="s">
+      <c r="BH7" t="s">
         <v>140</v>
       </c>
-      <c r="BI7" s="2">
+      <c r="BI7">
         <v>6</v>
       </c>
-      <c r="BJ7" s="2" t="s">
+      <c r="BJ7" t="s">
         <v>162</v>
       </c>
-      <c r="BK7" s="2" t="s">
+      <c r="BK7" t="s">
         <v>163</v>
       </c>
-      <c r="BL7" s="2"/>
-      <c r="BM7" s="2"/>
-      <c r="BN7" s="2" t="s">
+      <c r="BN7" t="s">
         <v>154</v>
       </c>
-      <c r="BO7" s="2" t="s">
+      <c r="BO7" t="s">
         <v>155</v>
       </c>
-      <c r="BP7" s="2"/>
-      <c r="BQ7" s="2" t="s">
+      <c r="BQ7" t="s">
         <v>156</v>
       </c>
-      <c r="BR7" s="2" t="s">
+      <c r="BR7" t="s">
         <v>156</v>
       </c>
-      <c r="BS7" s="2"/>
-      <c r="BT7" s="2">
+      <c r="BT7">
         <v>1</v>
       </c>
     </row>
@@ -3954,7 +3727,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3964,99 +3736,100 @@
   <dimension ref="A1:DI59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="1"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="1"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="1"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="1"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1" style="1"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1" style="1"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="1"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="1"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="1"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="1"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="1"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="1"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="1"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="1"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="1"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="1"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="1"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="1"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="1"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="1"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="1"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="1"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="1"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="1"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="1"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="1"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="1"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="1"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="1"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="1"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="1"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="1"/>
-    <col min="40" max="40" width="15" customWidth="1" style="1"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="1"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="1"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="1"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="1"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="1"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="1"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="1"/>
-    <col min="51" max="51" width="9" customWidth="1" style="1"/>
-    <col min="52" max="52" width="7" customWidth="1" style="1"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="1"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="1"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="1"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="1"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="1"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="1"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="1"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="1"/>
-    <col min="61" max="66" width="8.33203125" customWidth="1" style="1"/>
-    <col min="67" max="67" width="19.25" customWidth="1" style="1"/>
-    <col min="68" max="68" width="22.33203125" customWidth="1" style="1"/>
-    <col min="69" max="70" width="11.25" customWidth="1" style="1"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="1"/>
-    <col min="72" max="73" width="8" customWidth="1" style="1"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="1"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="1"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="1"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="1"/>
-    <col min="80" max="80" width="35" customWidth="1" style="1"/>
-    <col min="81" max="81" width="20.6640625" customWidth="1" style="1"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="1"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="1"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="1"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="1"/>
-    <col min="86" max="86" width="9" customWidth="1" style="1"/>
-    <col min="87" max="87" width="16" customWidth="1" style="1"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="1"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="1"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="1"/>
-    <col min="92" max="92" width="25.9140625" customWidth="1" style="1"/>
-    <col min="93" max="93" width="9.5" customWidth="1" style="1"/>
-    <col min="94" max="98" width="9" customWidth="1" style="1"/>
-    <col min="99" max="99" width="14" customWidth="1" style="1"/>
-    <col min="100" max="100" width="8" customWidth="1" style="1"/>
-    <col min="101" max="101" width="9" customWidth="1" style="1"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="1"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="1"/>
-    <col min="104" max="104" width="9.5" customWidth="1" style="1"/>
-    <col min="105" max="106" width="9" customWidth="1" style="1"/>
-    <col min="107" max="108" width="9.5" customWidth="1" style="1"/>
-    <col min="109" max="109" width="9" customWidth="1" style="1"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="1"/>
-    <col min="111" max="111" width="9" customWidth="1" style="1"/>
-    <col min="112" max="113" width="9.5" customWidth="1" style="1"/>
-    <col min="114" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="21.08203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" style="1" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="21.5" style="1" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="17.75" style="1" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="18.5" style="1" customWidth="1"/>
+    <col min="25" max="25" width="16.58203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="8.33203125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" style="1" customWidth="1"/>
+    <col min="29" max="30" width="8.58203125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="13.4140625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="13.75" style="1" customWidth="1"/>
+    <col min="33" max="33" width="14.58203125" style="1" customWidth="1"/>
+    <col min="34" max="34" width="17.4140625" style="1" customWidth="1"/>
+    <col min="35" max="35" width="8.58203125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="12.5" style="1" customWidth="1"/>
+    <col min="37" max="37" width="8.58203125" style="1" customWidth="1"/>
+    <col min="38" max="39" width="8.33203125" style="1" customWidth="1"/>
+    <col min="40" max="40" width="15" style="1" customWidth="1"/>
+    <col min="41" max="41" width="13.25" style="1" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" style="1" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" style="1" customWidth="1"/>
+    <col min="47" max="47" width="12.25" style="1" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" style="1" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" style="1" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" style="1" customWidth="1"/>
+    <col min="51" max="51" width="9" style="1" customWidth="1"/>
+    <col min="52" max="52" width="7" style="1" customWidth="1"/>
+    <col min="53" max="53" width="11.75" style="1" customWidth="1"/>
+    <col min="54" max="54" width="19.75" style="1" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" style="1" customWidth="1"/>
+    <col min="56" max="56" width="8.5" style="1" customWidth="1"/>
+    <col min="57" max="57" width="13.5" style="1" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" style="1" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" style="1" customWidth="1"/>
+    <col min="60" max="60" width="8.25" style="1" customWidth="1"/>
+    <col min="61" max="66" width="8.33203125" style="1" customWidth="1"/>
+    <col min="67" max="67" width="19.25" style="1" customWidth="1"/>
+    <col min="68" max="68" width="22.33203125" style="1" customWidth="1"/>
+    <col min="69" max="70" width="11.25" style="1" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" style="1" customWidth="1"/>
+    <col min="72" max="73" width="8" style="1" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" style="1" customWidth="1"/>
+    <col min="75" max="76" width="8.5" style="1" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" style="1" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" style="1" customWidth="1"/>
+    <col min="80" max="80" width="35" style="1" customWidth="1"/>
+    <col min="81" max="81" width="20.6640625" style="1" customWidth="1"/>
+    <col min="82" max="82" width="15.75" style="1" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" style="1" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" style="1" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" style="1" customWidth="1"/>
+    <col min="86" max="86" width="9" style="1" customWidth="1"/>
+    <col min="87" max="87" width="16" style="1" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" style="1" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" style="1" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" style="1" customWidth="1"/>
+    <col min="92" max="92" width="25.9140625" style="1" customWidth="1"/>
+    <col min="93" max="93" width="9.5" style="1" customWidth="1"/>
+    <col min="94" max="98" width="9" style="1" customWidth="1"/>
+    <col min="99" max="99" width="14" style="1" customWidth="1"/>
+    <col min="100" max="100" width="8" style="1" customWidth="1"/>
+    <col min="101" max="101" width="9" style="1" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" style="1" customWidth="1"/>
+    <col min="103" max="103" width="13.75" style="1" customWidth="1"/>
+    <col min="104" max="104" width="9.5" style="1" customWidth="1"/>
+    <col min="105" max="106" width="9" style="1" customWidth="1"/>
+    <col min="107" max="108" width="9.5" style="1" customWidth="1"/>
+    <col min="109" max="109" width="9" style="1" customWidth="1"/>
+    <col min="110" max="110" width="15.5" style="1" customWidth="1"/>
+    <col min="111" max="111" width="9" style="1" customWidth="1"/>
+    <col min="112" max="113" width="9.5" style="1" customWidth="1"/>
+    <col min="114" max="114" width="9" style="1" customWidth="1"/>
+    <col min="115" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>164</v>
       </c>
@@ -4388,7 +4161,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4726,7 +4499,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -5064,7 +4837,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>394</v>
       </c>
@@ -5135,7 +4908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>410</v>
       </c>
@@ -5203,7 +4976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>412</v>
       </c>
@@ -5271,7 +5044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>415</v>
       </c>
@@ -5309,7 +5082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>417</v>
       </c>
@@ -5350,7 +5123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>420</v>
       </c>
@@ -5394,7 +5167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>424</v>
       </c>
@@ -5441,7 +5214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>427</v>
       </c>
@@ -5482,7 +5255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>429</v>
       </c>
@@ -5523,7 +5296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>434</v>
       </c>
@@ -5561,7 +5334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>436</v>
       </c>
@@ -5599,7 +5372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>439</v>
       </c>
@@ -5646,7 +5419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>440</v>
       </c>
@@ -5690,7 +5463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>447</v>
       </c>
@@ -5734,7 +5507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>450</v>
       </c>
@@ -5766,7 +5539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>454</v>
       </c>
@@ -5804,7 +5577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>456</v>
       </c>
@@ -5839,7 +5612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>457</v>
       </c>
@@ -5865,7 +5638,7 @@
         <v>448</v>
       </c>
       <c r="CR22" s="1">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="DH22" s="1">
         <v>1</v>
@@ -5874,7 +5647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>442</v>
       </c>
@@ -5915,7 +5688,7 @@
         <v>99999</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>460</v>
       </c>
@@ -5965,7 +5738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>462</v>
       </c>
@@ -5991,7 +5764,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>461</v>
       </c>
@@ -6044,7 +5817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>470</v>
       </c>
@@ -6115,7 +5888,7 @@
         <v>99999</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>477</v>
       </c>
@@ -6177,7 +5950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>476</v>
       </c>
@@ -6218,7 +5991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>482</v>
       </c>
@@ -6289,7 +6062,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>490</v>
       </c>
@@ -6321,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="BJ31" s="1">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="BK31" s="1">
         <v>1</v>
@@ -6360,7 +6133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>494</v>
       </c>
@@ -6401,7 +6174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>497</v>
       </c>
@@ -6445,7 +6218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>500</v>
       </c>
@@ -6510,7 +6283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>503</v>
       </c>
@@ -6539,7 +6312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>504</v>
       </c>
@@ -6583,7 +6356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>506</v>
       </c>
@@ -6630,7 +6403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>508</v>
       </c>
@@ -6662,7 +6435,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>512</v>
       </c>
@@ -6697,7 +6470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>514</v>
       </c>
@@ -6738,7 +6511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>516</v>
       </c>
@@ -6839,7 +6612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>525</v>
       </c>
@@ -6874,7 +6647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>527</v>
       </c>
@@ -6906,7 +6679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>529</v>
       </c>
@@ -6944,7 +6717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>531</v>
       </c>
@@ -6985,7 +6758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>533</v>
       </c>
@@ -7026,7 +6799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>535</v>
       </c>
@@ -7061,7 +6834,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>150</v>
       </c>
@@ -7093,7 +6866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>540</v>
       </c>
@@ -7152,7 +6925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>542</v>
       </c>
@@ -7217,7 +6990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>159</v>
       </c>
@@ -7255,7 +7028,7 @@
         <v>99999</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>547</v>
       </c>
@@ -7308,7 +7081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>552</v>
       </c>
@@ -7349,7 +7122,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>553</v>
       </c>
@@ -7387,7 +7160,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>557</v>
       </c>
@@ -7428,7 +7201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>559</v>
       </c>
@@ -7460,7 +7233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>558</v>
       </c>
@@ -7499,7 +7272,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -7509,20 +7281,21 @@
   <dimension ref="A1:Q126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1" style="1"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="1"/>
-    <col min="3" max="6" width="9" customWidth="1" style="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="1"/>
-    <col min="8" max="8" width="15" customWidth="1" style="1"/>
-    <col min="9" max="13" width="9" customWidth="1" style="1"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="1"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1" style="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="1"/>
-    <col min="18" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="19" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.25" style="1" customWidth="1"/>
+    <col min="3" max="6" width="9" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" customWidth="1"/>
+    <col min="9" max="13" width="9" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16.08203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5" style="1" customWidth="1"/>
+    <col min="16" max="16" width="22.1640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7563,7 +7336,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -7613,7 +7386,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7663,7 +7436,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>416</v>
       </c>
@@ -7671,7 +7444,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>397</v>
       </c>
@@ -7679,7 +7452,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>422</v>
       </c>
@@ -7696,7 +7469,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>449</v>
       </c>
@@ -7704,7 +7477,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>554</v>
       </c>
@@ -7724,7 +7497,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>429</v>
       </c>
@@ -7732,7 +7505,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>479</v>
       </c>
@@ -7743,7 +7516,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>481</v>
       </c>
@@ -7751,7 +7524,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>396</v>
       </c>
@@ -7768,7 +7541,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>489</v>
       </c>
@@ -7779,7 +7552,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>496</v>
       </c>
@@ -7787,7 +7560,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>515</v>
       </c>
@@ -7804,7 +7577,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>428</v>
       </c>
@@ -7818,7 +7591,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>599</v>
       </c>
@@ -7826,7 +7599,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>601</v>
       </c>
@@ -7834,7 +7607,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>440</v>
       </c>
@@ -7842,7 +7615,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>444</v>
       </c>
@@ -7850,7 +7623,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>446</v>
       </c>
@@ -7858,7 +7631,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>464</v>
       </c>
@@ -7866,7 +7639,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>469</v>
       </c>
@@ -7874,7 +7647,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>495</v>
       </c>
@@ -7882,7 +7655,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>418</v>
       </c>
@@ -7890,7 +7663,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>438</v>
       </c>
@@ -7901,7 +7674,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>431</v>
       </c>
@@ -7918,7 +7691,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>606</v>
       </c>
@@ -7929,7 +7702,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>529</v>
       </c>
@@ -7943,7 +7716,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>459</v>
       </c>
@@ -7957,7 +7730,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>448</v>
       </c>
@@ -7965,7 +7738,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>534</v>
       </c>
@@ -7973,22 +7746,22 @@
         <v>583</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>552</v>
       </c>
@@ -7997,7 +7770,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -8006,14 +7778,15 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="1"/>
-    <col min="3" max="3" width="9" customWidth="1" style="1"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="1"/>
-    <col min="5" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8021,7 +7794,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -8035,7 +7808,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8049,7 +7822,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>406</v>
       </c>
@@ -8067,7 +7840,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -8076,20 +7848,20 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
-    <col min="2" max="2" width="9" customWidth="1" style="1"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="1"/>
-    <col min="5" max="10" width="9" customWidth="1" style="1"/>
-    <col min="11" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="11" width="9" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -8121,7 +7893,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8157,7 +7929,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -8166,16 +7937,16 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
-    <col min="2" max="2" width="28" customWidth="1" style="1"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="1"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="1"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="1"/>
-    <col min="12" max="12" width="9" customWidth="1" style="1"/>
-    <col min="13" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.08203125" style="1" customWidth="1"/>
+    <col min="5" max="10" width="11.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" style="1" customWidth="1"/>
+    <col min="12" max="13" width="9" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8210,7 +7981,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -8248,7 +8019,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8290,7 +8061,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -8300,18 +8070,19 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="1"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="1"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="1"/>
-    <col min="7" max="9" width="9" customWidth="1" style="1"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="1"/>
-    <col min="11" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="19.08203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" style="1" customWidth="1"/>
+    <col min="7" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -8343,7 +8114,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8378,7 +8149,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -8387,18 +8157,19 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" customWidth="1" style="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1" style="1"/>
-    <col min="3" max="3" width="21.9140625" customWidth="1" style="1"/>
-    <col min="4" max="4" width="16.25" customWidth="1" style="1"/>
-    <col min="5" max="5" width="14" customWidth="1" style="1"/>
-    <col min="6" max="7" width="15.1640625" customWidth="1" style="1"/>
-    <col min="8" max="8" width="12.9140625" customWidth="1" style="1"/>
-    <col min="9" max="9" width="14" customWidth="1" style="1"/>
-    <col min="10" max="16384" width="8.75" customWidth="1" style="1"/>
+    <col min="1" max="1" width="7.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.9140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="1" customWidth="1"/>
+    <col min="6" max="7" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.9140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8427,7 +8198,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -8456,7 +8227,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8485,7 +8256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -8514,7 +8285,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -8543,7 +8314,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -8575,7 +8346,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/尊尼获加/莫菲丝.xlsx
+++ b/Excel/尊尼获加/莫菲丝.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\尊尼获加\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C26DB0-F44E-490F-9007-790A3E0381EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B538B12-DEBA-4C4C-9254-2B68583BA7BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -47,6 +47,30 @@
   </authors>
   <commentList>
     <comment ref="AK1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>PC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0:干员 1:敌人 2:仅技能条 3:技能+血条</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AM1" authorId="0" shapeId="0" xr:uid="{12E1295C-2DE1-4AD2-8005-6F2FD31270A6}">
       <text>
         <r>
           <rPr>
@@ -299,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="675">
   <si>
     <t>Id</t>
   </si>
@@ -394,9 +418,6 @@
     <t>可选技能</t>
   </si>
   <si>
-    <t>血条类型</t>
-  </si>
-  <si>
     <t>高度</t>
   </si>
   <si>
@@ -2306,13 +2327,41 @@
   </si>
   <si>
     <t>/Spine/卡尔顿/enemy_10106_mjcbat.skel.bytes</t>
+  </si>
+  <si>
+    <t>血条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技力条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpBarType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:蓝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:绿</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:橙</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2338,6 +2387,21 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2371,11 +2435,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2729,997 +2796,1013 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BT7"/>
+  <dimension ref="A1:BU7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
-    <col min="2" max="3" width="9" customWidth="1"/>
-    <col min="4" max="5" width="8.58203125" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1"/>
-    <col min="7" max="7" width="8.25" customWidth="1"/>
-    <col min="8" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="5.5" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1"/>
-    <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="7.75" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" customWidth="1"/>
-    <col min="21" max="21" width="10.25" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1"/>
-    <col min="23" max="23" width="10.75" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1"/>
-    <col min="26" max="26" width="10.75" customWidth="1"/>
-    <col min="27" max="28" width="9" customWidth="1"/>
-    <col min="29" max="29" width="8" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1"/>
-    <col min="31" max="32" width="9" customWidth="1"/>
-    <col min="33" max="33" width="9.75" customWidth="1"/>
-    <col min="34" max="34" width="7.83203125" customWidth="1"/>
-    <col min="35" max="35" width="15.83203125" customWidth="1"/>
-    <col min="36" max="36" width="13.83203125" customWidth="1"/>
-    <col min="37" max="37" width="34.5" customWidth="1"/>
-    <col min="38" max="39" width="9.83203125" customWidth="1"/>
-    <col min="40" max="43" width="9" customWidth="1"/>
-    <col min="44" max="44" width="12.5" customWidth="1"/>
-    <col min="45" max="50" width="9" customWidth="1"/>
-    <col min="51" max="51" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="9" customWidth="1"/>
-    <col min="53" max="53" width="17.75" customWidth="1"/>
-    <col min="54" max="54" width="7.83203125" customWidth="1"/>
-    <col min="55" max="56" width="9" customWidth="1"/>
-    <col min="57" max="57" width="24.25" customWidth="1"/>
-    <col min="58" max="58" width="13.25" customWidth="1"/>
-    <col min="59" max="59" width="16.08203125" customWidth="1"/>
-    <col min="60" max="60" width="8" customWidth="1"/>
-    <col min="61" max="62" width="9" customWidth="1"/>
-    <col min="63" max="63" width="27.33203125" customWidth="1"/>
-    <col min="64" max="64" width="9" customWidth="1"/>
-    <col min="65" max="65" width="39.58203125" customWidth="1"/>
-    <col min="66" max="66" width="14" customWidth="1"/>
-    <col min="67" max="67" width="14.83203125" customWidth="1"/>
-    <col min="68" max="71" width="14" customWidth="1"/>
-    <col min="72" max="72" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="22.58203125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.25" style="1" customWidth="1"/>
+    <col min="8" max="10" width="9" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5.58203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" style="1" customWidth="1"/>
+    <col min="17" max="18" width="3.83203125" style="1" customWidth="1"/>
+    <col min="19" max="20" width="3.58203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.25" style="1" customWidth="1"/>
+    <col min="22" max="22" width="9.58203125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="10.75" style="1" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="13.08203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="10.75" style="1" customWidth="1"/>
+    <col min="27" max="28" width="9" style="1" customWidth="1"/>
+    <col min="29" max="29" width="8" style="1" customWidth="1"/>
+    <col min="30" max="30" width="17.08203125" style="1" customWidth="1"/>
+    <col min="31" max="32" width="9" style="1" customWidth="1"/>
+    <col min="33" max="33" width="9.75" style="1" customWidth="1"/>
+    <col min="34" max="34" width="7.83203125" style="1" customWidth="1"/>
+    <col min="35" max="35" width="15.83203125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="13.83203125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="34.5" style="1" customWidth="1"/>
+    <col min="38" max="40" width="9.83203125" style="1" customWidth="1"/>
+    <col min="41" max="44" width="9" style="1" customWidth="1"/>
+    <col min="45" max="45" width="12.5" style="1" customWidth="1"/>
+    <col min="46" max="51" width="9" style="1" customWidth="1"/>
+    <col min="52" max="52" width="24.33203125" style="1" customWidth="1"/>
+    <col min="53" max="53" width="9" style="1" customWidth="1"/>
+    <col min="54" max="54" width="17.75" style="1" customWidth="1"/>
+    <col min="55" max="55" width="7.83203125" style="1" customWidth="1"/>
+    <col min="56" max="57" width="9" style="1" customWidth="1"/>
+    <col min="58" max="58" width="24.25" style="1" customWidth="1"/>
+    <col min="59" max="59" width="13.25" style="1" customWidth="1"/>
+    <col min="60" max="60" width="16.08203125" style="1" customWidth="1"/>
+    <col min="61" max="61" width="8" style="1" customWidth="1"/>
+    <col min="62" max="63" width="9" style="1" customWidth="1"/>
+    <col min="64" max="64" width="27.33203125" style="1" customWidth="1"/>
+    <col min="65" max="65" width="9" style="1" customWidth="1"/>
+    <col min="66" max="66" width="39.58203125" style="1" customWidth="1"/>
+    <col min="67" max="67" width="14" style="1" customWidth="1"/>
+    <col min="68" max="68" width="14.83203125" style="1" customWidth="1"/>
+    <col min="69" max="72" width="14" style="1" customWidth="1"/>
+    <col min="73" max="73" width="19.1640625" style="1" customWidth="1"/>
+    <col min="74" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="D1" t="s">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="AO1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BI1" t="s">
+    </row>
+    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AT2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AU2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AY2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BB2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BI2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BL2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BM2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BN2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BP2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="BR2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="BS2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU2" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="BA3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BK3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BM3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BN3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BO3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BP3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BQ3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BS3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BT3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BU3" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2</v>
+      </c>
+      <c r="J5" s="1">
+        <v>90</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1950</v>
+      </c>
+      <c r="M5" s="1">
+        <v>605</v>
+      </c>
+      <c r="N5" s="1">
+        <v>90</v>
+      </c>
+      <c r="O5" s="1">
+        <v>125</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>25</v>
+      </c>
+      <c r="S5" s="1">
+        <v>13</v>
+      </c>
+      <c r="T5" s="1">
+        <v>-2</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="V5" s="1">
+        <v>70</v>
+      </c>
+      <c r="W5" s="1">
+        <v>-4</v>
+      </c>
+      <c r="X5" s="1">
+        <v>7</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AL5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="AY5" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="BD5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="BF5" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="BG5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="BH5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="BI5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="BJ5" s="1">
+        <v>6</v>
+      </c>
+      <c r="BK5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="BL5" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="BM5" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="BN5" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="BO5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="BP5" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="BR5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="BS5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="BU5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1">
+        <v>90</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1500</v>
+      </c>
+      <c r="M6" s="1">
+        <v>520</v>
+      </c>
+      <c r="O6" s="1">
+        <v>115</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>50</v>
+      </c>
+      <c r="S6" s="1">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M2" t="s">
-        <v>60</v>
-      </c>
-      <c r="N2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>64</v>
-      </c>
-      <c r="R2" t="s">
-        <v>65</v>
-      </c>
-      <c r="S2" t="s">
-        <v>66</v>
-      </c>
-      <c r="T2" t="s">
-        <v>67</v>
-      </c>
-      <c r="U2" t="s">
-        <v>68</v>
-      </c>
-      <c r="V2" t="s">
-        <v>69</v>
-      </c>
-      <c r="W2" t="s">
-        <v>70</v>
-      </c>
-      <c r="X2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AQ2" t="s">
+      <c r="U6" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="V6" s="1">
+        <v>25</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ6" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AL6" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM6" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="AP6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="BD6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE6" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="BJ6" s="1">
+        <v>6</v>
+      </c>
+      <c r="BK6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="BL6" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="BO6" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="BP6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="BR6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="BS6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="BU6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1">
         <v>90</v>
       </c>
-      <c r="AR2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>99</v>
-      </c>
-      <c r="BA2" t="s">
+      <c r="K7" s="1">
         <v>100</v>
       </c>
-      <c r="BB2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>104</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>106</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>108</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>116</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>117</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" t="s">
-        <v>122</v>
-      </c>
-      <c r="L3" t="s">
-        <v>122</v>
-      </c>
-      <c r="M3" t="s">
-        <v>122</v>
-      </c>
-      <c r="N3" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" t="s">
-        <v>122</v>
-      </c>
-      <c r="P3" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>122</v>
-      </c>
-      <c r="R3" t="s">
-        <v>122</v>
-      </c>
-      <c r="S3" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" t="s">
-        <v>122</v>
-      </c>
-      <c r="U3" t="s">
-        <v>121</v>
-      </c>
-      <c r="V3" t="s">
-        <v>122</v>
-      </c>
-      <c r="W3" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>121</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>123</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>123</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>124</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>125</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>126</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>127</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>128</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>129</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="M7" s="1">
+        <v>175</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>90</v>
-      </c>
-      <c r="K5">
-        <v>1950</v>
-      </c>
-      <c r="M5">
-        <v>605</v>
-      </c>
-      <c r="N5">
-        <v>90</v>
-      </c>
-      <c r="O5">
-        <v>125</v>
-      </c>
-      <c r="Q5">
-        <v>25</v>
-      </c>
-      <c r="S5">
-        <v>13</v>
-      </c>
-      <c r="T5">
-        <v>-2</v>
-      </c>
-      <c r="U5">
-        <v>0.5</v>
-      </c>
-      <c r="V5">
-        <v>70</v>
-      </c>
-      <c r="W5">
-        <v>-4</v>
-      </c>
-      <c r="X5">
-        <v>7</v>
-      </c>
-      <c r="Y5">
-        <v>0.05</v>
-      </c>
-      <c r="Z5">
-        <v>1.6</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>132</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>133</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>134</v>
-      </c>
-      <c r="AO5" t="s">
+      <c r="AK7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD7" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="AP5">
-        <v>1</v>
-      </c>
-      <c r="AQ5">
-        <v>0.5</v>
-      </c>
-      <c r="AX5">
-        <v>0.25</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>136</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>137</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>138</v>
-      </c>
-      <c r="BF5" t="s">
+      <c r="BE7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="BG7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="BH7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="BI7" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="BG5" t="s">
-        <v>131</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>140</v>
-      </c>
-      <c r="BI5">
+      <c r="BJ7" s="1">
         <v>6</v>
       </c>
-      <c r="BJ5" t="s">
-        <v>141</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>142</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>143</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>144</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>145</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>146</v>
-      </c>
-      <c r="BQ5" t="s">
-        <v>147</v>
-      </c>
-      <c r="BR5" t="s">
-        <v>147</v>
-      </c>
-      <c r="BT5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>90</v>
-      </c>
-      <c r="K6">
-        <v>1500</v>
-      </c>
-      <c r="M6">
-        <v>520</v>
-      </c>
-      <c r="O6">
-        <v>115</v>
-      </c>
-      <c r="Q6">
-        <v>50</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0.5</v>
-      </c>
-      <c r="V6">
-        <v>25</v>
-      </c>
-      <c r="Y6">
-        <v>0.05</v>
-      </c>
-      <c r="Z6">
-        <v>1.2</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>132</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>150</v>
-      </c>
-      <c r="AM6">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>135</v>
-      </c>
-      <c r="AP6">
-        <v>1</v>
-      </c>
-      <c r="AQ6">
-        <v>0.5</v>
-      </c>
-      <c r="AX6">
-        <v>0.25</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>152</v>
-      </c>
-      <c r="BI6">
-        <v>6</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BK6" t="s">
+      <c r="BK7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="BL7" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="BO7" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BP7" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="BO6" t="s">
+      <c r="BR7" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="BQ6" t="s">
-        <v>156</v>
-      </c>
-      <c r="BR6" t="s">
-        <v>156</v>
-      </c>
-      <c r="BT6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>90</v>
-      </c>
-      <c r="K7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>175</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>10</v>
-      </c>
-      <c r="Y7">
-        <v>0.05</v>
-      </c>
-      <c r="Z7">
-        <v>0.4</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>132</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>158</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>159</v>
-      </c>
-      <c r="AM7">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>160</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>136</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>151</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>161</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>157</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>140</v>
-      </c>
-      <c r="BI7">
-        <v>6</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>162</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>163</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>154</v>
-      </c>
-      <c r="BO7" t="s">
+      <c r="BS7" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="BQ7" t="s">
-        <v>156</v>
-      </c>
-      <c r="BR7" t="s">
-        <v>156</v>
-      </c>
-      <c r="BT7">
+      <c r="BU7" s="1">
         <v>1</v>
       </c>
     </row>
@@ -3831,334 +3914,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="BK1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="BJ1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="CS1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="CR1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="DA1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="CZ1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="DI1" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -4166,337 +4249,337 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AX2" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="BA2" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BF2" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BG2" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BI2" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="BM2" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="BN2" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="BN2" s="1" t="s">
+      <c r="BO2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BP2" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="BO2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="BP2" s="1" t="s">
+      <c r="BQ2" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="BR2" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="BR2" s="1" t="s">
+      <c r="BS2" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="BS2" s="1" t="s">
+      <c r="BT2" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="BT2" s="1" t="s">
+      <c r="BU2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BV2" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="BU2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="BV2" s="1" t="s">
+      <c r="BW2" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="BW2" s="1" t="s">
+      <c r="BX2" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="BX2" s="1" t="s">
+      <c r="BY2" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="BY2" s="1" t="s">
+      <c r="BZ2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="BZ2" s="1" t="s">
+      <c r="CA2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="CA2" s="1" t="s">
+      <c r="CB2" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="CB2" s="1" t="s">
+      <c r="CC2" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="CC2" s="1" t="s">
+      <c r="CD2" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="CD2" s="1" t="s">
+      <c r="CE2" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="CE2" s="1" t="s">
+      <c r="CF2" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="CF2" s="1" t="s">
+      <c r="CG2" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="CG2" s="1" t="s">
+      <c r="CH2" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="CH2" s="1" t="s">
+      <c r="CI2" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="CI2" s="1" t="s">
+      <c r="CJ2" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="CJ2" s="1" t="s">
+      <c r="CK2" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="CK2" s="1" t="s">
+      <c r="CL2" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="CL2" s="1" t="s">
+      <c r="CM2" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="CM2" s="1" t="s">
+      <c r="CN2" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="CN2" s="1" t="s">
+      <c r="CO2" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="CO2" s="1" t="s">
+      <c r="CP2" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="CP2" s="1" t="s">
+      <c r="CQ2" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="CQ2" s="1" t="s">
+      <c r="CR2" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="CR2" s="1" t="s">
+      <c r="CS2" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="CS2" s="1" t="s">
+      <c r="CT2" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="CT2" s="1" t="s">
+      <c r="CU2" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="CU2" s="1" t="s">
+      <c r="CV2" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="CV2" s="1" t="s">
+      <c r="CW2" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="CW2" s="1" t="s">
+      <c r="CX2" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="CX2" s="1" t="s">
+      <c r="CY2" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="CY2" s="1" t="s">
+      <c r="CZ2" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="CZ2" s="1" t="s">
+      <c r="DA2" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="DA2" s="1" t="s">
+      <c r="DB2" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="DB2" s="1" t="s">
+      <c r="DC2" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="DC2" s="1" t="s">
+      <c r="DD2" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="DD2" s="1" t="s">
+      <c r="DE2" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="DE2" s="1" t="s">
+      <c r="DF2" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="DF2" s="1" t="s">
+      <c r="DG2" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="DG2" s="1" t="s">
+      <c r="DH2" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="DH2" s="1" t="s">
+      <c r="DI2" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="DI2" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -4516,381 +4599,381 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="U3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG3" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="AH3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AJ3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AK3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BA3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BF3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BG3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="BI3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BK3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BL3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BM3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BN3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BO3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="AL3" s="1" t="s">
+      <c r="BP3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="AM3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AN3" s="1" t="s">
+      <c r="BQ3" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="BS3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="AO3" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="AP3" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="AQ3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="AU3" s="1" t="s">
+      <c r="BT3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="AV3" s="1" t="s">
+      <c r="BU3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BV3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BW3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BX3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="AW3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AX3" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="AY3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AZ3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BA3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BB3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BD3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BE3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BF3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BH3" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="BI3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BJ3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BK3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BL3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BM3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BN3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BO3" s="1" t="s">
+      <c r="BY3" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="BZ3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="CA3" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="CB3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="BP3" s="1" t="s">
+      <c r="CC3" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="CD3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="BQ3" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BT3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BU3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BV3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BX3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BY3" s="1" t="s">
+      <c r="CE3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="CF3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="CG3" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="CH3" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="CI3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="CK3" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="CL3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="CN3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="CO3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR3" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="BZ3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="CA3" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="CB3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="CC3" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="CD3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="CE3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="CF3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="CG3" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="CH3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="CI3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="1" t="s">
+      <c r="CS3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CT3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="CU3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV3" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="CK3" s="1" t="s">
+      <c r="CW3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="CX3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="CY3" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="CL3" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="CM3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="CN3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="CO3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="CQ3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="CR3" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="CS3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="CT3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="CU3" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="CV3" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="CW3" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="CX3" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="CY3" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="CZ3" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="DA3" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="DB3" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="DC3" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="DD3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="DE3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="DF3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="DG3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="DH3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="DI3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="AC5" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="AC5" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO5" s="1" t="s">
+      <c r="AT5" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="AT5" s="1" t="s">
+      <c r="AX5" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="AX5" s="1" t="s">
+      <c r="AZ5" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO5" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="AZ5" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD5" s="1">
-        <v>1</v>
-      </c>
-      <c r="BO5" s="1" t="s">
+      <c r="CB5" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="CB5" s="1" t="s">
+      <c r="CG5" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="CG5" s="1" t="s">
+      <c r="CH5" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="CH5" s="1" t="s">
+      <c r="CI5" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="CI5" s="1" t="s">
+      <c r="CJ5" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="CJ5" s="1" t="s">
+      <c r="CN5" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="CN5" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="CO5" s="1">
         <v>-0.1</v>
@@ -4899,10 +4982,10 @@
         <v>2</v>
       </c>
       <c r="CW5" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="CY5" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="CY5" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="DG5" s="1">
         <v>1</v>
@@ -4910,17 +4993,17 @@
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="AC6" s="1">
         <v>2</v>
       </c>
@@ -4928,14 +5011,14 @@
         <v>1</v>
       </c>
       <c r="AO6" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AT6" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="AT6" s="1" t="s">
+      <c r="AX6" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="AX6" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="AZ6" s="1">
         <v>1</v>
       </c>
@@ -4943,22 +5026,22 @@
         <v>1</v>
       </c>
       <c r="CB6" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="CG6" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="CG6" s="1" t="s">
+      <c r="CH6" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="CH6" s="1" t="s">
+      <c r="CI6" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="CI6" s="1" t="s">
+      <c r="CJ6" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="CJ6" s="1" t="s">
+      <c r="CN6" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="CN6" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="CO6" s="1">
         <v>-0.1</v>
@@ -4967,10 +5050,10 @@
         <v>2</v>
       </c>
       <c r="CW6" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="CY6" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="CY6" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="DG6" s="1">
         <v>1</v>
@@ -4978,55 +5061,55 @@
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AT7" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AX7" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="AZ7" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB7" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="AT7" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="AX7" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="AZ7" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD7" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB7" s="1" t="s">
+      <c r="CG7" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CH7" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="CI7" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="CJ7" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="CN7" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="CG7" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="CH7" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="CI7" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="CJ7" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="CN7" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="CO7" s="1">
         <v>-0.1</v>
@@ -5035,10 +5118,10 @@
         <v>8</v>
       </c>
       <c r="CW7" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="CY7" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="CY7" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="DG7" s="1">
         <v>1</v>
@@ -5046,19 +5129,19 @@
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="R8" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC8" s="1">
         <v>2</v>
@@ -5073,7 +5156,7 @@
         <v>99</v>
       </c>
       <c r="CN8" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="CR8" s="1">
         <v>99999</v>
@@ -5084,19 +5167,19 @@
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="1" t="s">
+      <c r="R9" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>419</v>
       </c>
       <c r="AC9" s="1">
         <v>2</v>
@@ -5111,7 +5194,7 @@
         <v>99</v>
       </c>
       <c r="CN9" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="CO9" s="1">
         <v>-0.1</v>
@@ -5125,19 +5208,19 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="AC10" s="1">
         <v>2</v>
@@ -5155,10 +5238,10 @@
         <v>0.1</v>
       </c>
       <c r="CN10" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="CO10" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="CO10" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="CR10" s="1">
         <v>0.2</v>
@@ -5169,22 +5252,22 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="R11" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="AC11" s="1">
         <v>2</v>
@@ -5202,10 +5285,10 @@
         <v>0.1</v>
       </c>
       <c r="CN11" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="CO11" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="CR11" s="1">
         <v>0.2</v>
@@ -5216,19 +5299,19 @@
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AC12" s="1">
         <v>2</v>
@@ -5246,7 +5329,7 @@
         <v>0.1</v>
       </c>
       <c r="CN12" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="CR12" s="1">
         <v>0.2</v>
@@ -5257,37 +5340,37 @@
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="I13" s="1">
-        <v>1</v>
-      </c>
-      <c r="P13" s="1" t="s">
+      <c r="AC13" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AW13" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD13" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO13" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="AC13" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD13" s="1">
-        <v>1</v>
-      </c>
-      <c r="AW13" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD13" s="1">
-        <v>1</v>
-      </c>
-      <c r="BO13" s="1" t="s">
+      <c r="CN13" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="CN13" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="CR13" s="1">
         <v>10</v>
@@ -5298,19 +5381,19 @@
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="I14" s="1">
         <v>1</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AC14" s="1">
         <v>2</v>
@@ -5325,7 +5408,7 @@
         <v>1</v>
       </c>
       <c r="CN14" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="CR14" s="1">
         <v>10</v>
@@ -5336,16 +5419,16 @@
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="AC15" s="1">
         <v>2</v>
@@ -5363,7 +5446,7 @@
         <v>0.1</v>
       </c>
       <c r="CN15" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="CR15" s="1">
         <v>0.2</v>
@@ -5374,19 +5457,19 @@
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="AC16" s="1">
         <v>2</v>
@@ -5401,16 +5484,16 @@
         <v>99</v>
       </c>
       <c r="BO16" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="BP16" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="CM16" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="CN16" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="CM16" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="CN16" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="CR16" s="1">
         <v>10.1</v>
@@ -5421,19 +5504,19 @@
     </row>
     <row r="17" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
       </c>
       <c r="Q17" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="R17" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>445</v>
       </c>
       <c r="AC17" s="1">
         <v>2</v>
@@ -5448,13 +5531,13 @@
         <v>99</v>
       </c>
       <c r="BP17" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="CM17" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="CN17" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="CR17" s="1">
         <v>99999</v>
@@ -5465,34 +5548,34 @@
     </row>
     <row r="18" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="P18" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I18" s="1">
-        <v>1</v>
-      </c>
-      <c r="P18" s="1" t="s">
+      <c r="Q18" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="Q18" s="1" t="s">
+      <c r="AC18" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AW18" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD18" s="1">
+        <v>1</v>
+      </c>
+      <c r="BP18" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="AC18" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD18" s="1">
-        <v>1</v>
-      </c>
-      <c r="AW18" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD18" s="1">
-        <v>1</v>
-      </c>
-      <c r="BP18" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="BS18" s="1">
         <v>1</v>
@@ -5509,31 +5592,31 @@
     </row>
     <row r="19" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="I19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1" t="s">
+      <c r="AC19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="AC19" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="1" t="s">
+      <c r="BD19" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO19" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="BD19" s="1">
-        <v>1</v>
-      </c>
-      <c r="BO19" s="1" t="s">
+      <c r="CU19" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="CU19" s="1" t="s">
-        <v>455</v>
       </c>
       <c r="DI19" s="1">
         <v>1</v>
@@ -5541,16 +5624,16 @@
     </row>
     <row r="20" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AC20" s="1">
         <v>2</v>
@@ -5579,10 +5662,10 @@
     </row>
     <row r="21" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
@@ -5600,7 +5683,7 @@
         <v>99</v>
       </c>
       <c r="BP21" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="BS21" s="1">
         <v>0.1</v>
@@ -5614,28 +5697,28 @@
     </row>
     <row r="22" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="AC22" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="AC22" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="BD22" s="1">
         <v>1</v>
       </c>
       <c r="CN22" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="CR22" s="1">
         <v>1.1000000000000001</v>
@@ -5649,37 +5732,37 @@
     </row>
     <row r="23" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I23" s="1">
         <v>1</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG23" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="Q23" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="AC23" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG23" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="BD23" s="1">
         <v>1</v>
       </c>
       <c r="CB23" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="CG23" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CN23" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="CG23" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="CN23" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="CO23" s="1">
         <v>0.15</v>
@@ -5690,19 +5773,19 @@
     </row>
     <row r="24" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC24" s="1">
         <v>2</v>
@@ -5717,16 +5800,16 @@
         <v>99</v>
       </c>
       <c r="BO24" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="BP24" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="BP24" s="1" t="s">
+      <c r="CM24" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="CM24" s="1" t="s">
+      <c r="CN24" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="CN24" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="CR24" s="1">
         <v>99999</v>
@@ -5740,16 +5823,16 @@
     </row>
     <row r="25" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AC25" s="1">
         <v>1</v>
@@ -5761,24 +5844,24 @@
         <v>99</v>
       </c>
       <c r="CU25" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="26" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I26" s="1">
         <v>1</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AC26" s="1">
         <v>2</v>
@@ -5790,7 +5873,7 @@
         <v>20</v>
       </c>
       <c r="AX26" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AZ26" s="1">
         <v>9999999</v>
@@ -5802,10 +5885,10 @@
         <v>99</v>
       </c>
       <c r="CM26" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="CN26" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="CR26" s="1">
         <v>99999</v>
@@ -5819,43 +5902,43 @@
     </row>
     <row r="27" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="AC27" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="BD27" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO27" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="AC27" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG27" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="BD27" s="1">
-        <v>1</v>
-      </c>
-      <c r="BO27" s="1" t="s">
+      <c r="BP27" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="BP27" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="BT27" s="1">
         <v>0.2</v>
@@ -5870,16 +5953,16 @@
         <v>2</v>
       </c>
       <c r="BY27" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="CB27" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="CG27" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CN27" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="CG27" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="CN27" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="CO27" s="1">
         <v>0.08</v>
@@ -5890,13 +5973,13 @@
     </row>
     <row r="28" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AC28" s="1">
         <v>2</v>
@@ -5905,16 +5988,16 @@
         <v>1</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AR28" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AW28" s="1">
         <v>1</v>
       </c>
       <c r="AX28" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AZ28" s="1">
         <v>1.6</v>
@@ -5923,28 +6006,28 @@
         <v>2</v>
       </c>
       <c r="CG28" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CH28" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="CH28" s="1" t="s">
+      <c r="CI28" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="CI28" s="1" t="s">
+      <c r="CJ28" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="CJ28" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="CN28" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="CR28" s="1">
         <v>5</v>
       </c>
       <c r="CW28" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="CY28" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="CY28" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="DG28" s="1">
         <v>1</v>
@@ -5952,19 +6035,19 @@
     </row>
     <row r="29" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC29" s="1">
         <v>2</v>
@@ -5979,7 +6062,7 @@
         <v>99</v>
       </c>
       <c r="CN29" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="CO29" s="1">
         <v>-0.1</v>
@@ -5993,43 +6076,43 @@
     </row>
     <row r="30" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="G30" s="1">
         <v>3</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K30" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="AB30" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="BD30" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO30" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="AB30" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="BD30" s="1">
-        <v>1</v>
-      </c>
-      <c r="BO30" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="BT30" s="1">
         <v>15</v>
@@ -6044,19 +6127,19 @@
         <v>1</v>
       </c>
       <c r="BY30" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="CB30" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="CG30" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CM30" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="CG30" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="CM30" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="CN30" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="CR30" s="1">
         <v>15</v>
@@ -6064,28 +6147,28 @@
     </row>
     <row r="31" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC31" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD31" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO31" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC31" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD31" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO31" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="AT31" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AX31" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="AX31" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="AZ31" s="1">
         <v>1.2</v>
@@ -6106,16 +6189,16 @@
         <v>1</v>
       </c>
       <c r="CH31" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="CI31" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="CI31" s="1" t="s">
+      <c r="CJ31" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="CJ31" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="CN31" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="CO31" s="1">
         <v>-0.1</v>
@@ -6127,7 +6210,7 @@
         <v>2</v>
       </c>
       <c r="CY31" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="DG31" s="1">
         <v>1</v>
@@ -6135,19 +6218,19 @@
     </row>
     <row r="32" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I32" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="1" t="s">
+      <c r="R32" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>496</v>
       </c>
       <c r="AC32" s="1">
         <v>2</v>
@@ -6162,10 +6245,10 @@
         <v>99</v>
       </c>
       <c r="CM32" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="CN32" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="CR32" s="1">
         <v>2</v>
@@ -6176,43 +6259,43 @@
     </row>
     <row r="33" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="AC33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="BD33" s="1">
+        <v>1</v>
+      </c>
+      <c r="BP33" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="CB33" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="CG33" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CM33" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="I33" s="1">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="AC33" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG33" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="BD33" s="1">
-        <v>1</v>
-      </c>
-      <c r="BP33" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="CB33" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="CG33" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="CM33" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="CN33" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="CR33" s="1">
         <v>1</v>
@@ -6220,13 +6303,13 @@
     </row>
     <row r="34" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AC34" s="1">
         <v>2</v>
@@ -6235,13 +6318,13 @@
         <v>1</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AT34" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AX34" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="AX34" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="AZ34" s="1">
         <v>3</v>
@@ -6259,13 +6342,13 @@
         <v>1</v>
       </c>
       <c r="CG34" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="CJ34" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="CN34" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="CO34" s="1">
         <v>0.8</v>
@@ -6277,7 +6360,7 @@
         <v>8</v>
       </c>
       <c r="CY34" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="DG34" s="1">
         <v>1</v>
@@ -6285,13 +6368,13 @@
     </row>
     <row r="35" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AC35" s="1">
         <v>2</v>
@@ -6306,7 +6389,7 @@
         <v>99</v>
       </c>
       <c r="CM35" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="DG35" s="1">
         <v>1</v>
@@ -6314,19 +6397,19 @@
     </row>
     <row r="36" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="I36" s="1">
-        <v>1</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="Q36" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AC36" s="1">
         <v>2</v>
@@ -6344,10 +6427,10 @@
         <v>0.1</v>
       </c>
       <c r="CN36" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="CO36" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="CR36" s="1">
         <v>0.2</v>
@@ -6358,22 +6441,22 @@
     </row>
     <row r="37" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="I37" s="1">
-        <v>1</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="Q37" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AC37" s="1">
         <v>2</v>
@@ -6391,10 +6474,10 @@
         <v>0.1</v>
       </c>
       <c r="CN37" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="CO37" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="CR37" s="1">
         <v>0.2</v>
@@ -6405,42 +6488,42 @@
     </row>
     <row r="38" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="L38" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="I38" s="1">
-        <v>1</v>
-      </c>
-      <c r="K38" s="1" t="s">
+      <c r="AC38" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG38" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="BD38" s="1">
+        <v>1</v>
+      </c>
+      <c r="CU38" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="AC38" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF38" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="BD38" s="1">
-        <v>1</v>
-      </c>
-      <c r="CU38" s="1" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="39" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
@@ -6461,7 +6544,7 @@
         <v>0.1</v>
       </c>
       <c r="CN39" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="CR39" s="1">
         <v>0.2</v>
@@ -6472,16 +6555,16 @@
     </row>
     <row r="40" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="O40" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="I40" s="1">
-        <v>1</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="AC40" s="1">
         <v>1</v>
@@ -6499,7 +6582,7 @@
         <v>0.1</v>
       </c>
       <c r="CN40" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="CO40" s="1">
         <v>80</v>
@@ -6513,46 +6596,46 @@
     </row>
     <row r="41" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
       </c>
       <c r="J41" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="AB41" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO41" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="AB41" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC41" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD41" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO41" s="1" t="s">
+      <c r="AT41" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="AT41" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="AX41" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AZ41" s="1">
         <v>1</v>
@@ -6561,7 +6644,7 @@
         <v>4</v>
       </c>
       <c r="BO41" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="BT41" s="1">
         <v>35</v>
@@ -6576,34 +6659,34 @@
         <v>1</v>
       </c>
       <c r="BY41" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="CB41" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="CE41" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="CG41" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CH41" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="CH41" s="1" t="s">
+      <c r="CI41" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="CI41" s="1" t="s">
+      <c r="CJ41" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="CJ41" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="CN41" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="CR41" s="1">
         <v>1</v>
       </c>
       <c r="CY41" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="DG41" s="1">
         <v>1</v>
@@ -6614,28 +6697,28 @@
     </row>
     <row r="42" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="L42" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="L42" s="1" t="s">
+      <c r="AC42" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD42" s="1">
+        <v>1</v>
+      </c>
+      <c r="BP42" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="AC42" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD42" s="1">
-        <v>1</v>
-      </c>
-      <c r="BP42" s="1" t="s">
+      <c r="CN42" s="1" t="s">
         <v>527</v>
-      </c>
-      <c r="CN42" s="1" t="s">
-        <v>528</v>
       </c>
       <c r="CO42" s="1">
         <v>-0.8</v>
@@ -6649,13 +6732,13 @@
     </row>
     <row r="43" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AC43" s="1">
         <v>2</v>
@@ -6664,13 +6747,13 @@
         <v>1</v>
       </c>
       <c r="AT43" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="BD43" s="1">
         <v>99</v>
       </c>
       <c r="CN43" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="CR43" s="1">
         <v>15</v>
@@ -6681,13 +6764,13 @@
     </row>
     <row r="44" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AC44" s="1">
         <v>2</v>
@@ -6705,10 +6788,10 @@
         <v>0.1</v>
       </c>
       <c r="CN44" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="CO44" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="CO44" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="CR44" s="1">
         <v>0.2</v>
@@ -6719,40 +6802,40 @@
     </row>
     <row r="45" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="AC45" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG45" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="BD45" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB45" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="CG45" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CM45" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I45" s="1">
-        <v>1</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="AC45" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG45" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="BD45" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB45" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="CG45" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="CM45" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="CN45" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="CR45" s="1">
         <v>1</v>
@@ -6760,16 +6843,16 @@
     </row>
     <row r="46" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I46" s="1">
         <v>1</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AC46" s="1">
         <v>1</v>
@@ -6787,7 +6870,7 @@
         <v>0.1</v>
       </c>
       <c r="CN46" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="CR46" s="1">
         <v>0.2</v>
@@ -6801,66 +6884,66 @@
     </row>
     <row r="47" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="L47" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I47" s="1">
-        <v>1</v>
-      </c>
-      <c r="K47" s="1" t="s">
+      <c r="N47" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC47" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG47" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="BD47" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB47" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="N47" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC47" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG47" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="BD47" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB47" s="1" t="s">
-        <v>537</v>
-      </c>
       <c r="CG47" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="49" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="I49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="L49" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="I49" s="1">
-        <v>1</v>
-      </c>
-      <c r="K49" s="1" t="s">
+      <c r="AC49" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG49" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="AC49" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG49" s="1" t="s">
-        <v>453</v>
       </c>
       <c r="BD49" s="1">
         <v>1</v>
@@ -6868,58 +6951,58 @@
     </row>
     <row r="50" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="AC50" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD50" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO50" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AR50" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="AT50" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="AC50" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD50" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO50" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="AR50" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="AT50" s="1" t="s">
+      <c r="AX50" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="AZ50" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD50" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO50" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="AX50" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="AZ50" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD50" s="1">
-        <v>1</v>
-      </c>
-      <c r="BO50" s="1" t="s">
+      <c r="CB50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="CG50" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CH50" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="CB50" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="CG50" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="CH50" s="1" t="s">
+      <c r="CI50" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="CI50" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="CJ50" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="CM50" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="CY50" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="DG50" s="1">
         <v>1</v>
@@ -6927,64 +7010,64 @@
     </row>
     <row r="51" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="AC51" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD51" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO51" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AR51" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="AT51" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="AX51" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="AZ51" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD51" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="CG51" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CH51" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="AC51" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD51" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO51" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="AR51" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="AT51" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="AX51" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="AZ51" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD51" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB51" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="CG51" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="CH51" s="1" t="s">
+      <c r="CI51" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="CI51" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="CJ51" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="CM51" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="CN51" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="CR51" s="1">
         <v>15</v>
       </c>
       <c r="CY51" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="DG51" s="1">
         <v>1</v>
@@ -6992,37 +7075,37 @@
     </row>
     <row r="53" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="I53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="AC53" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG53" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="BD53" s="1">
+        <v>1</v>
+      </c>
+      <c r="CN53" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="I53" s="1">
-        <v>1</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="AC53" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG53" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="BD53" s="1">
-        <v>1</v>
-      </c>
-      <c r="CN53" s="1" t="s">
-        <v>546</v>
       </c>
       <c r="CR53" s="1">
         <v>99999</v>
@@ -7030,52 +7113,52 @@
     </row>
     <row r="54" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="AC54" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD54" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO54" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AR54" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="AT54" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="AC54" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD54" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO54" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="AR54" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="AT54" s="1" t="s">
+      <c r="AX54" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="AZ54" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD54" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB54" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="CG54" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CH54" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="AX54" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="AZ54" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD54" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="CG54" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="CH54" s="1" t="s">
+      <c r="CI54" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="CI54" s="1" t="s">
+      <c r="CJ54" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="CY54" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="CJ54" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="CY54" s="1" t="s">
-        <v>551</v>
       </c>
       <c r="DG54" s="1">
         <v>1</v>
@@ -7083,16 +7166,16 @@
     </row>
     <row r="55" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I55" s="1">
         <v>1</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AC55" s="1">
         <v>2</v>
@@ -7101,22 +7184,22 @@
         <v>1</v>
       </c>
       <c r="AT55" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="BD55" s="1">
         <v>99</v>
       </c>
       <c r="BO55" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="BS55" s="1">
         <v>0.1</v>
       </c>
       <c r="CN55" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="CO55" s="1" t="s">
         <v>554</v>
-      </c>
-      <c r="CO55" s="1" t="s">
-        <v>555</v>
       </c>
       <c r="CR55" s="1">
         <v>0.2</v>
@@ -7124,16 +7207,16 @@
     </row>
     <row r="56" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I56" s="1">
         <v>1</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AC56" s="1">
         <v>2</v>
@@ -7142,7 +7225,7 @@
         <v>1</v>
       </c>
       <c r="AT56" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="BD56" s="1">
         <v>99</v>
@@ -7151,10 +7234,10 @@
         <v>0.1</v>
       </c>
       <c r="CN56" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="CO56" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="CR56" s="1">
         <v>0.2</v>
@@ -7162,16 +7245,16 @@
     </row>
     <row r="57" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I57" s="1">
         <v>1</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AC57" s="1">
         <v>2</v>
@@ -7186,10 +7269,10 @@
         <v>1</v>
       </c>
       <c r="BO57" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="BP57" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="BP57" s="1" t="s">
-        <v>559</v>
       </c>
       <c r="BS57" s="1">
         <v>0.1</v>
@@ -7203,28 +7286,28 @@
     </row>
     <row r="58" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I58" s="1">
         <v>1</v>
       </c>
       <c r="K58" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="AC58" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="AC58" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG58" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="BD58" s="1">
         <v>1</v>
       </c>
       <c r="CN58" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="CR58" s="1">
         <v>0.2</v>
@@ -7235,22 +7318,22 @@
     </row>
     <row r="59" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I59" s="1">
         <v>1</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AC59" s="1">
         <v>1</v>
       </c>
       <c r="AG59" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="BD59" s="1">
         <v>1</v>
@@ -7259,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="CN59" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="CR59" s="1">
         <v>99999</v>
@@ -7303,37 +7386,37 @@
         <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -7341,49 +7424,49 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -7397,373 +7480,373 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>585</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K9" s="1">
         <v>5</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="Q11" s="1" t="s">
         <v>590</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K13" s="1">
         <v>5</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K16" s="1">
         <v>5</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>597</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="Q27" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K28" s="1">
         <v>5</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q29" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K30" s="1">
         <v>5</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K31" s="1">
         <v>5</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -7791,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7799,13 +7882,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -7816,24 +7899,24 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -7858,7 +7941,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -7866,31 +7949,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -7907,22 +7990,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -7951,34 +8034,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -7986,37 +8069,37 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -8027,34 +8110,34 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -8087,31 +8170,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>642</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -8128,22 +8211,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -8174,28 +8257,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -8203,28 +8286,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -8232,10 +8315,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -8267,22 +8350,22 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>662</v>
-      </c>
       <c r="G4" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>661</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -8296,22 +8379,22 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="G5" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>664</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -8325,22 +8408,22 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>668</v>
-      </c>
       <c r="G6" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>667</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>668</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/尊尼获加/莫菲丝.xlsx
+++ b/Excel/尊尼获加/莫菲丝.xlsx
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="676">
   <si>
     <t>Id</t>
   </si>
@@ -340,459 +340,486 @@
     <t>莫菲丝</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>模型大小倍率</t>
+  </si>
+  <si>
+    <t>模型偏移</t>
+  </si>
+  <si>
+    <t>精英化</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>血</t>
+  </si>
+  <si>
+    <t>攻</t>
+  </si>
+  <si>
+    <t>防</t>
+  </si>
+  <si>
+    <t>魔防</t>
+  </si>
+  <si>
+    <t>消耗</t>
+  </si>
+  <si>
+    <t>消耗增长</t>
+  </si>
+  <si>
+    <t>复活时间</t>
+  </si>
+  <si>
+    <t>额外攻速</t>
+  </si>
+  <si>
+    <t>抛光系数</t>
+  </si>
+  <si>
+    <t>攻击间隔</t>
+  </si>
+  <si>
+    <t>重量</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>部署占用数</t>
+  </si>
+  <si>
+    <t>撤离后不返回</t>
+  </si>
+  <si>
+    <t>部署策略</t>
+  </si>
+  <si>
+    <t>可部署上限</t>
+  </si>
+  <si>
+    <t>仇恨等级</t>
+  </si>
+  <si>
+    <t>被攻击点</t>
+  </si>
+  <si>
+    <t>常驻技能</t>
+  </si>
+  <si>
+    <t>可选技能</t>
+  </si>
+  <si>
+    <t>血条</t>
+  </si>
+  <si>
+    <t>技力条</t>
+  </si>
+  <si>
+    <t>高度</t>
+  </si>
+  <si>
+    <t>可部署位</t>
+  </si>
+  <si>
+    <t>阻挡个数</t>
+  </si>
+  <si>
+    <t>返还倍率</t>
+  </si>
+  <si>
+    <t>不占用地板</t>
+  </si>
+  <si>
+    <t>生命恢复</t>
+  </si>
+  <si>
+    <t>不参与击杀计数</t>
+  </si>
+  <si>
+    <t>终点伤害</t>
+  </si>
+  <si>
+    <t>抗性</t>
+  </si>
+  <si>
+    <t>半径</t>
+  </si>
+  <si>
+    <t>大小</t>
+  </si>
+  <si>
+    <t>阻挡？</t>
+  </si>
+  <si>
+    <t>仅阻挡时可被攻击</t>
+  </si>
+  <si>
+    <t>存活时间</t>
+  </si>
+  <si>
+    <t>头像</t>
+  </si>
+  <si>
+    <t>半身像</t>
+  </si>
+  <si>
+    <t>立绘</t>
+  </si>
+  <si>
+    <t>立绘位置</t>
+  </si>
+  <si>
+    <t>稀有</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>ModelScale</t>
+  </si>
+  <si>
+    <t>ModelOffset</t>
+  </si>
+  <si>
+    <t>engName</t>
+  </si>
+  <si>
+    <t>Upgrade</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>HpEx</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>AttackEx</t>
+  </si>
+  <si>
+    <t>Defence</t>
+  </si>
+  <si>
+    <t>DefenceEx</t>
+  </si>
+  <si>
+    <t>MagicDefence</t>
+  </si>
+  <si>
+    <t>MagicDefenceEx</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>CostEx</t>
+  </si>
+  <si>
+    <t>CostAdd</t>
+  </si>
+  <si>
+    <t>ResetTime</t>
+  </si>
+  <si>
+    <t>ResetTimeEx</t>
+  </si>
+  <si>
+    <t>ExAgi</t>
+  </si>
+  <si>
+    <t>MinDamageRate</t>
+  </si>
+  <si>
+    <t>AttackGap</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>BuildCountCost</t>
+  </si>
+  <si>
+    <t>NotReturn</t>
+  </si>
+  <si>
+    <t>RedeployPolicy</t>
+  </si>
+  <si>
+    <t>BuildCountLimit</t>
+  </si>
+  <si>
+    <t>Hatred</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>HitPointName</t>
+  </si>
+  <si>
+    <t>Skills</t>
+  </si>
+  <si>
+    <t>MainSkill</t>
+  </si>
+  <si>
+    <t>HpBarType</t>
+  </si>
+  <si>
+    <t>SpBarType</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>CanSetPos</t>
+  </si>
+  <si>
+    <t>StopCount</t>
+  </si>
+  <si>
+    <t>LeaveReturn</t>
+  </si>
+  <si>
+    <t>NotUseTile</t>
+  </si>
+  <si>
+    <t>#敌人用</t>
+  </si>
+  <si>
+    <t>HpRecover</t>
+  </si>
+  <si>
+    <t>WithoutCheckCount</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>IgnoreBuff</t>
+  </si>
+  <si>
+    <t>Radius</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>CanStop</t>
+  </si>
+  <si>
+    <t>StopAttackOnly</t>
+  </si>
+  <si>
+    <t>LifeTime</t>
+  </si>
+  <si>
+    <t>Profession</t>
+  </si>
+  <si>
+    <t>Profession2</t>
+  </si>
+  <si>
+    <t>HeadIcon</t>
+  </si>
+  <si>
+    <t>HalfIcon</t>
+  </si>
+  <si>
+    <t>StandPic</t>
+  </si>
+  <si>
+    <t>StandPicPos</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>SetPos</t>
+  </si>
+  <si>
+    <t>Tags</t>
+  </si>
+  <si>
+    <t>AblitityInfo</t>
+  </si>
+  <si>
+    <t>Ablititys</t>
+  </si>
+  <si>
+    <t>DefaultAnimation</t>
+  </si>
+  <si>
+    <t>IdleAnimation</t>
+  </si>
+  <si>
+    <t>MoveAnimation</t>
+  </si>
+  <si>
+    <t>DeadAnimation</t>
+  </si>
+  <si>
+    <t>StunAnimation</t>
+  </si>
+  <si>
+    <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>MaxAnimationScale</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>UnityEngine.Vector3</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>SkillData[]</t>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>BuffData[]</t>
+  </si>
+  <si>
+    <t>UnityEngine.Vector2Int</t>
+  </si>
+  <si>
+    <t>UnitTypeEnum</t>
+  </si>
+  <si>
+    <t>float[]</t>
+  </si>
+  <si>
+    <t>System.Collections.Generic.Dictionary&lt;string,object&gt;</t>
+  </si>
+  <si>
+    <t>干员</t>
+  </si>
+  <si>
+    <t>hamoni</t>
+  </si>
+  <si>
+    <t>Hip</t>
+  </si>
+  <si>
+    <t>莫菲丝攻击,莫菲丝入场,莫菲丝死亡倒计时</t>
+  </si>
+  <si>
+    <t>莫菲丝1,莫菲丝2,莫菲丝3</t>
+  </si>
+  <si>
+    <t>小型:蓝</t>
+  </si>
+  <si>
+    <t>小型:绿</t>
+  </si>
+  <si>
+    <t>高台位</t>
+  </si>
+  <si>
+    <t>辅助</t>
+  </si>
+  <si>
+    <t>削弱者</t>
+  </si>
+  <si>
+    <t>icon_morphis</t>
+  </si>
+  <si>
+    <t>half_hamoni</t>
+  </si>
+  <si>
+    <t>211,81,1500,1500</t>
+  </si>
+  <si>
+    <t>远程位</t>
+  </si>
+  <si>
+    <t>维多利亚,远程</t>
+  </si>
+  <si>
+    <t>攻击造成法术伤害,对目标造成10％虚弱效果，持续2秒</t>
+  </si>
+  <si>
+    <t>{"梦境缠绕":"自身及召唤物可以攻击进入睡眠状态的敌人，且攻击倍率提升至160%，优先攻击自身未攻击过或睡眠中的敌人，自身对每个敌人首次造成伤害的同时，令其进入8秒睡眠。被自身睡眠的敌人法术抗性-100%。若睡眠失败或被打断睡眠则改为等时长的束缚，期间其法术抗性-40%","意识脱离":"攻击范围内敌人濒死或生命值低于自身攻击力150%时，令其进入意识脱离状态，持续10秒，期间目标获得无敌，不可移动与攻击，不可被阻挡，场上不存在卡尔顿时，选择一个处于意识脱离状态的敌人所在格部署卡尔顿，卡尔顿所在格及周围八格的敌人攻击力-40%，移动速度-40%。目标意识脱离状态结束后将其击杀，且自身攻击范围内所有干员回复2点技力"}</t>
+  </si>
+  <si>
+    <t>B_Default</t>
+  </si>
+  <si>
+    <t>B_Idle</t>
+  </si>
+  <si>
+    <t>B_Die</t>
+  </si>
+  <si>
     <t>沃尔夫</t>
   </si>
   <si>
+    <t>mjcgst</t>
+  </si>
+  <si>
+    <t>沃尔夫攻击,通用绝食</t>
+  </si>
+  <si>
+    <t>沃尔夫描述</t>
+  </si>
+  <si>
+    <t>小型:橙</t>
+  </si>
+  <si>
+    <t>召唤物</t>
+  </si>
+  <si>
+    <t>icon_wolf</t>
+  </si>
+  <si>
+    <t>召唤物,远程</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Idle</t>
+  </si>
+  <si>
+    <t>Die</t>
+  </si>
+  <si>
     <t>卡尔顿</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>模型大小倍率</t>
-  </si>
-  <si>
-    <t>精英化</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>血</t>
-  </si>
-  <si>
-    <t>攻</t>
-  </si>
-  <si>
-    <t>防</t>
-  </si>
-  <si>
-    <t>魔防</t>
-  </si>
-  <si>
-    <t>消耗</t>
-  </si>
-  <si>
-    <t>消耗增长</t>
-  </si>
-  <si>
-    <t>复活时间</t>
-  </si>
-  <si>
-    <t>额外攻速</t>
-  </si>
-  <si>
-    <t>抛光系数</t>
-  </si>
-  <si>
-    <t>攻击间隔</t>
-  </si>
-  <si>
-    <t>重量</t>
-  </si>
-  <si>
-    <t>移动速度</t>
-  </si>
-  <si>
-    <t>部署占用数</t>
-  </si>
-  <si>
-    <t>撤离后不返回</t>
-  </si>
-  <si>
-    <t>部署策略</t>
-  </si>
-  <si>
-    <t>可部署上限</t>
-  </si>
-  <si>
-    <t>仇恨等级</t>
-  </si>
-  <si>
-    <t>被攻击点</t>
-  </si>
-  <si>
-    <t>常驻技能</t>
-  </si>
-  <si>
-    <t>可选技能</t>
-  </si>
-  <si>
-    <t>高度</t>
-  </si>
-  <si>
-    <t>可部署位</t>
-  </si>
-  <si>
-    <t>阻挡个数</t>
-  </si>
-  <si>
-    <t>返还倍率</t>
-  </si>
-  <si>
-    <t>不占用地板</t>
-  </si>
-  <si>
-    <t>生命恢复</t>
-  </si>
-  <si>
-    <t>不参与击杀计数</t>
-  </si>
-  <si>
-    <t>终点伤害</t>
-  </si>
-  <si>
-    <t>抗性</t>
-  </si>
-  <si>
-    <t>半径</t>
-  </si>
-  <si>
-    <t>大小</t>
-  </si>
-  <si>
-    <t>阻挡？</t>
-  </si>
-  <si>
-    <t>仅阻挡时可被攻击</t>
-  </si>
-  <si>
-    <t>存活时间</t>
-  </si>
-  <si>
-    <t>头像</t>
-  </si>
-  <si>
-    <t>半身像</t>
-  </si>
-  <si>
-    <t>立绘</t>
-  </si>
-  <si>
-    <t>立绘位置</t>
-  </si>
-  <si>
-    <t>稀有</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>ModelScale</t>
-  </si>
-  <si>
-    <t>engName</t>
-  </si>
-  <si>
-    <t>Upgrade</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Hp</t>
-  </si>
-  <si>
-    <t>HpEx</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>AttackEx</t>
-  </si>
-  <si>
-    <t>Defence</t>
-  </si>
-  <si>
-    <t>DefenceEx</t>
-  </si>
-  <si>
-    <t>MagicDefence</t>
-  </si>
-  <si>
-    <t>MagicDefenceEx</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>CostEx</t>
-  </si>
-  <si>
-    <t>CostAdd</t>
-  </si>
-  <si>
-    <t>ResetTime</t>
-  </si>
-  <si>
-    <t>ResetTimeEx</t>
-  </si>
-  <si>
-    <t>ExAgi</t>
-  </si>
-  <si>
-    <t>MinDamageRate</t>
-  </si>
-  <si>
-    <t>AttackGap</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>Speed</t>
-  </si>
-  <si>
-    <t>BuildCountCost</t>
-  </si>
-  <si>
-    <t>NotReturn</t>
-  </si>
-  <si>
-    <t>RedeployPolicy</t>
-  </si>
-  <si>
-    <t>BuildCountLimit</t>
-  </si>
-  <si>
-    <t>Hatred</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>HitPointName</t>
-  </si>
-  <si>
-    <t>Skills</t>
-  </si>
-  <si>
-    <t>MainSkill</t>
-  </si>
-  <si>
-    <t>HpBarType</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>CanSetPos</t>
-  </si>
-  <si>
-    <t>StopCount</t>
-  </si>
-  <si>
-    <t>LeaveReturn</t>
-  </si>
-  <si>
-    <t>NotUseTile</t>
-  </si>
-  <si>
-    <t>#敌人用</t>
-  </si>
-  <si>
-    <t>HpRecover</t>
-  </si>
-  <si>
-    <t>WithoutCheckCount</t>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
-    <t>IgnoreBuff</t>
-  </si>
-  <si>
-    <t>Radius</t>
-  </si>
-  <si>
-    <t>Size</t>
-  </si>
-  <si>
-    <t>CanStop</t>
-  </si>
-  <si>
-    <t>StopAttackOnly</t>
-  </si>
-  <si>
-    <t>LifeTime</t>
-  </si>
-  <si>
-    <t>Profession</t>
-  </si>
-  <si>
-    <t>Profession2</t>
-  </si>
-  <si>
-    <t>HeadIcon</t>
-  </si>
-  <si>
-    <t>HalfIcon</t>
-  </si>
-  <si>
-    <t>StandPic</t>
-  </si>
-  <si>
-    <t>StandPicPos</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>SetPos</t>
-  </si>
-  <si>
-    <t>Tags</t>
-  </si>
-  <si>
-    <t>AblitityInfo</t>
-  </si>
-  <si>
-    <t>Ablititys</t>
-  </si>
-  <si>
-    <t>DefaultAnimation</t>
-  </si>
-  <si>
-    <t>IdleAnimation</t>
-  </si>
-  <si>
-    <t>MoveAnimation</t>
-  </si>
-  <si>
-    <t>DeadAnimation</t>
-  </si>
-  <si>
-    <t>StunAnimation</t>
-  </si>
-  <si>
-    <t>ForwardAnimation</t>
-  </si>
-  <si>
-    <t>MaxAnimationScale</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>SkillData[]</t>
-  </si>
-  <si>
-    <t>string[]</t>
-  </si>
-  <si>
-    <t>BuffData[]</t>
-  </si>
-  <si>
-    <t>UnityEngine.Vector2Int</t>
-  </si>
-  <si>
-    <t>UnitTypeEnum</t>
-  </si>
-  <si>
-    <t>float[]</t>
-  </si>
-  <si>
-    <t>System.Collections.Generic.Dictionary&lt;string,object&gt;</t>
-  </si>
-  <si>
-    <t>干员</t>
-  </si>
-  <si>
-    <t>hamoni</t>
-  </si>
-  <si>
-    <t>Hip</t>
-  </si>
-  <si>
-    <t>莫菲丝攻击,莫菲丝入场,莫菲丝死亡倒计时</t>
-  </si>
-  <si>
-    <t>莫菲丝1,莫菲丝2,莫菲丝3</t>
-  </si>
-  <si>
-    <t>高台位</t>
-  </si>
-  <si>
-    <t>辅助</t>
-  </si>
-  <si>
-    <t>削弱者</t>
-  </si>
-  <si>
-    <t>icon_morphis</t>
-  </si>
-  <si>
-    <t>half_hamoni</t>
-  </si>
-  <si>
-    <t>211,81,1500,1500</t>
-  </si>
-  <si>
-    <t>远程位</t>
-  </si>
-  <si>
-    <t>维多利亚,远程</t>
-  </si>
-  <si>
-    <t>攻击造成法术伤害,对目标造成10％虚弱效果，持续2秒</t>
-  </si>
-  <si>
-    <t>{"梦境缠绕":"自身及召唤物可以攻击进入睡眠状态的敌人，且攻击倍率提升至160%，优先攻击自身未攻击过或睡眠中的敌人，自身对每个敌人首次造成伤害的同时，令其进入8秒睡眠。被自身睡眠的敌人法术抗性-100%。若睡眠失败或被打断睡眠则改为等时长的束缚，期间其法术抗性-40%","意识脱离":"攻击范围内敌人濒死或生命值低于自身攻击力150%时，令其进入意识脱离状态，持续10秒，期间目标获得无敌，不可移动与攻击，不可被阻挡，场上不存在卡尔顿时，选择一个处于意识脱离状态的敌人所在格部署卡尔顿，卡尔顿所在格及周围八格的敌人攻击力-40%，移动速度-40%。目标意识脱离状态结束后将其击杀，且自身攻击范围内所有干员回复2点技力"}</t>
-  </si>
-  <si>
-    <t>B_Default</t>
-  </si>
-  <si>
-    <t>B_Idle</t>
-  </si>
-  <si>
-    <t>B_Die</t>
-  </si>
-  <si>
-    <t>mjcgst</t>
-  </si>
-  <si>
-    <t>沃尔夫攻击,通用绝食</t>
-  </si>
-  <si>
-    <t>沃尔夫描述</t>
-  </si>
-  <si>
-    <t>召唤物</t>
-  </si>
-  <si>
-    <t>icon_wolf</t>
-  </si>
-  <si>
-    <t>召唤物,远程</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>Idle</t>
-  </si>
-  <si>
-    <t>Die</t>
-  </si>
-  <si>
     <t>mjcbat</t>
   </si>
   <si>
@@ -2236,9 +2263,6 @@
     <t>ForwordDirection</t>
   </si>
   <si>
-    <t>UnityEngine.Vector3</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -2327,41 +2351,14 @@
   </si>
   <si>
     <t>/Spine/卡尔顿/enemy_10106_mjcbat.skel.bytes</t>
-  </si>
-  <si>
-    <t>血条</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>技力条</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpBarType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小型:蓝</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小型:绿</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小型:橙</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2373,34 +2370,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2436,19 +2405,19 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2760,11 +2729,11 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="3" width="9" customWidth="1" style="1"/>
+    <col min="4" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2772,7 +2741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2780,7 +2749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -2791,1018 +2760,1254 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BU7"/>
+  <dimension ref="A1:BV7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.58203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.25" style="1" customWidth="1"/>
-    <col min="8" max="10" width="9" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="4" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.75" style="1" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" style="1" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" style="1" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10.25" style="1" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.75" style="1" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="10.75" style="1" customWidth="1"/>
-    <col min="27" max="28" width="9" style="1" customWidth="1"/>
-    <col min="29" max="29" width="8" style="1" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" style="1" customWidth="1"/>
-    <col min="31" max="32" width="9" style="1" customWidth="1"/>
-    <col min="33" max="33" width="9.75" style="1" customWidth="1"/>
-    <col min="34" max="34" width="7.83203125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="15.83203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="13.83203125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="34.5" style="1" customWidth="1"/>
-    <col min="38" max="40" width="9.83203125" style="1" customWidth="1"/>
-    <col min="41" max="44" width="9" style="1" customWidth="1"/>
-    <col min="45" max="45" width="12.5" style="1" customWidth="1"/>
-    <col min="46" max="51" width="9" style="1" customWidth="1"/>
-    <col min="52" max="52" width="24.33203125" style="1" customWidth="1"/>
-    <col min="53" max="53" width="9" style="1" customWidth="1"/>
-    <col min="54" max="54" width="17.75" style="1" customWidth="1"/>
-    <col min="55" max="55" width="7.83203125" style="1" customWidth="1"/>
-    <col min="56" max="57" width="9" style="1" customWidth="1"/>
-    <col min="58" max="58" width="24.25" style="1" customWidth="1"/>
-    <col min="59" max="59" width="13.25" style="1" customWidth="1"/>
-    <col min="60" max="60" width="16.08203125" style="1" customWidth="1"/>
-    <col min="61" max="61" width="8" style="1" customWidth="1"/>
-    <col min="62" max="63" width="9" style="1" customWidth="1"/>
-    <col min="64" max="64" width="27.33203125" style="1" customWidth="1"/>
-    <col min="65" max="65" width="9" style="1" customWidth="1"/>
-    <col min="66" max="66" width="39.58203125" style="1" customWidth="1"/>
-    <col min="67" max="67" width="14" style="1" customWidth="1"/>
-    <col min="68" max="68" width="14.83203125" style="1" customWidth="1"/>
-    <col min="69" max="72" width="14" style="1" customWidth="1"/>
-    <col min="73" max="73" width="19.1640625" style="1" customWidth="1"/>
-    <col min="74" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
+    <col min="8" max="8" width="9" customWidth="1" style="2"/>
+    <col min="9" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="9" customWidth="1" style="2"/>
+    <col min="11" max="11" width="9" customWidth="1" style="2"/>
+    <col min="12" max="12" width="6" customWidth="1" style="2"/>
+    <col min="13" max="13" width="5.5" customWidth="1" style="2"/>
+    <col min="14" max="14" width="5.58203125" customWidth="1" style="2"/>
+    <col min="15" max="15" width="4" customWidth="1" style="2"/>
+    <col min="16" max="16" width="7.75" customWidth="1" style="2"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1" style="2"/>
+    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="3.83203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="3.58203125" customWidth="1" style="2"/>
+    <col min="22" max="22" width="10.25" customWidth="1" style="2"/>
+    <col min="23" max="23" width="9.58203125" customWidth="1" style="2"/>
+    <col min="24" max="24" width="10.75" customWidth="1" style="2"/>
+    <col min="25" max="25" width="12.83203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="13.08203125" customWidth="1" style="2"/>
+    <col min="27" max="27" width="10.75" customWidth="1" style="2"/>
+    <col min="28" max="28" width="9" customWidth="1" style="2"/>
+    <col min="29" max="29" width="9" customWidth="1" style="2"/>
+    <col min="30" max="30" width="8" customWidth="1" style="2"/>
+    <col min="31" max="31" width="17.08203125" customWidth="1" style="2"/>
+    <col min="32" max="32" width="9" customWidth="1" style="2"/>
+    <col min="33" max="33" width="9" customWidth="1" style="2"/>
+    <col min="34" max="34" width="9.75" customWidth="1" style="2"/>
+    <col min="35" max="35" width="7.83203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="15.83203125" customWidth="1" style="2"/>
+    <col min="37" max="37" width="13.83203125" customWidth="1" style="2"/>
+    <col min="38" max="38" width="34.5" customWidth="1" style="2"/>
+    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="9.83203125" customWidth="1" style="2"/>
+    <col min="41" max="41" width="9.83203125" customWidth="1" style="2"/>
+    <col min="42" max="42" width="9" customWidth="1" style="2"/>
+    <col min="43" max="43" width="9" customWidth="1" style="2"/>
+    <col min="44" max="44" width="9" customWidth="1" style="2"/>
+    <col min="45" max="45" width="9" customWidth="1" style="2"/>
+    <col min="46" max="46" width="12.5" customWidth="1" style="2"/>
+    <col min="47" max="47" width="9" customWidth="1" style="2"/>
+    <col min="48" max="48" width="9" customWidth="1" style="2"/>
+    <col min="49" max="49" width="9" customWidth="1" style="2"/>
+    <col min="50" max="50" width="9" customWidth="1" style="2"/>
+    <col min="51" max="51" width="9" customWidth="1" style="2"/>
+    <col min="52" max="52" width="9" customWidth="1" style="2"/>
+    <col min="53" max="53" width="24.33203125" customWidth="1" style="2"/>
+    <col min="54" max="54" width="9" customWidth="1" style="2"/>
+    <col min="55" max="55" width="17.75" customWidth="1" style="2"/>
+    <col min="56" max="56" width="7.83203125" customWidth="1" style="2"/>
+    <col min="57" max="57" width="9" customWidth="1" style="2"/>
+    <col min="58" max="58" width="9" customWidth="1" style="2"/>
+    <col min="59" max="59" width="24.25" customWidth="1" style="2"/>
+    <col min="60" max="60" width="13.25" customWidth="1" style="2"/>
+    <col min="61" max="61" width="16.08203125" customWidth="1" style="2"/>
+    <col min="62" max="62" width="8" customWidth="1" style="2"/>
+    <col min="63" max="63" width="9" customWidth="1" style="2"/>
+    <col min="64" max="64" width="9" customWidth="1" style="2"/>
+    <col min="65" max="65" width="27.33203125" customWidth="1" style="2"/>
+    <col min="66" max="66" width="9" customWidth="1" style="2"/>
+    <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
+    <col min="68" max="68" width="14" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="71" max="71" width="14" customWidth="1" style="2"/>
+    <col min="72" max="72" width="14" customWidth="1" style="2"/>
+    <col min="73" max="73" width="14" customWidth="1" style="2"/>
+    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="D1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AT1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU1" s="2"/>
+      <c r="AV1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AY1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="BB1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="BC1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="BD1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BE1" s="2"/>
+      <c r="BF1" s="2"/>
+      <c r="BG1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="BH1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="BI1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="BJ1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="BK1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2"/>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+      <c r="BU1" s="2"/>
+      <c r="BV1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BD2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BI2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BK2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BP2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BV2" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AU3" s="2"/>
+      <c r="AV3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2"/>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2"/>
+      <c r="BA4" s="2"/>
+      <c r="BB4" s="2"/>
+      <c r="BC4" s="2"/>
+      <c r="BD4" s="2"/>
+      <c r="BE4" s="2"/>
+      <c r="BF4" s="2"/>
+      <c r="BG4" s="2"/>
+      <c r="BH4" s="2"/>
+      <c r="BI4" s="2"/>
+      <c r="BJ4" s="2"/>
+      <c r="BK4" s="2"/>
+      <c r="BL4" s="2"/>
+      <c r="BM4" s="2"/>
+      <c r="BN4" s="2"/>
+      <c r="BO4" s="2"/>
+      <c r="BP4" s="2"/>
+      <c r="BQ4" s="2"/>
+      <c r="BR4" s="2"/>
+      <c r="BS4" s="2"/>
+      <c r="BT4" s="2"/>
+      <c r="BU4" s="2"/>
+      <c r="BV4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
+        <v>2</v>
+      </c>
+      <c r="K5" s="2">
+        <v>90</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1950</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2">
+        <v>605</v>
+      </c>
+      <c r="O5" s="2">
+        <v>90</v>
+      </c>
+      <c r="P5" s="2">
+        <v>125</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2">
+        <v>25</v>
+      </c>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2">
+        <v>13</v>
+      </c>
+      <c r="U5" s="2">
+        <v>-2</v>
+      </c>
+      <c r="V5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="W5" s="2">
+        <v>70</v>
+      </c>
+      <c r="X5" s="2">
+        <v>-4</v>
+      </c>
+      <c r="Y5" s="2">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="Z5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AR5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2"/>
+      <c r="AW5" s="2"/>
+      <c r="AX5" s="2"/>
+      <c r="AY5" s="2"/>
+      <c r="AZ5" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="BA5" s="2"/>
+      <c r="BB5" s="2"/>
+      <c r="BC5" s="2"/>
+      <c r="BD5" s="2"/>
+      <c r="BE5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BK5" s="2">
+        <v>6</v>
+      </c>
+      <c r="BL5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BN5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BP5" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BR5" s="2"/>
+      <c r="BS5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BT5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BU5" s="2"/>
+      <c r="BV5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2">
+        <v>90</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1500</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2">
+        <v>520</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2">
+        <v>115</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2">
+        <v>50</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="W6" s="2">
+        <v>25</v>
+      </c>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2"/>
+      <c r="AJ6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AO6" s="2"/>
+      <c r="AP6" s="2"/>
+      <c r="AQ6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AR6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AT6" s="2"/>
+      <c r="AU6" s="2"/>
+      <c r="AV6" s="2"/>
+      <c r="AW6" s="2"/>
+      <c r="AX6" s="2"/>
+      <c r="AY6" s="2"/>
+      <c r="AZ6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="BA6" s="2"/>
+      <c r="BB6" s="2"/>
+      <c r="BC6" s="2"/>
+      <c r="BD6" s="2"/>
+      <c r="BE6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BF6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BG6" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="BH6" s="2"/>
+      <c r="BI6" s="2"/>
+      <c r="BJ6" s="2"/>
+      <c r="BK6" s="2">
+        <v>6</v>
+      </c>
+      <c r="BL6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="BM6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="BN6" s="2"/>
+      <c r="BO6" s="2"/>
+      <c r="BP6" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="BQ6" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="BR6" s="2"/>
+      <c r="BS6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BT6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BU6" s="2"/>
+      <c r="BV6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2">
+        <v>2</v>
+      </c>
+      <c r="K7" s="2">
+        <v>90</v>
+      </c>
+      <c r="L7" s="2">
+        <v>100</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
+        <v>175</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AM1" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="AN1" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AU2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AW2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AX2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="BB2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="BD2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="BE2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="BF2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="BG2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="BH2" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="BI2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="BJ2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="BK2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="BO2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="BP2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="BQ2" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="BR2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="BS2" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="BT2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU2" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AL3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="AO3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AP3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AQ3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AR3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AS3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AU3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AV3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AW3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AX3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="AY3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AZ3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="BA3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BB3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BD3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BI3" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="BJ3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BK3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BL3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BM3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BN3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="BO3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BP3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BQ3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BT3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BU3" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1">
-        <v>90</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1950</v>
-      </c>
-      <c r="M5" s="1">
-        <v>605</v>
-      </c>
-      <c r="N5" s="1">
-        <v>90</v>
-      </c>
-      <c r="O5" s="1">
-        <v>125</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>25</v>
-      </c>
-      <c r="S5" s="1">
-        <v>13</v>
-      </c>
-      <c r="T5" s="1">
-        <v>-2</v>
-      </c>
-      <c r="U5" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="V5" s="1">
-        <v>70</v>
-      </c>
-      <c r="W5" s="1">
-        <v>-4</v>
-      </c>
-      <c r="X5" s="1">
-        <v>7</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ5" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL5" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM5" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="AN5" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="AP5" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AQ5" s="1">
-        <v>1</v>
-      </c>
-      <c r="AR5" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="AY5" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="BD5" s="1" t="s">
+      <c r="AE7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="2"/>
+      <c r="AG7" s="2"/>
+      <c r="AH7" s="2"/>
+      <c r="AI7" s="2"/>
+      <c r="AJ7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="AK7" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="BE5" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="BF5" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="BG5" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="BH5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="BI5" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="BJ5" s="1">
+      <c r="AL7" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AO7" s="2"/>
+      <c r="AP7" s="2"/>
+      <c r="AQ7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="AR7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="2"/>
+      <c r="AU7" s="2"/>
+      <c r="AV7" s="2"/>
+      <c r="AW7" s="2"/>
+      <c r="AX7" s="2"/>
+      <c r="AY7" s="2"/>
+      <c r="AZ7" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="2"/>
+      <c r="BB7" s="2"/>
+      <c r="BC7" s="2"/>
+      <c r="BD7" s="2"/>
+      <c r="BE7" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BF7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BG7" s="2"/>
+      <c r="BH7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BI7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="BJ7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BK7" s="2">
         <v>6</v>
       </c>
-      <c r="BK5" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="BL5" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="BM5" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="BN5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BO5" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="BP5" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="BR5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="BS5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="BU5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>90</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1500</v>
-      </c>
-      <c r="M6" s="1">
-        <v>520</v>
-      </c>
-      <c r="O6" s="1">
-        <v>115</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>50</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
-      <c r="U6" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="V6" s="1">
-        <v>25</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK6" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL6" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM6" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="AP6" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AQ6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AR6" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="AY6" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="BD6" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE6" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="BF6" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="BJ6" s="1">
-        <v>6</v>
-      </c>
-      <c r="BK6" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="BL6" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BO6" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BP6" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BR6" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="BS6" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="BU6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
-        <v>2</v>
-      </c>
-      <c r="J7" s="1">
-        <v>90</v>
-      </c>
-      <c r="K7" s="1">
-        <v>100</v>
-      </c>
-      <c r="M7" s="1">
-        <v>175</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1">
-        <v>10</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK7" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AL7" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AM7" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="AP7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="AQ7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY7" s="1">
-        <v>0</v>
-      </c>
-      <c r="BD7" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE7" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="BG7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="BH7" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="BI7" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="BJ7" s="1">
-        <v>6</v>
-      </c>
-      <c r="BK7" s="1" t="s">
+      <c r="BL7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BM7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="BN7" s="2"/>
+      <c r="BO7" s="2"/>
+      <c r="BP7" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="BL7" s="1" t="s">
+      <c r="BQ7" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="BO7" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BP7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BR7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="BS7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="BU7" s="1">
+      <c r="BR7" s="2"/>
+      <c r="BS7" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BT7" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BU7" s="2"/>
+      <c r="BV7" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3810,6 +4015,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3819,770 +4025,770 @@
   <dimension ref="A1:DI59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" style="1" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="21.5" style="1" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="19.08203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="17.75" style="1" customWidth="1"/>
-    <col min="23" max="23" width="8.33203125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="18.5" style="1" customWidth="1"/>
-    <col min="25" max="25" width="16.58203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" style="1" customWidth="1"/>
-    <col min="29" max="30" width="8.58203125" style="1" customWidth="1"/>
-    <col min="31" max="31" width="13.4140625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="13.75" style="1" customWidth="1"/>
-    <col min="33" max="33" width="14.58203125" style="1" customWidth="1"/>
-    <col min="34" max="34" width="17.4140625" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5" style="1" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" style="1" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" style="1" customWidth="1"/>
-    <col min="40" max="40" width="15" style="1" customWidth="1"/>
-    <col min="41" max="41" width="13.25" style="1" customWidth="1"/>
-    <col min="42" max="45" width="11.83203125" style="1" customWidth="1"/>
-    <col min="46" max="46" width="18.4140625" style="1" customWidth="1"/>
-    <col min="47" max="47" width="12.25" style="1" customWidth="1"/>
-    <col min="48" max="48" width="11.9140625" style="1" customWidth="1"/>
-    <col min="49" max="49" width="19.58203125" style="1" customWidth="1"/>
-    <col min="50" max="50" width="12.6640625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="9" style="1" customWidth="1"/>
-    <col min="52" max="52" width="7" style="1" customWidth="1"/>
-    <col min="53" max="53" width="11.75" style="1" customWidth="1"/>
-    <col min="54" max="54" width="19.75" style="1" customWidth="1"/>
-    <col min="55" max="55" width="5.08203125" style="1" customWidth="1"/>
-    <col min="56" max="56" width="8.5" style="1" customWidth="1"/>
-    <col min="57" max="57" width="13.5" style="1" customWidth="1"/>
-    <col min="58" max="58" width="14.6640625" style="1" customWidth="1"/>
-    <col min="59" max="59" width="10.1640625" style="1" customWidth="1"/>
-    <col min="60" max="60" width="8.25" style="1" customWidth="1"/>
-    <col min="61" max="66" width="8.33203125" style="1" customWidth="1"/>
-    <col min="67" max="67" width="19.25" style="1" customWidth="1"/>
-    <col min="68" max="68" width="22.33203125" style="1" customWidth="1"/>
-    <col min="69" max="70" width="11.25" style="1" customWidth="1"/>
-    <col min="71" max="71" width="6.58203125" style="1" customWidth="1"/>
-    <col min="72" max="73" width="8" style="1" customWidth="1"/>
-    <col min="74" max="74" width="7.33203125" style="1" customWidth="1"/>
-    <col min="75" max="76" width="8.5" style="1" customWidth="1"/>
-    <col min="77" max="78" width="7.83203125" style="1" customWidth="1"/>
-    <col min="79" max="79" width="22.1640625" style="1" customWidth="1"/>
-    <col min="80" max="80" width="35" style="1" customWidth="1"/>
-    <col min="81" max="81" width="20.6640625" style="1" customWidth="1"/>
-    <col min="82" max="82" width="15.75" style="1" customWidth="1"/>
-    <col min="83" max="83" width="15.58203125" style="1" customWidth="1"/>
-    <col min="84" max="84" width="12.83203125" style="1" customWidth="1"/>
-    <col min="85" max="85" width="16.1640625" style="1" customWidth="1"/>
-    <col min="86" max="86" width="9" style="1" customWidth="1"/>
-    <col min="87" max="87" width="16" style="1" customWidth="1"/>
-    <col min="88" max="89" width="12.83203125" style="1" customWidth="1"/>
-    <col min="90" max="90" width="23.58203125" style="1" customWidth="1"/>
-    <col min="91" max="91" width="12.83203125" style="1" customWidth="1"/>
-    <col min="92" max="92" width="25.9140625" style="1" customWidth="1"/>
-    <col min="93" max="93" width="9.5" style="1" customWidth="1"/>
-    <col min="94" max="98" width="9" style="1" customWidth="1"/>
-    <col min="99" max="99" width="14" style="1" customWidth="1"/>
-    <col min="100" max="100" width="8" style="1" customWidth="1"/>
-    <col min="101" max="101" width="9" style="1" customWidth="1"/>
-    <col min="102" max="102" width="11.08203125" style="1" customWidth="1"/>
-    <col min="103" max="103" width="13.75" style="1" customWidth="1"/>
-    <col min="104" max="104" width="9.5" style="1" customWidth="1"/>
-    <col min="105" max="106" width="9" style="1" customWidth="1"/>
-    <col min="107" max="108" width="9.5" style="1" customWidth="1"/>
-    <col min="109" max="109" width="9" style="1" customWidth="1"/>
-    <col min="110" max="110" width="15.5" style="1" customWidth="1"/>
-    <col min="111" max="111" width="9" style="1" customWidth="1"/>
-    <col min="112" max="113" width="9.5" style="1" customWidth="1"/>
-    <col min="114" max="114" width="9" style="1" customWidth="1"/>
-    <col min="115" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1" style="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1" style="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="1"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="1"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="1"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="1"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="1"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="1"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="1"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="1"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="1"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="1"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="1"/>
+    <col min="40" max="40" width="15" customWidth="1" style="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="1"/>
+    <col min="51" max="51" width="9" customWidth="1" style="1"/>
+    <col min="52" max="52" width="7" customWidth="1" style="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="1"/>
+    <col min="61" max="66" width="8.33203125" customWidth="1" style="1"/>
+    <col min="67" max="67" width="19.25" customWidth="1" style="1"/>
+    <col min="68" max="68" width="22.33203125" customWidth="1" style="1"/>
+    <col min="69" max="70" width="11.25" customWidth="1" style="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="1"/>
+    <col min="72" max="73" width="8" customWidth="1" style="1"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="1"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="1"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="1"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="1"/>
+    <col min="80" max="80" width="35" customWidth="1" style="1"/>
+    <col min="81" max="81" width="20.6640625" customWidth="1" style="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="1"/>
+    <col min="86" max="86" width="9" customWidth="1" style="1"/>
+    <col min="87" max="87" width="16" customWidth="1" style="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="1"/>
+    <col min="92" max="92" width="25.9140625" customWidth="1" style="1"/>
+    <col min="93" max="93" width="9.5" customWidth="1" style="1"/>
+    <col min="94" max="98" width="9" customWidth="1" style="1"/>
+    <col min="99" max="99" width="14" customWidth="1" style="1"/>
+    <col min="100" max="100" width="8" customWidth="1" style="1"/>
+    <col min="101" max="101" width="9" customWidth="1" style="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="1"/>
+    <col min="104" max="104" width="9.5" customWidth="1" style="1"/>
+    <col min="105" max="106" width="9" customWidth="1" style="1"/>
+    <col min="107" max="108" width="9.5" customWidth="1" style="1"/>
+    <col min="109" max="109" width="9" customWidth="1" style="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="1"/>
+    <col min="111" max="111" width="9" customWidth="1" style="1"/>
+    <col min="112" max="113" width="9.5" customWidth="1" style="1"/>
+    <col min="114" max="114" width="9" customWidth="1" style="1"/>
+    <col min="115" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="B1" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="CC1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="CR1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="CD1" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="CS1" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="BT2" s="1" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="BU2" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="CB2" s="1" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="CC2" s="1" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="CD2" s="1" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="CE2" s="1" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="CF2" s="1" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="CG2" s="1" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="CH2" s="1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="CI2" s="1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="CJ2" s="1" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="CK2" s="1" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="CL2" s="1" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="CM2" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="CN2" s="1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="CO2" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="CP2" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="CQ2" s="1" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="CR2" s="1" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="CS2" s="1" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="CT2" s="1" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="CU2" s="1" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="CV2" s="1" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="CW2" s="1" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="CX2" s="1" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="CY2" s="1" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="CZ2" s="1" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="DA2" s="1" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="DB2" s="1" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="DC2" s="1" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="DD2" s="1" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="DE2" s="1" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="DF2" s="1" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="DG2" s="1" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="DH2" s="1" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="DI2" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4599,112 +4805,112 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AJ3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="AQ3" s="1" t="s">
         <v>2</v>
@@ -4716,222 +4922,222 @@
         <v>2</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="AU3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AV3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="AY3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AZ3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BA3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="BB3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BC3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BD3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BF3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BG3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="BH3" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="BI3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="BJ3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BK3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BL3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BM3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BN3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BO3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BP3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BQ3" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="BS3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BT3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BU3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="BP3" s="1" t="s">
+      <c r="BV3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BW3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="BY3" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="BZ3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="BQ3" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BT3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BV3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BW3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BX3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BY3" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="BZ3" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="CA3" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="CB3" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="CC3" s="1" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="CD3" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="CE3" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="CF3" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="CG3" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="CH3" s="1" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="CI3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" s="1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="CK3" s="1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="CL3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="CM3" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="CM3" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="CN3" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="CO3" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="CP3" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="CQ3" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="CR3" s="1" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="CS3" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="CT3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="CU3" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="CV3" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="CW3" s="1" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="CX3" s="1" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="CY3" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="CZ3" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="DA3" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="DB3" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="DC3" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="DD3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="DE3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="DF3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="DG3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="DH3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="DI3" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="AC5" s="1">
         <v>2</v>
@@ -4940,13 +5146,13 @@
         <v>1</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="AT5" s="1" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="AX5" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="AZ5" s="1">
         <v>1</v>
@@ -4955,25 +5161,25 @@
         <v>1</v>
       </c>
       <c r="BO5" s="1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="CB5" s="1" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="CG5" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CH5" s="1" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="CI5" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="CJ5" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="CN5" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="CO5" s="1">
         <v>-0.1</v>
@@ -4982,66 +5188,66 @@
         <v>2</v>
       </c>
       <c r="CW5" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="CY5" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="DG5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT6" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="CY5" s="1" t="s">
+      <c r="AX6" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="DG5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="Q6" s="1" t="s">
+      <c r="AZ6" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD6" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB6" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="AC6" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="AT6" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="AX6" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="AZ6" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD6" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB6" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="CG6" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CH6" s="1" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="CI6" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="CJ6" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="CN6" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="CO6" s="1">
         <v>-0.1</v>
@@ -5050,66 +5256,66 @@
         <v>2</v>
       </c>
       <c r="CW6" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="CY6" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="DG6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT7" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="CY6" s="1" t="s">
+      <c r="AX7" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="DG6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="AZ7" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB7" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="CG7" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="AT7" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="AX7" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="AZ7" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD7" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB7" s="1" t="s">
+      <c r="CH7" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="CG7" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="CH7" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="CI7" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="CJ7" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="CN7" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="CO7" s="1">
         <v>-0.1</v>
@@ -5118,30 +5324,30 @@
         <v>8</v>
       </c>
       <c r="CW7" s="1" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="CY7" s="1" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="DG7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" s="1" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="AC8" s="1">
         <v>2</v>
@@ -5156,7 +5362,7 @@
         <v>99</v>
       </c>
       <c r="CN8" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="CR8" s="1">
         <v>99999</v>
@@ -5165,21 +5371,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="AC9" s="1">
         <v>2</v>
@@ -5194,7 +5400,7 @@
         <v>99</v>
       </c>
       <c r="CN9" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="CO9" s="1">
         <v>-0.1</v>
@@ -5206,21 +5412,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" s="1" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="AC10" s="1">
         <v>2</v>
@@ -5238,10 +5444,10 @@
         <v>0.1</v>
       </c>
       <c r="CN10" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="CO10" s="1" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="CR10" s="1">
         <v>0.2</v>
@@ -5250,24 +5456,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" s="1" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="AC11" s="1">
         <v>2</v>
@@ -5285,10 +5491,10 @@
         <v>0.1</v>
       </c>
       <c r="CN11" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="CO11" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="CR11" s="1">
         <v>0.2</v>
@@ -5297,21 +5503,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" s="1" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="AC12" s="1">
         <v>2</v>
@@ -5329,7 +5535,7 @@
         <v>0.1</v>
       </c>
       <c r="CN12" s="1" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="CR12" s="1">
         <v>0.2</v>
@@ -5338,21 +5544,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" s="1" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="AC13" s="1">
         <v>2</v>
@@ -5367,10 +5573,10 @@
         <v>1</v>
       </c>
       <c r="BO13" s="1" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="CN13" s="1" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="CR13" s="1">
         <v>10</v>
@@ -5379,21 +5585,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" s="1" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="AC14" s="1">
         <v>2</v>
@@ -5408,7 +5614,7 @@
         <v>1</v>
       </c>
       <c r="CN14" s="1" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="CR14" s="1">
         <v>10</v>
@@ -5417,18 +5623,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" s="1" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="AC15" s="1">
         <v>2</v>
@@ -5446,7 +5652,7 @@
         <v>0.1</v>
       </c>
       <c r="CN15" s="1" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="CR15" s="1">
         <v>0.2</v>
@@ -5455,21 +5661,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" s="1" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="AC16" s="1">
         <v>2</v>
@@ -5484,16 +5690,16 @@
         <v>99</v>
       </c>
       <c r="BO16" s="1" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="BP16" s="1" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="CM16" s="1" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="CN16" s="1" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="CR16" s="1">
         <v>10.1</v>
@@ -5502,21 +5708,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" s="1" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="AC17" s="1">
         <v>2</v>
@@ -5531,13 +5737,13 @@
         <v>99</v>
       </c>
       <c r="BP17" s="1" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="CM17" s="1" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="CN17" s="1" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="CR17" s="1">
         <v>99999</v>
@@ -5546,21 +5752,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" s="1" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="AC18" s="1">
         <v>2</v>
@@ -5575,7 +5781,7 @@
         <v>1</v>
       </c>
       <c r="BP18" s="1" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="BS18" s="1">
         <v>1</v>
@@ -5590,50 +5796,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" s="1" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="AC19" s="1">
         <v>1</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="BD19" s="1">
         <v>1</v>
       </c>
       <c r="BO19" s="1" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="CU19" s="1" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="DI19" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" s="1" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="AC20" s="1">
         <v>2</v>
@@ -5660,12 +5866,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" s="1" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
@@ -5674,7 +5880,7 @@
         <v>1</v>
       </c>
       <c r="AJ21" s="1" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="AV21" s="1">
         <v>20</v>
@@ -5683,7 +5889,7 @@
         <v>99</v>
       </c>
       <c r="BP21" s="1" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="BS21" s="1">
         <v>0.1</v>
@@ -5695,33 +5901,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="AC22" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="BD22" s="1">
+        <v>1</v>
+      </c>
+      <c r="CN22" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="AC22" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="BD22" s="1">
-        <v>1</v>
-      </c>
-      <c r="CN22" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="CR22" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="DH22" s="1">
         <v>1</v>
@@ -5730,39 +5936,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" s="1" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I23" s="1">
         <v>1</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="AC23" s="1">
         <v>1</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="BD23" s="1">
         <v>1</v>
       </c>
       <c r="CB23" s="1" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="CG23" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CN23" s="1" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="CO23" s="1">
         <v>0.15</v>
@@ -5771,21 +5977,21 @@
         <v>99999</v>
       </c>
     </row>
-    <row r="24" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" s="1" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="AC24" s="1">
         <v>2</v>
@@ -5800,16 +6006,16 @@
         <v>99</v>
       </c>
       <c r="BO24" s="1" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="BP24" s="1" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="CM24" s="1" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="CN24" s="1" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="CR24" s="1">
         <v>99999</v>
@@ -5821,18 +6027,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" s="1" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="AC25" s="1">
         <v>1</v>
@@ -5844,24 +6050,24 @@
         <v>99</v>
       </c>
       <c r="CU25" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="26" spans="1:113" x14ac:dyDescent="0.25">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" s="1" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I26" s="1">
         <v>1</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="AC26" s="1">
         <v>2</v>
@@ -5873,7 +6079,7 @@
         <v>20</v>
       </c>
       <c r="AX26" s="1" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="AZ26" s="1">
         <v>9999999</v>
@@ -5885,10 +6091,10 @@
         <v>99</v>
       </c>
       <c r="CM26" s="1" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="CN26" s="1" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="CR26" s="1">
         <v>99999</v>
@@ -5900,45 +6106,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" s="1" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="AC27" s="1">
         <v>1</v>
       </c>
       <c r="AG27" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="BD27" s="1">
         <v>1</v>
       </c>
       <c r="BO27" s="1" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="BP27" s="1" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="BT27" s="1">
         <v>0.2</v>
@@ -5953,16 +6159,16 @@
         <v>2</v>
       </c>
       <c r="BY27" s="1" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="CB27" s="1" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="CG27" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CN27" s="1" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="CO27" s="1">
         <v>0.08</v>
@@ -5971,15 +6177,15 @@
         <v>99999</v>
       </c>
     </row>
-    <row r="28" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" s="1" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="AC28" s="1">
         <v>2</v>
@@ -5988,16 +6194,16 @@
         <v>1</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="AR28" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="AW28" s="1">
         <v>1</v>
       </c>
       <c r="AX28" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="AZ28" s="1">
         <v>1.6</v>
@@ -6006,48 +6212,48 @@
         <v>2</v>
       </c>
       <c r="CG28" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CH28" s="1" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="CI28" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="CJ28" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="CN28" s="1" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="CR28" s="1">
         <v>5</v>
       </c>
       <c r="CW28" s="1" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="CY28" s="1" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="DG28" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" s="1" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="AC29" s="1">
         <v>2</v>
@@ -6062,7 +6268,7 @@
         <v>99</v>
       </c>
       <c r="CN29" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="CO29" s="1">
         <v>-0.1</v>
@@ -6074,30 +6280,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" s="1" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="G30" s="1">
         <v>3</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="AB30" s="1">
         <v>1</v>
@@ -6106,13 +6312,13 @@
         <v>1</v>
       </c>
       <c r="AG30" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="BD30" s="1">
         <v>1</v>
       </c>
       <c r="BO30" s="1" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="BT30" s="1">
         <v>15</v>
@@ -6127,33 +6333,33 @@
         <v>1</v>
       </c>
       <c r="BY30" s="1" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="CB30" s="1" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="CG30" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CM30" s="1" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="CN30" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="CR30" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" s="1" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="AC31" s="1">
         <v>2</v>
@@ -6162,13 +6368,13 @@
         <v>1</v>
       </c>
       <c r="AO31" s="1" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="AT31" s="1" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="AX31" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="AZ31" s="1">
         <v>1.2</v>
@@ -6177,7 +6383,7 @@
         <v>1</v>
       </c>
       <c r="BJ31" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="BK31" s="1">
         <v>1</v>
@@ -6189,16 +6395,16 @@
         <v>1</v>
       </c>
       <c r="CH31" s="1" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="CI31" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="CJ31" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="CN31" s="1" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="CO31" s="1">
         <v>-0.1</v>
@@ -6210,27 +6416,27 @@
         <v>2</v>
       </c>
       <c r="CY31" s="1" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="DG31" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" s="1" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="AC32" s="1">
         <v>2</v>
@@ -6245,10 +6451,10 @@
         <v>99</v>
       </c>
       <c r="CM32" s="1" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="CN32" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="CR32" s="1">
         <v>2</v>
@@ -6257,74 +6463,74 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" s="1" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I33" s="1">
         <v>1</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="L33" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="AC33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="BD33" s="1">
+        <v>1</v>
+      </c>
+      <c r="BP33" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="CB33" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="CG33" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="CM33" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="CN33" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="AC33" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG33" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="BD33" s="1">
-        <v>1</v>
-      </c>
-      <c r="BP33" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="CB33" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="CG33" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="CM33" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="CN33" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="CR33" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="AC34" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD34" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO34" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="AC34" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD34" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO34" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="AT34" s="1" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="AX34" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="AZ34" s="1">
         <v>3</v>
@@ -6342,13 +6548,13 @@
         <v>1</v>
       </c>
       <c r="CG34" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CJ34" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="CN34" s="1" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="CO34" s="1">
         <v>0.8</v>
@@ -6360,21 +6566,21 @@
         <v>8</v>
       </c>
       <c r="CY34" s="1" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="DG34" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" s="1" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="AC35" s="1">
         <v>2</v>
@@ -6389,27 +6595,27 @@
         <v>99</v>
       </c>
       <c r="CM35" s="1" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="DG35" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" s="1" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I36" s="1">
         <v>1</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="AC36" s="1">
         <v>2</v>
@@ -6427,10 +6633,10 @@
         <v>0.1</v>
       </c>
       <c r="CN36" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="CO36" s="1" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="CR36" s="1">
         <v>0.2</v>
@@ -6439,24 +6645,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" s="1" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="AC37" s="1">
         <v>2</v>
@@ -6474,10 +6680,10 @@
         <v>0.1</v>
       </c>
       <c r="CN37" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="CO37" s="1" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="CR37" s="1">
         <v>0.2</v>
@@ -6486,21 +6692,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" s="1" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="AC38" s="1">
         <v>1</v>
@@ -6509,21 +6715,21 @@
         <v>1</v>
       </c>
       <c r="AG38" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="BD38" s="1">
         <v>1</v>
       </c>
       <c r="CU38" s="1" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="39" spans="1:113" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" s="1" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
@@ -6532,7 +6738,7 @@
         <v>1</v>
       </c>
       <c r="AJ39" s="1" t="s">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="AW39" s="1">
         <v>1</v>
@@ -6544,7 +6750,7 @@
         <v>0.1</v>
       </c>
       <c r="CN39" s="1" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="CR39" s="1">
         <v>0.2</v>
@@ -6553,24 +6759,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" s="1" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="AC40" s="1">
         <v>1</v>
       </c>
       <c r="AJ40" s="1" t="s">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="AV40" s="1">
         <v>20</v>
@@ -6582,7 +6788,7 @@
         <v>0.1</v>
       </c>
       <c r="CN40" s="1" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="CO40" s="1">
         <v>80</v>
@@ -6594,30 +6800,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" s="1" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="AB41" s="1">
         <v>1</v>
@@ -6629,13 +6835,13 @@
         <v>1</v>
       </c>
       <c r="AO41" s="1" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="AT41" s="1" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="AX41" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="AZ41" s="1">
         <v>1</v>
@@ -6644,7 +6850,7 @@
         <v>4</v>
       </c>
       <c r="BO41" s="1" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="BT41" s="1">
         <v>35</v>
@@ -6659,54 +6865,54 @@
         <v>1</v>
       </c>
       <c r="BY41" s="1" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="CB41" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="CE41" s="1" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="CG41" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CH41" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="CI41" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="CJ41" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="CN41" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="CR41" s="1">
+        <v>1</v>
+      </c>
+      <c r="CY41" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="DG41" s="1">
+        <v>1</v>
+      </c>
+      <c r="DI41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="CI41" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="CJ41" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="CN41" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="CR41" s="1">
-        <v>1</v>
-      </c>
-      <c r="CY41" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="DG41" s="1">
-        <v>1</v>
-      </c>
-      <c r="DI41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="K42" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="AC42" s="1">
         <v>1</v>
@@ -6715,10 +6921,10 @@
         <v>1</v>
       </c>
       <c r="BP42" s="1" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="CN42" s="1" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="CO42" s="1">
         <v>-0.8</v>
@@ -6730,15 +6936,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" s="1" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="AC43" s="1">
         <v>2</v>
@@ -6747,13 +6953,13 @@
         <v>1</v>
       </c>
       <c r="AT43" s="1" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="BD43" s="1">
         <v>99</v>
       </c>
       <c r="CN43" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="CR43" s="1">
         <v>15</v>
@@ -6762,15 +6968,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" s="1" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="AC44" s="1">
         <v>2</v>
@@ -6788,10 +6994,10 @@
         <v>0.1</v>
       </c>
       <c r="CN44" s="1" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="CO44" s="1" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="CR44" s="1">
         <v>0.2</v>
@@ -6800,65 +7006,65 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" s="1" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I45" s="1">
         <v>1</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="L45" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="AC45" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG45" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="BD45" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB45" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="CG45" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="CM45" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="CN45" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="AC45" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG45" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="BD45" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB45" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="CG45" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="CM45" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="CN45" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="CR45" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" s="1" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I46" s="1">
         <v>1</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="AC46" s="1">
         <v>1</v>
       </c>
       <c r="AJ46" s="1" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="AV46" s="1">
         <v>20</v>
@@ -6870,7 +7076,7 @@
         <v>0.1</v>
       </c>
       <c r="CN46" s="1" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="CR46" s="1">
         <v>0.2</v>
@@ -6882,21 +7088,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" s="1" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I47" s="1">
         <v>1</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="N47" s="1">
         <v>1</v>
@@ -6905,56 +7111,56 @@
         <v>1</v>
       </c>
       <c r="AG47" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="BD47" s="1">
         <v>1</v>
       </c>
       <c r="CB47" s="1" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="CG47" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="49" spans="1:112" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="I49" s="1">
         <v>1</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="AC49" s="1">
         <v>1</v>
       </c>
       <c r="AG49" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="BD49" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" s="1" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="AC50" s="1">
         <v>2</v>
@@ -6963,16 +7169,16 @@
         <v>1</v>
       </c>
       <c r="AO50" s="1" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="AR50" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="AT50" s="1" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="AX50" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="AZ50" s="1">
         <v>1</v>
@@ -6981,61 +7187,61 @@
         <v>1</v>
       </c>
       <c r="BO50" s="1" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="CB50" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="CG50" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CH50" s="1" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="CI50" s="1" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="CJ50" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="CM50" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="CY50" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="DG50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="AC51" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD51" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO51" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="AR51" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="AT51" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="AX51" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="DG50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="AC51" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD51" s="1">
-        <v>1</v>
-      </c>
-      <c r="AO51" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="AR51" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="AT51" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="AX51" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="AZ51" s="1">
         <v>1</v>
       </c>
@@ -7043,80 +7249,80 @@
         <v>1</v>
       </c>
       <c r="CB51" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="CG51" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CH51" s="1" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="CI51" s="1" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="CJ51" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="CM51" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="CN51" s="1" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="CR51" s="1">
         <v>15</v>
       </c>
       <c r="CY51" s="1" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="DG51" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="I53" s="1">
         <v>1</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="AC53" s="1">
         <v>1</v>
       </c>
       <c r="AG53" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="BD53" s="1">
         <v>1</v>
       </c>
       <c r="CN53" s="1" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="CR53" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="54" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" s="1" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="AC54" s="1">
         <v>2</v>
@@ -7125,16 +7331,16 @@
         <v>1</v>
       </c>
       <c r="AO54" s="1" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="AR54" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="AT54" s="1" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="AX54" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="AZ54" s="1">
         <v>1</v>
@@ -7143,39 +7349,39 @@
         <v>1</v>
       </c>
       <c r="CB54" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="CG54" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CH54" s="1" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="CI54" s="1" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="CJ54" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="CY54" s="1" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="DG54" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" s="1" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I55" s="1">
         <v>1</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="AC55" s="1">
         <v>2</v>
@@ -7184,39 +7390,39 @@
         <v>1</v>
       </c>
       <c r="AT55" s="1" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="BD55" s="1">
         <v>99</v>
       </c>
       <c r="BO55" s="1" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="BS55" s="1">
         <v>0.1</v>
       </c>
       <c r="CN55" s="1" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="CO55" s="1" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="CR55" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="56" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" s="1" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I56" s="1">
         <v>1</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="AC56" s="1">
         <v>2</v>
@@ -7225,7 +7431,7 @@
         <v>1</v>
       </c>
       <c r="AT56" s="1" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="BD56" s="1">
         <v>99</v>
@@ -7234,27 +7440,27 @@
         <v>0.1</v>
       </c>
       <c r="CN56" s="1" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="CO56" s="1" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="CR56" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="57" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" s="1" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I57" s="1">
         <v>1</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="AC57" s="1">
         <v>2</v>
@@ -7269,10 +7475,10 @@
         <v>1</v>
       </c>
       <c r="BO57" s="1" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="BP57" s="1" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="BS57" s="1">
         <v>0.1</v>
@@ -7284,30 +7490,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" s="1" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I58" s="1">
         <v>1</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="AC58" s="1">
         <v>1</v>
       </c>
       <c r="AG58" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="BD58" s="1">
         <v>1</v>
       </c>
       <c r="CN58" s="1" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="CR58" s="1">
         <v>0.2</v>
@@ -7316,24 +7522,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" s="1" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I59" s="1">
         <v>1</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="AC59" s="1">
         <v>1</v>
       </c>
       <c r="AG59" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="BD59" s="1">
         <v>1</v>
@@ -7342,7 +7548,7 @@
         <v>1</v>
       </c>
       <c r="CN59" s="1" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="CR59" s="1">
         <v>99999</v>
@@ -7355,6 +7561,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -7364,112 +7571,112 @@
   <dimension ref="A1:Q126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.25" style="1" customWidth="1"/>
-    <col min="3" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" customWidth="1"/>
-    <col min="9" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.08203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="22.1640625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="19" customWidth="1" style="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="1"/>
+    <col min="3" max="6" width="9" customWidth="1" style="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="1"/>
+    <col min="8" max="8" width="15" customWidth="1" style="1"/>
+    <col min="9" max="13" width="9" customWidth="1" style="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="1"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="1"/>
+    <col min="18" max="18" width="9" customWidth="1" style="1"/>
+    <col min="19" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7480,379 +7687,380 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="1" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="K9" s="1">
         <v>5</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="1" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="1" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="K13" s="1">
         <v>5</v>
       </c>
       <c r="Q13" s="1" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>583</v>
-      </c>
       <c r="J16" s="1" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="K16" s="1">
         <v>5</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="1" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="1" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>591</v>
       </c>
       <c r="K28" s="1">
         <v>5</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="1" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="1" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="K30" s="1">
         <v>5</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="1" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="K31" s="1">
         <v>5</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="1" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="1" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="1" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="125">
       <c r="A125" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="126">
       <c r="A126" s="1" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7861,37 +8069,37 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="1"/>
+    <col min="3" max="3" width="9" customWidth="1" style="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="1"/>
+    <col min="5" max="5" width="9" customWidth="1" style="1"/>
+    <col min="6" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7899,30 +8107,31 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7931,52 +8140,52 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
-    <col min="5" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
+    <col min="2" max="2" width="9" customWidth="1" style="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="1"/>
+    <col min="5" max="11" width="9" customWidth="1" style="1"/>
+    <col min="12" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="I1" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7990,28 +8199,29 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -8020,89 +8230,89 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.08203125" style="1" customWidth="1"/>
-    <col min="5" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
+    <col min="2" max="2" width="28" customWidth="1" style="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="1"/>
+    <col min="12" max="13" width="9" customWidth="1" style="1"/>
+    <col min="14" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8110,40 +8320,41 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>637</v>
+        <v>124</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -8153,51 +8364,51 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" style="1" customWidth="1"/>
-    <col min="7" max="9" width="9" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="1"/>
+    <col min="7" max="9" width="9" customWidth="1" style="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="1"/>
+    <col min="11" max="11" width="9" customWidth="1" style="1"/>
+    <col min="12" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8211,27 +8422,28 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -8240,85 +8452,85 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.9140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="1" customWidth="1"/>
-    <col min="6" max="7" width="15.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.9140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.75" style="1"/>
+    <col min="1" max="1" width="7.5" customWidth="1" style="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1" style="1"/>
+    <col min="3" max="3" width="21.9140625" customWidth="1" style="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1" style="1"/>
+    <col min="5" max="5" width="14" customWidth="1" style="1"/>
+    <col min="6" max="7" width="15.1640625" customWidth="1" style="1"/>
+    <col min="8" max="8" width="12.9140625" customWidth="1" style="1"/>
+    <col min="9" max="9" width="14" customWidth="1" style="1"/>
+    <col min="10" max="10" width="8.75" customWidth="1" style="1"/>
+    <col min="11" max="16384" width="8.75" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -8339,7 +8551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -8350,27 +8562,27 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -8379,27 +8591,27 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -8408,27 +8620,28 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/尊尼获加/莫菲丝.xlsx
+++ b/Excel/尊尼获加/莫菲丝.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="678">
   <si>
     <t>Id</t>
   </si>
@@ -670,6 +670,9 @@
     <t>Ablititys</t>
   </si>
   <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
     <t>DefaultAnimation</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
   </si>
   <si>
     <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>DieAnimation</t>
   </si>
   <si>
     <t>MaxAnimationScale</t>
@@ -2766,7 +2772,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BV7"/>
+  <dimension ref="A1:BX7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
@@ -2836,13 +2842,15 @@
     <col min="65" max="65" width="27.33203125" customWidth="1" style="2"/>
     <col min="66" max="66" width="9" customWidth="1" style="2"/>
     <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="68" max="68" width="9" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
     <col min="71" max="71" width="14" customWidth="1" style="2"/>
     <col min="72" max="72" width="14" customWidth="1" style="2"/>
     <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
+    <col min="74" max="74" width="14" customWidth="1" style="2"/>
+    <col min="75" max="75" width="9" customWidth="1" style="2"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3014,6 +3022,8 @@
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -3234,6 +3244,12 @@
       <c r="BV2" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="BW2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -3243,7 +3259,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3251,206 +3267,212 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE3" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="AF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="AQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AS3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AT3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AX3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="BA3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="BB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BN3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BX3" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="4">
@@ -3528,20 +3550,22 @@
       <c r="BT4" s="2"/>
       <c r="BU4" s="2"/>
       <c r="BV4" s="2"/>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>4</v>
@@ -3613,23 +3637,23 @@
         <v>4</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AN5" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AP5" s="2"/>
       <c r="AQ5" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR5" s="2">
         <v>1</v>
@@ -3651,72 +3675,74 @@
       <c r="BC5" s="2"/>
       <c r="BD5" s="2"/>
       <c r="BE5" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BF5" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BG5" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BH5" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BI5" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BJ5" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BK5" s="2">
         <v>6</v>
       </c>
       <c r="BL5" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BM5" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BN5" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BO5" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="BP5" s="2" t="s">
-        <v>150</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="BP5" s="2"/>
       <c r="BQ5" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BR5" s="2"/>
-      <c r="BS5" s="2" t="s">
         <v>152</v>
       </c>
+      <c r="BR5" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BS5" s="2"/>
       <c r="BT5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BU5" s="2"/>
-      <c r="BV5" s="2">
+        <v>154</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BV5" s="2"/>
+      <c r="BW5" s="2"/>
+      <c r="BX5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -3774,24 +3800,24 @@
       <c r="AH6" s="2"/>
       <c r="AI6" s="2"/>
       <c r="AJ6" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AM6" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AN6" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AO6" s="2"/>
       <c r="AP6" s="2"/>
       <c r="AQ6" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR6" s="2">
         <v>1</v>
@@ -3813,13 +3839,13 @@
       <c r="BC6" s="2"/>
       <c r="BD6" s="2"/>
       <c r="BE6" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BF6" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BG6" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BH6" s="2"/>
       <c r="BI6" s="2"/>
@@ -3828,47 +3854,49 @@
         <v>6</v>
       </c>
       <c r="BL6" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BM6" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BN6" s="2"/>
       <c r="BO6" s="2"/>
-      <c r="BP6" s="2" t="s">
-        <v>161</v>
-      </c>
+      <c r="BP6" s="2"/>
       <c r="BQ6" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="BR6" s="2"/>
-      <c r="BS6" s="2" t="s">
         <v>163</v>
       </c>
+      <c r="BR6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="BS6" s="2"/>
       <c r="BT6" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="BU6" s="2"/>
-      <c r="BV6" s="2">
+        <v>165</v>
+      </c>
+      <c r="BU6" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="BV6" s="2"/>
+      <c r="BW6" s="2"/>
+      <c r="BX6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -3928,24 +3956,24 @@
       <c r="AH7" s="2"/>
       <c r="AI7" s="2"/>
       <c r="AJ7" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL7" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AO7" s="2"/>
       <c r="AP7" s="2"/>
       <c r="AQ7" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AR7" s="2">
         <v>0</v>
@@ -3967,47 +3995,49 @@
       <c r="BC7" s="2"/>
       <c r="BD7" s="2"/>
       <c r="BE7" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BG7" s="2"/>
       <c r="BH7" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BI7" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BJ7" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BK7" s="2">
         <v>6</v>
       </c>
       <c r="BL7" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BM7" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BN7" s="2"/>
       <c r="BO7" s="2"/>
-      <c r="BP7" s="2" t="s">
-        <v>161</v>
-      </c>
+      <c r="BP7" s="2"/>
       <c r="BQ7" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="BR7" s="2"/>
-      <c r="BS7" s="2" t="s">
         <v>163</v>
       </c>
+      <c r="BR7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="BS7" s="2"/>
       <c r="BT7" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="BU7" s="2"/>
-      <c r="BV7" s="2">
+        <v>165</v>
+      </c>
+      <c r="BU7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="BV7" s="2"/>
+      <c r="BW7" s="2"/>
+      <c r="BX7" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4120,334 +4150,334 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="BV1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="CR1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="BW1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="CB1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="CS1" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -4461,331 +4491,331 @@
         <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>57</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="BO2" s="1" t="s">
         <v>85</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="BT2" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BU2" s="1" t="s">
         <v>101</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="CB2" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="CC2" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="CD2" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="CE2" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="CF2" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="CG2" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="CH2" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="CI2" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="CJ2" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="CK2" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="CL2" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="CM2" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="CN2" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="CO2" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="CP2" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="CQ2" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="CR2" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="CS2" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="CT2" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="CU2" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="CV2" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="CW2" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="CX2" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="CY2" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="CZ2" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="DA2" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="DB2" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="DC2" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="DD2" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="DE2" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="DF2" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="DG2" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="DH2" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="DI2" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3">
@@ -4805,339 +4835,339 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="M3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="W3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AJ3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AK3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="AL3" s="1" t="s">
+      <c r="AW3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="AM3" s="1" t="s">
+      <c r="BA3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BC3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="AN3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO3" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="AP3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="AQ3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="AU3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AV3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AW3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AX3" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="AY3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BB3" s="1" t="s">
+      <c r="BD3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="BC3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BD3" s="1" t="s">
+      <c r="BG3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="BI3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="BE3" s="1" t="s">
+      <c r="BK3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="BF3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BH3" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="BI3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK3" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="BL3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BM3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BP3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BQ3" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="BS3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="BN3" s="1" t="s">
+      <c r="BT3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="BO3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="BP3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="BQ3" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BT3" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="BU3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BV3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BW3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BX3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BY3" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="BZ3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="CA3" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="CB3" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="CC3" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="CD3" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="CE3" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="CF3" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="CG3" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="CH3" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="CI3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="CK3" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="CL3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="CN3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="CO3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="CP3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR3" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="CI3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="CK3" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="CL3" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="CM3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO3" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="CP3" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="CQ3" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="CR3" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="CS3" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="CT3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="CU3" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="CV3" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="CW3" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CX3" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CY3" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="CZ3" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="DA3" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="DB3" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="DC3" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="DD3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="DE3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="DF3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="DG3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="DH3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="DI3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AC5" s="1">
         <v>2</v>
@@ -5146,13 +5176,13 @@
         <v>1</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AT5" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AX5" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AZ5" s="1">
         <v>1</v>
@@ -5161,25 +5191,25 @@
         <v>1</v>
       </c>
       <c r="BO5" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="CB5" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="CG5" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CH5" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="CI5" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="CJ5" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="CN5" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="CO5" s="1">
         <v>-0.1</v>
@@ -5188,10 +5218,10 @@
         <v>2</v>
       </c>
       <c r="CW5" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="CY5" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="DG5" s="1">
         <v>1</v>
@@ -5199,16 +5229,16 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AC6" s="1">
         <v>2</v>
@@ -5217,13 +5247,13 @@
         <v>1</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AT6" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AX6" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AZ6" s="1">
         <v>1</v>
@@ -5232,22 +5262,22 @@
         <v>1</v>
       </c>
       <c r="CB6" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="CG6" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CH6" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="CI6" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="CJ6" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="CN6" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="CO6" s="1">
         <v>-0.1</v>
@@ -5256,10 +5286,10 @@
         <v>2</v>
       </c>
       <c r="CW6" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="CY6" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="DG6" s="1">
         <v>1</v>
@@ -5267,16 +5297,16 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AC7" s="1">
         <v>2</v>
@@ -5285,13 +5315,13 @@
         <v>1</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AX7" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AZ7" s="1">
         <v>1</v>
@@ -5300,22 +5330,22 @@
         <v>1</v>
       </c>
       <c r="CB7" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="CG7" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CH7" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="CI7" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="CJ7" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="CN7" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="CO7" s="1">
         <v>-0.1</v>
@@ -5324,10 +5354,10 @@
         <v>8</v>
       </c>
       <c r="CW7" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="CY7" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="DG7" s="1">
         <v>1</v>
@@ -5335,19 +5365,19 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AC8" s="1">
         <v>2</v>
@@ -5362,7 +5392,7 @@
         <v>99</v>
       </c>
       <c r="CN8" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="CR8" s="1">
         <v>99999</v>
@@ -5373,19 +5403,19 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AC9" s="1">
         <v>2</v>
@@ -5400,7 +5430,7 @@
         <v>99</v>
       </c>
       <c r="CN9" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="CO9" s="1">
         <v>-0.1</v>
@@ -5414,19 +5444,19 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AC10" s="1">
         <v>2</v>
@@ -5444,10 +5474,10 @@
         <v>0.1</v>
       </c>
       <c r="CN10" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="CO10" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="CR10" s="1">
         <v>0.2</v>
@@ -5458,22 +5488,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AC11" s="1">
         <v>2</v>
@@ -5491,10 +5521,10 @@
         <v>0.1</v>
       </c>
       <c r="CN11" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="CO11" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="CR11" s="1">
         <v>0.2</v>
@@ -5505,19 +5535,19 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="AC12" s="1">
         <v>2</v>
@@ -5535,7 +5565,7 @@
         <v>0.1</v>
       </c>
       <c r="CN12" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="CR12" s="1">
         <v>0.2</v>
@@ -5546,19 +5576,19 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AC13" s="1">
         <v>2</v>
@@ -5573,10 +5603,10 @@
         <v>1</v>
       </c>
       <c r="BO13" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="CN13" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="CR13" s="1">
         <v>10</v>
@@ -5587,34 +5617,34 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H14" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AW14" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD14" s="1">
+        <v>1</v>
+      </c>
+      <c r="CN14" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="AC14" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AW14" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD14" s="1">
-        <v>1</v>
-      </c>
-      <c r="CN14" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="CR14" s="1">
         <v>10</v>
@@ -5625,16 +5655,16 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AC15" s="1">
         <v>2</v>
@@ -5652,7 +5682,7 @@
         <v>0.1</v>
       </c>
       <c r="CN15" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="CR15" s="1">
         <v>0.2</v>
@@ -5663,19 +5693,19 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AC16" s="1">
         <v>2</v>
@@ -5690,16 +5720,16 @@
         <v>99</v>
       </c>
       <c r="BO16" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="BP16" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="CM16" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="CM16" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="CN16" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="CR16" s="1">
         <v>10.1</v>
@@ -5710,19 +5740,19 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AC17" s="1">
         <v>2</v>
@@ -5737,13 +5767,13 @@
         <v>99</v>
       </c>
       <c r="BP17" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="CM17" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="CN17" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="CR17" s="1">
         <v>99999</v>
@@ -5754,19 +5784,19 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AC18" s="1">
         <v>2</v>
@@ -5781,7 +5811,7 @@
         <v>1</v>
       </c>
       <c r="BP18" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BS18" s="1">
         <v>1</v>
@@ -5798,31 +5828,31 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AC19" s="1">
         <v>1</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD19" s="1">
         <v>1</v>
       </c>
       <c r="BO19" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="CU19" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="DI19" s="1">
         <v>1</v>
@@ -5830,16 +5860,16 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AC20" s="1">
         <v>2</v>
@@ -5868,10 +5898,10 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
@@ -5880,7 +5910,7 @@
         <v>1</v>
       </c>
       <c r="AJ21" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AV21" s="1">
         <v>20</v>
@@ -5889,7 +5919,7 @@
         <v>99</v>
       </c>
       <c r="BP21" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="BS21" s="1">
         <v>0.1</v>
@@ -5903,28 +5933,28 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AC22" s="1">
         <v>1</v>
       </c>
       <c r="AG22" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD22" s="1">
         <v>1</v>
       </c>
       <c r="CN22" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="CR22" s="1">
         <v>1.1</v>
@@ -5938,37 +5968,37 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I23" s="1">
         <v>1</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AC23" s="1">
         <v>1</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD23" s="1">
         <v>1</v>
       </c>
       <c r="CB23" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="CG23" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CN23" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="CO23" s="1">
         <v>0.15</v>
@@ -5979,19 +6009,19 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AC24" s="1">
         <v>2</v>
@@ -6006,16 +6036,16 @@
         <v>99</v>
       </c>
       <c r="BO24" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="BP24" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="CM24" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="CN24" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="CR24" s="1">
         <v>99999</v>
@@ -6029,16 +6059,16 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AC25" s="1">
         <v>1</v>
@@ -6050,24 +6080,24 @@
         <v>99</v>
       </c>
       <c r="CU25" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I26" s="1">
         <v>1</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AC26" s="1">
         <v>2</v>
@@ -6079,7 +6109,7 @@
         <v>20</v>
       </c>
       <c r="AX26" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AZ26" s="1">
         <v>9999999</v>
@@ -6091,10 +6121,10 @@
         <v>99</v>
       </c>
       <c r="CM26" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="CN26" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="CR26" s="1">
         <v>99999</v>
@@ -6108,43 +6138,43 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AC27" s="1">
         <v>1</v>
       </c>
       <c r="AG27" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD27" s="1">
         <v>1</v>
       </c>
       <c r="BO27" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="BP27" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="BT27" s="1">
         <v>0.2</v>
@@ -6159,16 +6189,16 @@
         <v>2</v>
       </c>
       <c r="BY27" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="CB27" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="CG27" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CN27" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="CO27" s="1">
         <v>0.08</v>
@@ -6179,13 +6209,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AC28" s="1">
         <v>2</v>
@@ -6194,16 +6224,16 @@
         <v>1</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AR28" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AW28" s="1">
         <v>1</v>
       </c>
       <c r="AX28" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AZ28" s="1">
         <v>1.6</v>
@@ -6212,28 +6242,28 @@
         <v>2</v>
       </c>
       <c r="CG28" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CH28" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="CI28" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="CJ28" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="CN28" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="CR28" s="1">
         <v>5</v>
       </c>
       <c r="CW28" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="CY28" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="DG28" s="1">
         <v>1</v>
@@ -6241,19 +6271,19 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AC29" s="1">
         <v>2</v>
@@ -6268,7 +6298,7 @@
         <v>99</v>
       </c>
       <c r="CN29" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="CO29" s="1">
         <v>-0.1</v>
@@ -6282,28 +6312,28 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G30" s="1">
         <v>3</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AB30" s="1">
         <v>1</v>
@@ -6312,13 +6342,13 @@
         <v>1</v>
       </c>
       <c r="AG30" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD30" s="1">
         <v>1</v>
       </c>
       <c r="BO30" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="BT30" s="1">
         <v>15</v>
@@ -6333,19 +6363,19 @@
         <v>1</v>
       </c>
       <c r="BY30" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="CB30" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="CG30" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CM30" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="CN30" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="CR30" s="1">
         <v>15</v>
@@ -6353,13 +6383,13 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AC31" s="1">
         <v>2</v>
@@ -6368,13 +6398,13 @@
         <v>1</v>
       </c>
       <c r="AO31" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AT31" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AX31" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AZ31" s="1">
         <v>1.2</v>
@@ -6395,16 +6425,16 @@
         <v>1</v>
       </c>
       <c r="CH31" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="CI31" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="CJ31" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="CN31" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="CO31" s="1">
         <v>-0.1</v>
@@ -6416,7 +6446,7 @@
         <v>2</v>
       </c>
       <c r="CY31" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="DG31" s="1">
         <v>1</v>
@@ -6424,19 +6454,19 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AC32" s="1">
         <v>2</v>
@@ -6451,10 +6481,10 @@
         <v>99</v>
       </c>
       <c r="CM32" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="CN32" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="CR32" s="1">
         <v>2</v>
@@ -6465,43 +6495,43 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I33" s="1">
         <v>1</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AC33" s="1">
         <v>1</v>
       </c>
       <c r="AG33" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD33" s="1">
         <v>1</v>
       </c>
       <c r="BP33" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="CB33" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="CG33" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CM33" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="CN33" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="CR33" s="1">
         <v>1</v>
@@ -6509,13 +6539,13 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AC34" s="1">
         <v>2</v>
@@ -6524,13 +6554,13 @@
         <v>1</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AT34" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AX34" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AZ34" s="1">
         <v>3</v>
@@ -6548,13 +6578,13 @@
         <v>1</v>
       </c>
       <c r="CG34" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CJ34" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="CN34" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="CO34" s="1">
         <v>0.8</v>
@@ -6566,7 +6596,7 @@
         <v>8</v>
       </c>
       <c r="CY34" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="DG34" s="1">
         <v>1</v>
@@ -6574,13 +6604,13 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AC35" s="1">
         <v>2</v>
@@ -6595,7 +6625,7 @@
         <v>99</v>
       </c>
       <c r="CM35" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="DG35" s="1">
         <v>1</v>
@@ -6603,19 +6633,19 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I36" s="1">
         <v>1</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AC36" s="1">
         <v>2</v>
@@ -6633,10 +6663,10 @@
         <v>0.1</v>
       </c>
       <c r="CN36" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="CO36" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="CR36" s="1">
         <v>0.2</v>
@@ -6647,22 +6677,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AC37" s="1">
         <v>2</v>
@@ -6680,10 +6710,10 @@
         <v>0.1</v>
       </c>
       <c r="CN37" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="CO37" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="CR37" s="1">
         <v>0.2</v>
@@ -6694,19 +6724,19 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AC38" s="1">
         <v>1</v>
@@ -6715,21 +6745,21 @@
         <v>1</v>
       </c>
       <c r="AG38" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD38" s="1">
         <v>1</v>
       </c>
       <c r="CU38" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
@@ -6738,7 +6768,7 @@
         <v>1</v>
       </c>
       <c r="AJ39" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AW39" s="1">
         <v>1</v>
@@ -6750,7 +6780,7 @@
         <v>0.1</v>
       </c>
       <c r="CN39" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="CR39" s="1">
         <v>0.2</v>
@@ -6761,22 +6791,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AC40" s="1">
         <v>1</v>
       </c>
       <c r="AJ40" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AV40" s="1">
         <v>20</v>
@@ -6788,7 +6818,7 @@
         <v>0.1</v>
       </c>
       <c r="CN40" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="CO40" s="1">
         <v>80</v>
@@ -6802,28 +6832,28 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AB41" s="1">
         <v>1</v>
@@ -6835,13 +6865,13 @@
         <v>1</v>
       </c>
       <c r="AO41" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AT41" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AX41" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AZ41" s="1">
         <v>1</v>
@@ -6850,7 +6880,7 @@
         <v>4</v>
       </c>
       <c r="BO41" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="BT41" s="1">
         <v>35</v>
@@ -6865,34 +6895,34 @@
         <v>1</v>
       </c>
       <c r="BY41" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="CB41" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="CE41" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="CG41" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CH41" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="CI41" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="CJ41" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="CN41" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="CR41" s="1">
         <v>1</v>
       </c>
       <c r="CY41" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="DG41" s="1">
         <v>1</v>
@@ -6903,16 +6933,16 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AC42" s="1">
         <v>1</v>
@@ -6921,10 +6951,10 @@
         <v>1</v>
       </c>
       <c r="BP42" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="CN42" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="CO42" s="1">
         <v>-0.8</v>
@@ -6938,13 +6968,13 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AC43" s="1">
         <v>2</v>
@@ -6953,13 +6983,13 @@
         <v>1</v>
       </c>
       <c r="AT43" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="BD43" s="1">
         <v>99</v>
       </c>
       <c r="CN43" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="CR43" s="1">
         <v>15</v>
@@ -6970,13 +7000,13 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AC44" s="1">
         <v>2</v>
@@ -6994,10 +7024,10 @@
         <v>0.1</v>
       </c>
       <c r="CN44" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="CO44" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="CR44" s="1">
         <v>0.2</v>
@@ -7008,40 +7038,40 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I45" s="1">
         <v>1</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AC45" s="1">
         <v>1</v>
       </c>
       <c r="AG45" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD45" s="1">
         <v>1</v>
       </c>
       <c r="CB45" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="CG45" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CM45" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="CN45" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="CR45" s="1">
         <v>1</v>
@@ -7049,22 +7079,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I46" s="1">
         <v>1</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AC46" s="1">
         <v>1</v>
       </c>
       <c r="AJ46" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AV46" s="1">
         <v>20</v>
@@ -7076,7 +7106,7 @@
         <v>0.1</v>
       </c>
       <c r="CN46" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="CR46" s="1">
         <v>0.2</v>
@@ -7090,19 +7120,19 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I47" s="1">
         <v>1</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N47" s="1">
         <v>1</v>
@@ -7111,45 +7141,45 @@
         <v>1</v>
       </c>
       <c r="AG47" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD47" s="1">
         <v>1</v>
       </c>
       <c r="CB47" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="CG47" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I49" s="1">
         <v>1</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AC49" s="1">
         <v>1</v>
       </c>
       <c r="AG49" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD49" s="1">
         <v>1</v>
@@ -7157,10 +7187,10 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AC50" s="1">
         <v>2</v>
@@ -7169,16 +7199,16 @@
         <v>1</v>
       </c>
       <c r="AO50" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AR50" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AT50" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AX50" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AZ50" s="1">
         <v>1</v>
@@ -7187,28 +7217,28 @@
         <v>1</v>
       </c>
       <c r="BO50" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="CB50" s="1" t="s">
         <v>61</v>
       </c>
       <c r="CG50" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CH50" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="CI50" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="CJ50" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="CM50" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="CY50" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="DG50" s="1">
         <v>1</v>
@@ -7216,13 +7246,13 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AC51" s="1">
         <v>2</v>
@@ -7231,16 +7261,16 @@
         <v>1</v>
       </c>
       <c r="AO51" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AR51" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AT51" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AX51" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AZ51" s="1">
         <v>1</v>
@@ -7252,28 +7282,28 @@
         <v>61</v>
       </c>
       <c r="CG51" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CH51" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="CI51" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="CJ51" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="CM51" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="CN51" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="CR51" s="1">
         <v>15</v>
       </c>
       <c r="CY51" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="DG51" s="1">
         <v>1</v>
@@ -7281,37 +7311,37 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="I53" s="1">
         <v>1</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AC53" s="1">
         <v>1</v>
       </c>
       <c r="AG53" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD53" s="1">
         <v>1</v>
       </c>
       <c r="CN53" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="CR53" s="1">
         <v>99999</v>
@@ -7319,10 +7349,10 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AC54" s="1">
         <v>2</v>
@@ -7331,16 +7361,16 @@
         <v>1</v>
       </c>
       <c r="AO54" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AR54" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AT54" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AX54" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AZ54" s="1">
         <v>1</v>
@@ -7352,19 +7382,19 @@
         <v>61</v>
       </c>
       <c r="CG54" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CH54" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="CI54" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="CJ54" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="CY54" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="DG54" s="1">
         <v>1</v>
@@ -7372,16 +7402,16 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I55" s="1">
         <v>1</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AC55" s="1">
         <v>2</v>
@@ -7390,22 +7420,22 @@
         <v>1</v>
       </c>
       <c r="AT55" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="BD55" s="1">
         <v>99</v>
       </c>
       <c r="BO55" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="BS55" s="1">
         <v>0.1</v>
       </c>
       <c r="CN55" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="CO55" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="CR55" s="1">
         <v>0.2</v>
@@ -7413,16 +7443,16 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I56" s="1">
         <v>1</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AC56" s="1">
         <v>2</v>
@@ -7431,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="AT56" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="BD56" s="1">
         <v>99</v>
@@ -7440,10 +7470,10 @@
         <v>0.1</v>
       </c>
       <c r="CN56" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="CO56" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="CR56" s="1">
         <v>0.2</v>
@@ -7451,16 +7481,16 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I57" s="1">
         <v>1</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AC57" s="1">
         <v>2</v>
@@ -7475,10 +7505,10 @@
         <v>1</v>
       </c>
       <c r="BO57" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="BP57" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="BS57" s="1">
         <v>0.1</v>
@@ -7492,28 +7522,28 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I58" s="1">
         <v>1</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AC58" s="1">
         <v>1</v>
       </c>
       <c r="AG58" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD58" s="1">
         <v>1</v>
       </c>
       <c r="CN58" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="CR58" s="1">
         <v>0.2</v>
@@ -7524,22 +7554,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I59" s="1">
         <v>1</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AC59" s="1">
         <v>1</v>
       </c>
       <c r="AG59" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BD59" s="1">
         <v>1</v>
@@ -7548,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="CN59" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="CR59" s="1">
         <v>99999</v>
@@ -7593,37 +7623,37 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="2">
@@ -7637,43 +7667,43 @@
         <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>57</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
@@ -7687,373 +7717,373 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="K9" s="1">
         <v>5</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="K13" s="1">
         <v>5</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="K16" s="1">
         <v>5</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="K28" s="1">
         <v>5</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="K30" s="1">
         <v>5</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="K31" s="1">
         <v>5</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -8082,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="2">
@@ -8093,10 +8123,10 @@
         <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
@@ -8107,24 +8137,24 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
   </sheetData>
@@ -8150,7 +8180,7 @@
   <sheetData>
     <row r="1">
       <c r="I1" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2">
@@ -8164,25 +8194,25 @@
         <v>53</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
@@ -8199,22 +8229,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -8244,34 +8274,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="2">
@@ -8279,34 +8309,34 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>103</v>
@@ -8320,34 +8350,34 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -8381,28 +8411,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>58</v>
@@ -8422,22 +8452,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -8469,28 +8499,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="2">
@@ -8498,28 +8528,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3">
@@ -8527,10 +8557,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -8562,27 +8592,27 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -8591,27 +8621,27 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>670</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -8620,22 +8650,22 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>673</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>
